--- a/Leads.xlsx
+++ b/Leads.xlsx
@@ -7,7 +7,7 @@
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="CRM_Leads" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -46,8 +46,10 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="1">
+  <cellXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="49" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="3" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -413,8 +415,26 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:P46"/>
+  <dimension ref="A1:P47"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="21" customWidth="1" min="1" max="1"/>
+    <col width="27" customWidth="1" min="2" max="2"/>
+    <col width="35" customWidth="1" min="3" max="3"/>
+    <col width="20" customWidth="1" min="4" max="4"/>
+    <col width="15" customWidth="1" min="5" max="5"/>
+    <col width="22" customWidth="1" min="6" max="6"/>
+    <col width="12" customWidth="1" min="7" max="7"/>
+    <col width="12" customWidth="1" min="8" max="8"/>
+    <col width="270" customWidth="1" min="9" max="9"/>
+    <col width="101" customWidth="1" min="10" max="10"/>
+    <col width="20" customWidth="1" min="11" max="11"/>
+    <col width="14" customWidth="1" min="12" max="12"/>
+    <col width="13" customWidth="1" min="13" max="13"/>
+    <col width="17" customWidth="1" min="14" max="14"/>
+    <col width="36" customWidth="1" min="15" max="15"/>
+    <col width="18" customWidth="1" min="16" max="16"/>
+  </cols>
   <sheetData>
     <row r="1">
       <c r="A1" t="inlineStr">
@@ -499,23 +519,25 @@
       </c>
     </row>
     <row r="2">
-      <c r="A2" t="inlineStr">
-        <is>
-          <t>LEAD-AGENDA-GLOBAL</t>
-        </is>
-      </c>
-      <c r="B2" t="inlineStr">
-        <is>
-          <t>2026-06-05T23:08:01.417Z</t>
+      <c r="A2" s="1" t="inlineStr">
+        <is>
+          <t>1778195260246</t>
+        </is>
+      </c>
+      <c r="B2" s="1" t="inlineStr">
+        <is>
+          <t>2026-06-05T12:42:07.176Z</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>Agenda Global (Citas Genéricas)</t>
-        </is>
-      </c>
-      <c r="D2" t="n">
-        <v>0</v>
+          <t>✅Paola</t>
+        </is>
+      </c>
+      <c r="D2" s="1" t="inlineStr">
+        <is>
+          <t>+1 (720) 581-2521</t>
+        </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
@@ -525,58 +547,56 @@
       <c r="F2" t="inlineStr"/>
       <c r="G2" t="inlineStr">
         <is>
-          <t>inactivo</t>
+          <t>visita</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>inactivo</t>
-        </is>
-      </c>
-      <c r="I2" t="inlineStr">
-        <is>
-          <t>Contenedor para sincronizar citas antiguas o sin datos en la nube.</t>
-        </is>
-      </c>
-      <c r="J2" t="inlineStr"/>
+          <t>activo</t>
+        </is>
+      </c>
+      <c r="I2" s="1" t="inlineStr">
+        <is>
+          <t>Presupuesto $100 mlls . Casa para la mamá, un piso. Ubicada en el exterior . . desea comprar Aun no tiene el familiar disponible que le visite los dos inmuebles. Codg. 4733 limonar - Primavera y Códg. 514 Caracoli - Primavera . . . ya tiene el contacto de la cliente.</t>
+        </is>
+      </c>
+      <c r="J2" s="1" t="inlineStr"/>
       <c r="K2" t="inlineStr"/>
       <c r="L2" t="inlineStr"/>
-      <c r="M2" t="n">
+      <c r="M2" t="inlineStr">
+        <is>
+          <t>manual</t>
+        </is>
+      </c>
+      <c r="N2" t="n">
         <v>0</v>
       </c>
-      <c r="N2" t="inlineStr">
-        <is>
-          <t>{"id":"LEAD-AGENDA-GLOBAL","fecha":"2026-06-05T22:50:41.132Z","nombre":"Agenda Global (Citas Genéricas)","celular":0,"tipo":"cliente","estado":"inactivo","etiqueta":"inactivo","notas":"Contenedor para sincronizar citas antiguas o sin datos en la nube.","metodoPago":[],"fromCloud":true,"visitas":[{"id":"1779119510834","codigo":"662","fecha":"2026-05-18","hora":"","estado":"agendada","oferto":"no","oferta":"","notas":"","cliente":"María Nohora  Rojas","celular":"3124797922","inmobiliaria":""},{"id":"1780002087534","codigo":"223","fecha":"2026-05-29","hora":"09:00","estado":"agendada","oferto":"no","oferta":"","notas":"Don Ignacio enseña la casa","cliente":"Oscar Luis Suarez Cubillos","celular":"3118571606","inmobiliaria":"","updatedAt":1780002087534},{"id":"1777996776453","codigo":"622","fecha":"2026-05-09","hora":"","estado":"solicito_visita","oferto":"no","oferta":"","notas":"Inmueble de Rustika. Desocupada. Propietario viajando. hasta el sábado en la tarde  la visita. No se ha coordinado la hora.","cliente":"Hector","celular":"3159057825","inmobiliaria":"","updatedAt":1779144488081},{"id":"1779744890238","codigo":"449","fecha":"2026-05-26","hora":"","estado":"agendada","oferto":"no","oferta":"","notas":"","cliente":"Paola","celular":"+1 (720) 581-2521","inmobiliaria":"","updatedAt":1779744890238},{"id":"1779803459727","codigo":"325","fecha":"2026-05-26","hora":"","estado":"solicito_visita","oferto":"no","oferta":"","notas":"","cliente":"Paola","celular":"+1 (720) 581-2521","inmobiliaria":"","updatedAt":1779803459727},{"id":"1779803499789","codigo":"514","fecha":"2026-05-26","hora":"","estado":"solicito_visita","oferto":"no","oferta":"","notas":"","cliente":"Paola","celular":"+1 (720) 581-2521","inmobiliaria":"","updatedAt":1779803499789},{"id":"1780001589171","codigo":"078","fecha":"2026-05-29","hora":"16:00","estado":"agendada","oferto":"no","oferta":"","notas":"","cliente":"Martha Cubillos","celular":"3209029142","inmobiliaria":"","updatedAt":1780001589171}]}</t>
-        </is>
-      </c>
-      <c r="O2" t="inlineStr">
-        <is>
-          <t>{"id":"LEAD-AGENDA-GLOBAL","fecha":"2026-06-05T22:48:39.864Z","nombre":"Agenda Global (Citas Genéricas)","celular":0,"tipo":"cliente","estado":"inactivo","etiqueta":"inactivo","notas":"Contenedor para sincronizar citas antiguas o sin datos en la nube.","metodoPago":[],"fromCloud":true,"visitas":[{"id":"1779119510834","codigo":"662","fecha":"2026-05-18","hora":"","estado":"agendada","oferto":"no","oferta":"","notas":"","cliente":"María Nohora  Rojas","celular":"3124797922","inmobiliaria":""},{"id":"1780002087534","codigo":"223","fecha":"2026-05-29","hora":"09:00","estado":"agendada","oferto":"no","oferta":"","notas":"Don Ignacio enseña la casa","cliente":"Oscar Luis Suarez Cubillos","celular":"3118571606","inmobiliaria":"","updatedAt":1780002087534},{"id":"1777996776453","codigo":"622","fecha":"2026-05-09","hora":"","estado":"solicito_visita","oferto":"no","oferta":"","notas":"Inmueble de Rustika. Desocupada. Propietario viajando. hasta el sábado en la tarde  la visita. No se ha coordinado la hora.","cliente":"Hector","celular":"3159057825","inmobiliaria":"","updatedAt":1779144488081},{"id":"1779744890238","codigo":"449","fecha":"2026-05-26","hora":"","estado":"agendada","oferto":"no","oferta":"","notas":"","cliente":"Paola","celular":"+1 (720) 581-2521","inmobiliaria":"","updatedAt":1779744890238},{"id":"1779803459727","codigo":"325","fecha":"2026-05-26","hora":"","estado":"solicito_visita","oferto":"no","oferta":"","notas":"","cliente":"Paola","celular":"+1 (720) 581-2521","inmobiliaria":"","updatedAt":1779803459727},{"id":"1779803499789","codigo":"514","fecha":"2026-05-26","hora":"","estado":"solicito_visita","oferto":"no","oferta":"","notas":"","cliente":"Paola","celular":"+1 (720) 581-2521","inmobiliaria":"","updatedAt":1779803499789},{"id":"1780001589171","codigo":"078","fecha":"2026-05-29","hora":"16:00","estado":"agendada","oferto":"no","oferta":"","notas":"","cliente":"Martha Cubillos","celular":"3209029142","inmobiliaria":"","updatedAt":1780001589171}]}</t>
-        </is>
-      </c>
-      <c r="P2" t="inlineStr">
-        <is>
-          <t>{"id":"LEAD-AGENDA-GLOBAL","fecha":"2026-06-05T22:45:41.001Z","nombre":"Agenda Global (Citas Genéricas)","celular":0,"tipo":"cliente","estado":"inactivo","etiqueta":"inactivo","notas":"Contenedor para sincronizar citas antiguas o sin datos en la nube.","metodoPago":[],"fromCloud":true,"visitas":[{"id":"1779119510834","codigo":"662","fecha":"2026-05-18","hora":"","estado":"agendada","oferto":"no","oferta":"","notas":"","cliente":"María Nohora  Rojas","celular":"3124797922","inmobiliaria":""},{"id":"1780002087534","codigo":"223","fecha":"2026-05-29","hora":"09:00","estado":"agendada","oferto":"no","oferta":"","notas":"Don Ignacio enseña la casa","cliente":"Oscar Luis Suarez Cubillos","celular":"3118571606","inmobiliaria":"","updatedAt":1780002087534},{"id":"1777996776453","codigo":"622","fecha":"2026-05-09","hora":"","estado":"solicito_visita","oferto":"no","oferta":"","notas":"Inmueble de Rustika. Desocupada. Propietario viajando. hasta el sábado en la tarde  la visita. No se ha coordinado la hora.","cliente":"Hector","celular":"3159057825","inmobiliaria":"","updatedAt":1779144488081},{"id":"1779744890238","codigo":"449","fecha":"2026-05-26","hora":"","estado":"agendada","oferto":"no","oferta":"","notas":"","cliente":"Paola","celular":"+1 (720) 581-2521","inmobiliaria":"","updatedAt":1779744890238},{"id":"1779803459727","codigo":"325","fecha":"2026-05-26","hora":"","estado":"solicito_visita","oferto":"no","oferta":"","notas":"","cliente":"Paola","celular":"+1 (720) 581-2521","inmobiliaria":"","updatedAt":1779803459727},{"id":"1779803499789","codigo":"514","fecha":"2026-05-26","hora":"","estado":"solicito_visita","oferto":"no","oferta":"","notas":"","cliente":"Paola","celular":"+1 (720) 581-2521","inmobiliaria":"","updatedAt":1779803499789},{"id":"1780001589171","codigo":"078","fecha":"2026-05-29","hora":"16:00","estado":"agendada","oferto":"no","oferta":"","notas":"","cliente":"Martha Cubillos","celular":"3209029142","inmobiliaria":"","updatedAt":1780001589171}]}</t>
+      <c r="O2" s="1" t="inlineStr"/>
+      <c r="P2" s="1" t="inlineStr">
+        <is>
+          <t>{"id": 1778195260246, "fecha": "2026-06-05T12:42:07.176Z", "nombre": "✅Paola", "celular": "+1 (720) 581-2521", "tipo": "cliente", "estado": "visita", "etiqueta": "activo", "notas": "Presupuesto $100 mlls . Casa para la mamá, un piso. Ubicada en el exterior . . desea comprar Aun no tiene el familiar disponible que le visite los dos inmuebles. Codg. 4733 limonar - Primavera y Códg. 514 Caracoli - Primavera . . . ya tiene el contacto de la cliente."}</t>
         </is>
       </c>
     </row>
     <row r="3">
-      <c r="A3" t="n">
-        <v>1778195260246</v>
-      </c>
-      <c r="B3" t="inlineStr">
-        <is>
-          <t>2026-06-05T16:53:04.624Z</t>
+      <c r="A3" s="1" t="inlineStr">
+        <is>
+          <t>1777224335719</t>
+        </is>
+      </c>
+      <c r="B3" s="1" t="inlineStr">
+        <is>
+          <t>2026-06-03T15:53:56.748Z</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>✅Paola</t>
-        </is>
-      </c>
-      <c r="D3" t="inlineStr">
-        <is>
-          <t>+1 (720) 581-2521</t>
+          <t>Albeiro Prieto</t>
+        </is>
+      </c>
+      <c r="D3" s="1" t="inlineStr">
+        <is>
+          <t>3208788700</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
@@ -587,49 +607,53 @@
       <c r="F3" t="inlineStr"/>
       <c r="G3" t="inlineStr">
         <is>
-          <t>visita</t>
+          <t>enviando</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>activo</t>
-        </is>
-      </c>
-      <c r="I3" t="inlineStr">
-        <is>
-          <t>Presupuesto $100 mlls . Casa para la mamá, un piso. Ubicada en el exterior . . desea comprar Aun no tiene el familiar disponible que le visite los dos inmuebles.  Codg. 4733 limonar - Primavera y  Códg. 514 Caracoli - Primavera .  . . ya tiene el contacto de la cliente.</t>
-        </is>
-      </c>
-      <c r="J3" t="inlineStr"/>
+          <t>tibio</t>
+        </is>
+      </c>
+      <c r="I3" s="1" t="inlineStr"/>
+      <c r="J3" s="1" t="inlineStr"/>
       <c r="K3" t="inlineStr"/>
       <c r="L3" t="inlineStr"/>
-      <c r="M3" t="inlineStr"/>
+      <c r="M3" t="inlineStr">
+        <is>
+          <t>manual</t>
+        </is>
+      </c>
       <c r="N3" t="n">
         <v>0</v>
       </c>
-      <c r="O3" t="inlineStr"/>
-      <c r="P3" t="inlineStr">
-        <is>
-          <t>{"id":1778195260246,"fecha":"2026-06-05T12:42:07.176Z","nombre":"✅Paola","celular":"+1 (720) 581-2521","tipo":"cliente","estado":"visita","etiqueta":"activo","notas":"Presupuesto $100 mlls . Casa para la mamá, un piso. Ubicada en el exterior . . desea comprar Aun no tiene el familiar disponible que le visite los dos inmuebles.  Codg. 4733 limonar - Primavera y  Códg. 514 Caracoli - Primavera .  . . ya tiene el contacto de la cliente."}</t>
+      <c r="O3" s="1" t="inlineStr"/>
+      <c r="P3" s="1" t="inlineStr">
+        <is>
+          <t>{"id": 1777224335719, "fecha": "2026-06-03T15:53:56.748Z", "nombre": "Albeiro Prieto", "celular": "3208788700", "tipo": "cliente", "estado": "enviando", "etiqueta": "tibio", "notas": ""}</t>
         </is>
       </c>
     </row>
     <row r="4">
-      <c r="A4" t="n">
-        <v>1777566252041</v>
-      </c>
-      <c r="B4" t="inlineStr">
-        <is>
-          <t>2026-06-03T15:27:16.178Z</t>
+      <c r="A4" s="1" t="inlineStr">
+        <is>
+          <t>U-1780352084268612</t>
+        </is>
+      </c>
+      <c r="B4" s="1" t="inlineStr">
+        <is>
+          <t>2026-06-04T23:06:06.370Z</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Reinaldo  Diaz</t>
-        </is>
-      </c>
-      <c r="D4" t="n">
-        <v>3102684886</v>
+          <t>Andrea</t>
+        </is>
+      </c>
+      <c r="D4" s="1" t="inlineStr">
+        <is>
+          <t>3157094054</t>
+        </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
@@ -639,63 +663,57 @@
       <c r="F4" t="inlineStr"/>
       <c r="G4" t="inlineStr">
         <is>
-          <t>inactivo</t>
+          <t>proceso</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>inactivo</t>
-        </is>
-      </c>
-      <c r="I4" t="inlineStr">
-        <is>
-          <t>Visita del  4 al 10 de mayo - Se encuentra en el exterior.</t>
-        </is>
-      </c>
-      <c r="J4" t="inlineStr">
-        <is>
-          <t>Tipos: Casa rentable</t>
-        </is>
-      </c>
-      <c r="K4" t="inlineStr">
-        <is>
-          <t>Efectivo, Crédito</t>
-        </is>
-      </c>
+          <t>activo</t>
+        </is>
+      </c>
+      <c r="I4" s="1" t="inlineStr">
+        <is>
+          <t>Compra Apto en conjunto codg. 864 Bosques de Tamarindo - Jennifer y Codg. 1669 Tierra alta C&amp;C . . Ya se solicito verificación y visita. Ha tomado la decisión de comprar Codg. 864 Bosques de Tamarindo $250 - $230 - Jennifer.</t>
+        </is>
+      </c>
+      <c r="J4" s="1" t="inlineStr"/>
+      <c r="K4" t="inlineStr"/>
       <c r="L4" t="inlineStr"/>
       <c r="M4" t="inlineStr">
         <is>
-          <t>semanal</t>
+          <t>manual</t>
         </is>
       </c>
       <c r="N4" t="n">
         <v>0</v>
       </c>
-      <c r="O4" t="inlineStr"/>
-      <c r="P4" t="inlineStr">
-        <is>
-          <t>{"id":"1777566252041","tipo":"cliente","nombre":"Reinaldo  Diaz","celular":"3102684886","notas":"Visita del  4 al 10 de mayo - Se encuentra en el exterior.","metodoPago":["Efectivo","Crédito"],"estado":"inactivo","etiqueta":"inactivo","filtros":{"tipoInmueble":["Casa rentable"],"rangoPrecio":[],"zona":[],"habitaciones":[],"garaje":[],"pisos":[],"ubicacion":[],"piscina":[],"cocina":[],"barrio":[],"conjunto":[],"buscar":"223"},"frecuencia":"semanal","maxPorEnvio":4,"nombreInmobiliaria":"","nombreAgente":"","propsFiltradas":["223"],"propsEnviadas":[],"proximosEnvios":[{"fecha":"2026-05-07","codigos":[],"enviado":false,"esCheck":true}],"historialEnvios":[],"visitas":[],"creadoEn":"2026-04-30T16:24:12.044Z","fromCloud":true}</t>
+      <c r="O4" s="1" t="inlineStr"/>
+      <c r="P4" s="1" t="inlineStr">
+        <is>
+          <t>{"id": "U-1780352084268612", "fecha": "2026-06-04T23:06:06.370Z", "nombre": "Andrea", "celular": "3157094054", "tipo": "cliente", "estado": "proceso", "etiqueta": "activo", "notas": "Compra Apto en conjunto codg. 864 Bosques de Tamarindo - Jennifer y Codg. 1669 Tierra alta C&amp;C . . Ya se solicito verificación y visita. Ha tomado la decisión de comprar Codg. 864 Bosques de Tamarindo $250 - $230 - Jennifer.", "metodoPago": [], "Fecha Actualización": "2026-06-06T03:30:23.422Z", "fromCloud": true, "_localEditedAt": "2026-06-06T03:30:49.408Z"}</t>
         </is>
       </c>
     </row>
     <row r="5">
-      <c r="A5" t="inlineStr">
-        <is>
-          <t>U-1780093548365515</t>
-        </is>
-      </c>
-      <c r="B5" t="inlineStr">
-        <is>
-          <t>2026-06-05T16:52:35.104Z</t>
+      <c r="A5" s="1" t="inlineStr">
+        <is>
+          <t>U-1778329096171654</t>
+        </is>
+      </c>
+      <c r="B5" s="1" t="inlineStr">
+        <is>
+          <t>2026-04-28T15:42:57.486Z</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Natalia Cerquera</t>
-        </is>
-      </c>
-      <c r="D5" t="n">
-        <v>3102739529</v>
+          <t>Andres Silva</t>
+        </is>
+      </c>
+      <c r="D5" s="1" t="inlineStr">
+        <is>
+          <t>3116181559</t>
+        </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
@@ -713,23 +731,23 @@
           <t>tibio</t>
         </is>
       </c>
-      <c r="I5" t="inlineStr">
-        <is>
-          <t>Compra casa -con garaje-Norte-Créd. Hip. $260mlls</t>
-        </is>
-      </c>
-      <c r="J5" t="inlineStr">
-        <is>
-          <t>Tipos: Casa | Zonas: Norte | Precio: 150000000 - 266000000</t>
+      <c r="I5" s="1" t="inlineStr">
+        <is>
+          <t>Compra casa rentable en Las Granjas $250mlls.</t>
+        </is>
+      </c>
+      <c r="J5" s="1" t="inlineStr">
+        <is>
+          <t>Tipos: Casa, Casa rentable | Zonas: Norte | Precio: 0 - 303000000</t>
         </is>
       </c>
       <c r="K5" t="inlineStr">
         <is>
-          <t>Crédito, Efectivo</t>
-        </is>
-      </c>
-      <c r="L5" t="n">
-        <v>266000000</v>
+          <t>Efectivo, Crédito</t>
+        </is>
+      </c>
+      <c r="L5" s="2" t="n">
+        <v>303000000</v>
       </c>
       <c r="M5" t="inlineStr">
         <is>
@@ -739,33 +757,37 @@
       <c r="N5" t="n">
         <v>8</v>
       </c>
-      <c r="O5" t="inlineStr">
-        <is>
-          <t>2026-05-29 (8)</t>
-        </is>
-      </c>
-      <c r="P5" t="inlineStr">
-        <is>
-          <t>{"id":"U-1780093548365515","tipo":"cliente","nombre":"Natalia Cerquera","celular":"3102739529","notas":"Compra casa -con garaje-Norte-Créd. Hip. $260mlls","metodoPago":["Crédito","Efectivo"],"estado":"enviando","etiqueta":"tibio","filtros":{"tipoInmueble":["Casa"],"rangoPrecio":[],"zona":["Norte"],"habitaciones":[],"garaje":["1"],"pisos":[],"ubicacion":[],"piscina":[],"cocina":[],"barrio":[],"conjunto":[],"minPrice":150000000,"maxPrice":266000000,"kmzCategory":[],"buscar":""},"frecuencia":"semanal","maxPorEnvio":4,"nombreInmobiliaria":"","nombreAgente":"","propsFiltradas":["625","496","078","106","622","713","933","266","828","303","1193","623","692","4682"],"propsEnviadas":["078","933","266","303","1193","623","692","4682"],"proximosEnvios":[{"fecha":"2026-06-05","codigos":[],"enviado":false,"esCheck":true}],"historialEnvios":[{"fecha":"2026-05-29","codigos":["078","933","266","303","1193","623","692","4682"],"totalCods":8,"tipoEnvio":"individual","notas":"Envío selección individual"}],"visitas":[],"creadoEn":"2026-05-29T22:25:48.366Z"}</t>
+      <c r="O5" s="1" t="inlineStr">
+        <is>
+          <t>2026-04-28 (8)</t>
+        </is>
+      </c>
+      <c r="P5" s="1" t="inlineStr">
+        <is>
+          <t>{"id": "U-1778329096171654", "tipo": "cliente", "nombre": "Andres Silva", "celular": "3116181559", "notas": "Compra casa rentable en Las Granjas $250mlls.", "metodoPago": ["Efectivo", "Crédito"], "estado": "enviando", "etiqueta": "tibio", "filtros": {"tipoInmueble": ["Casa", "Casa rentable"], "rangoPrecio": [], "zona": ["Norte"], "habitaciones": [], "garaje": [], "pisos": [], "ubicacion": [], "piscina": [], "cocina": [], "barrio": [], "conjunto": [], "buscar": "granjas", "maxPrice": 303000000, "minPrice": 0}, "frecuencia": "semanal", "maxPorEnvio": 4, "nombreInmobiliaria": "", "nombreAgente": "", "propsFiltradas": ["321", "696", "038", "108", "520", "591", "025", "306"], "propsEnviadas": ["321", "696", "038", "108", "520", "591", "025", "306"], "proximosEnvios": [{"fecha": "2026-05-05", "codigos": [], "enviado": false, "esCheck": true}], "historialEnvios": [{"fecha": "2026-04-28", "codigos": ["321", "696", "038", "108", "520", "591", "025", "306"], "notas": "Envío de link catálogo"}], "visitas": [], "creadoEn": "2026-04-28T15:42:57.486Z", "feedback": {}}</t>
         </is>
       </c>
     </row>
     <row r="6">
-      <c r="A6" t="n">
-        <v>1777895403747</v>
-      </c>
-      <c r="B6" t="inlineStr">
-        <is>
-          <t>2026-06-05T16:52:32.943Z</t>
+      <c r="A6" s="1" t="inlineStr">
+        <is>
+          <t>1777600630249</t>
+        </is>
+      </c>
+      <c r="B6" s="1" t="inlineStr">
+        <is>
+          <t>2026-05-01T01:57:10.249Z</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Mónica Ramírez</t>
-        </is>
-      </c>
-      <c r="D6" t="n">
-        <v>3105635811</v>
+          <t>Bibiana Andrade</t>
+        </is>
+      </c>
+      <c r="D6" s="1" t="inlineStr">
+        <is>
+          <t>3112339422</t>
+        </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
@@ -775,51 +797,67 @@
       <c r="F6" t="inlineStr"/>
       <c r="G6" t="inlineStr">
         <is>
-          <t>inactivo</t>
+          <t>enviando</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>inactivo</t>
-        </is>
-      </c>
-      <c r="I6" t="inlineStr">
-        <is>
-          <t>Codg.  221 - 4170 - Solicita visita   - inmueble en obra. cita del 4 al 10 mayo.</t>
-        </is>
-      </c>
-      <c r="J6" t="inlineStr"/>
-      <c r="K6" t="inlineStr"/>
-      <c r="L6" t="inlineStr"/>
-      <c r="M6" t="inlineStr"/>
+          <t>tibio</t>
+        </is>
+      </c>
+      <c r="I6" s="1" t="inlineStr"/>
+      <c r="J6" s="1" t="inlineStr">
+        <is>
+          <t>Tipos: Casa | Zonas: Norte | Precio: 0 - 203000000</t>
+        </is>
+      </c>
+      <c r="K6" t="inlineStr">
+        <is>
+          <t>Efectivo, Crédito</t>
+        </is>
+      </c>
+      <c r="L6" s="2" t="n">
+        <v>203000000</v>
+      </c>
+      <c r="M6" t="inlineStr">
+        <is>
+          <t>semanal</t>
+        </is>
+      </c>
       <c r="N6" t="n">
-        <v>0</v>
-      </c>
-      <c r="O6" t="inlineStr"/>
-      <c r="P6" t="inlineStr">
-        <is>
-          <t>{"id":1777895403747,"fecha":"2026-06-03T13:30:40.811Z","nombre":"Mónica Ramírez","celular":3105635811,"tipo":"cliente","estado":"inactivo","etiqueta":"inactivo","notas":"Codg.  221 - 4170 - Solicita visita   - inmueble en obra. cita del 4 al 10 mayo."}</t>
+        <v>9</v>
+      </c>
+      <c r="O6" s="1" t="inlineStr">
+        <is>
+          <t>2026-05-01 (9)</t>
+        </is>
+      </c>
+      <c r="P6" s="1" t="inlineStr">
+        <is>
+          <t>{"id": "1777600630249", "tipo": "cliente", "nombre": "Bibiana Andrade", "celular": "3112339422", "notas": "", "metodoPago": ["Efectivo", "Crédito"], "estado": "enviando", "etiqueta": "tibio", "filtros": {"tipoInmueble": ["Casa"], "rangoPrecio": [], "zona": ["Norte"], "habitaciones": [], "garaje": [], "pisos": ["1"], "ubicacion": [], "piscina": [], "cocina": [], "barrio": [], "conjunto": [], "buscar": "", "maxPrice": 203000000}, "frecuencia": "semanal", "maxPorEnvio": 4, "nombreInmobiliaria": "", "nombreAgente": "", "propsFiltradas": ["078", "262", "496", "511", "541", "622", "625", "713", "766"], "propsEnviadas": ["078", "262", "496", "511", "541", "622", "625", "713", "766"], "proximosEnvios": [{"fecha": "2026-05-08", "codigos": [], "enviado": false, "esCheck": true}], "historialEnvios": [{"fecha": "2026-05-01", "codigos": ["078", "262", "496", "511", "541", "622", "625", "713", "766"], "totalCods": 9, "tipoEnvio": "link", "notas": "Envío de link catálogo"}], "visitas": [], "creadoEn": "2026-05-01T01:57:10.249Z"}</t>
         </is>
       </c>
     </row>
     <row r="7">
-      <c r="A7" t="inlineStr">
-        <is>
-          <t>U-1778683524865214</t>
-        </is>
-      </c>
-      <c r="B7" t="inlineStr">
-        <is>
-          <t>2026-06-05T16:52:07.344Z</t>
+      <c r="A7" s="1" t="inlineStr">
+        <is>
+          <t>U-1778271567218351</t>
+        </is>
+      </c>
+      <c r="B7" s="1" t="inlineStr">
+        <is>
+          <t>2026-05-04T23:00:04.712Z</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Martha Cecilia  Medina</t>
-        </is>
-      </c>
-      <c r="D7" t="n">
-        <v>3106186681</v>
+          <t>Bladimir</t>
+        </is>
+      </c>
+      <c r="D7" s="1" t="inlineStr">
+        <is>
+          <t>3162653365</t>
+        </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
@@ -829,31 +867,31 @@
       <c r="F7" t="inlineStr"/>
       <c r="G7" t="inlineStr">
         <is>
-          <t>enviando</t>
+          <t>visita</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>tibio</t>
-        </is>
-      </c>
-      <c r="I7" t="inlineStr">
-        <is>
-          <t>Compra casa de un piso, cerca a la iglesia Sta. María - Alamos norte. Precio $120.  Se envio propuestas de casa y Aptos en cj hasta  $209 mlls. Proceso INICIAL crédito.</t>
-        </is>
-      </c>
-      <c r="J7" t="inlineStr">
-        <is>
-          <t>Tipos: Casa, Apartamento en conjunto | Zonas: Norte | Precio: 0 - 209000000</t>
+          <t>activo</t>
+        </is>
+      </c>
+      <c r="I7" s="1" t="inlineStr">
+        <is>
+          <t>Busca : Casa en conjunto con 4 ha bitaciones. Presupuesto $350 mlls.</t>
+        </is>
+      </c>
+      <c r="J7" s="1" t="inlineStr">
+        <is>
+          <t>Tipos: Casa en conjunto, Casa campestre en conjunto | Precio: 200000000 - 404000000 | Hab: 4, 6</t>
         </is>
       </c>
       <c r="K7" t="inlineStr">
         <is>
-          <t>Crédito</t>
-        </is>
-      </c>
-      <c r="L7" t="n">
-        <v>209000000</v>
+          <t>Efectivo, Crédito</t>
+        </is>
+      </c>
+      <c r="L7" s="2" t="n">
+        <v>404000000</v>
       </c>
       <c r="M7" t="inlineStr">
         <is>
@@ -861,36 +899,38 @@
         </is>
       </c>
       <c r="N7" t="n">
-        <v>22</v>
-      </c>
-      <c r="O7" t="inlineStr">
-        <is>
-          <t>2026-05-13 (22) | 2026-05-13 (22)</t>
-        </is>
-      </c>
-      <c r="P7" t="inlineStr">
-        <is>
-          <t>{"id":"U-1778683524865214","tipo":"cliente","nombre":"Martha Cecilia  Medina","celular":"3106186681","notas":"Compra casa de un piso, cerca a la iglesia Sta. María - Alamos norte. Precio $120.  Se envio propuestas de casa y Aptos en cj hasta  $209 mlls. Proceso INICIAL crédito.","metodoPago":["Crédito"],"estado":"enviando","etiqueta":"tibio","filtros":{"tipoInmueble":["Casa","Apartamento en conjunto"],"rangoPrecio":[],"zona":["Norte"],"habitaciones":[],"garaje":[],"pisos":[],"ubicacion":[],"piscina":[],"cocina":[],"barrio":[],"conjunto":[],"minPrice":null,"maxPrice":209000000,"kmzCategory":[],"buscar":"","mapActive":false},"frecuencia":"semanal","maxPorEnvio":4,"nombreInmobiliaria":"","nombreAgente":"","propsFiltradas":["1721","933","713","106","078","622","496","662","511","1549","262","1781","215","592","105","625","1728","282","1383","920","766","541"],"propsEnviadas":["1721","078","622","496","1383","933","713","106","662","511","1549","262","1781","215","592","105","625","1728","282","920","766","541"],"proximosEnvios":[{"fecha":"2026-05-20","codigos":[],"enviado":false,"esCheck":true}],"historialEnvios":[{"fecha":"2026-05-13","codigos":["1721","933","713","106","078","622","496","662","511","1549","262","1781","215","592","105","625","1728","282","1383","920","766","541"],"totalCods":22,"tipoEnvio":"link","notas":"Envío de link catálogo"},{"fecha":"2026-05-13","codigos":["1721","933","713","106","078","622","496","662","511","1549","262","1781","215","592","105","625","1728","282","1383","920","766","541"],"totalCods":22,"tipoEnvio":"silencioso","notas":"Filtros actualizados (propiedades marcadas como vistas sin enviar WhatsApp)"}],"visitas":[],"creadoEn":"2026-05-13T14:45:24.869Z"}</t>
+        <v>6</v>
+      </c>
+      <c r="O7" s="1" t="inlineStr">
+        <is>
+          <t>2026-05-06 (6)</t>
+        </is>
+      </c>
+      <c r="P7" s="1" t="inlineStr">
+        <is>
+          <t>{"id": "U-1778271567218351", "tipo": "cliente", "nombre": "Bladimir", "celular": "3162653365", "notas": "Busca : Casa en conjunto con 4 ha bitaciones. Presupuesto $350 mlls.", "metodoPago": ["Efectivo", "Crédito"], "estado": "visita", "etiqueta": "activo", "filtros": {"tipoInmueble": ["Casa en conjunto", "Casa campestre en conjunto"], "rangoPrecio": [], "zona": [], "habitaciones": ["4", "6"], "garaje": [], "pisos": [], "ubicacion": [], "piscina": [], "cocina": [], "barrio": [], "conjunto": [], "buscar": "", "maxPrice": 404000000, "minPrice": 200000000}, "frecuencia": "semanal", "maxPorEnvio": 4, "nombreInmobiliaria": "", "nombreAgente": "", "propsFiltradas": ["1307", "1311", "1714", "1062", "636", "111"], "propsEnviadas": ["1307", "1311", "1714", "1062", "636", "111"], "proximosEnvios": [{"fecha": "2026-05-13", "codigos": [], "enviado": false, "esCheck": true}], "historialEnvios": [{"fecha": "2026-05-06", "codigos": ["1307", "1311", "1714", "1062", "636", "111"], "totalCods": 6, "tipoEnvio": "silencioso", "notas": "Filtros actualizados (propiedades marcadas como vistas sin enviar WhatsApp)"}], "visitas": [{"id": "1778191741569", "codigo": "1311", "fecha": "2026-05-08", "hora": "17:00", "estado": "realizada", "oferto": "no", "oferta": "", "notas": "Inmobiliaria Jovel. Disponible, Con Terceria. Conj. Res. Yahaira. Carrera 18 No. 45-04. Pendiente reconfirmar.", "cliente": "Bladimir", "celular": "3162653365", "inmobiliaria": ""}], "creadoEn": "2026-05-04T23:00:04.712Z", "fromCloud": true, "_localEditedAt": "2026-06-06T01:56:14.584Z"}</t>
         </is>
       </c>
     </row>
     <row r="8">
-      <c r="A8" t="n">
-        <v>1777676783626</v>
-      </c>
-      <c r="B8" t="inlineStr">
-        <is>
-          <t>2026-06-05T16:51:50.791Z</t>
+      <c r="A8" s="1" t="inlineStr">
+        <is>
+          <t>U-1778329096171811</t>
+        </is>
+      </c>
+      <c r="B8" s="1" t="inlineStr">
+        <is>
+          <t>2026-05-04T12:03:00.347Z</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>María Angelica Valderrama</t>
-        </is>
-      </c>
-      <c r="D8" t="inlineStr">
-        <is>
-          <t>311 2042459</t>
+          <t>✅Carlos Medina</t>
+        </is>
+      </c>
+      <c r="D8" s="1" t="inlineStr">
+        <is>
+          <t>3132476032</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
@@ -901,45 +941,71 @@
       <c r="F8" t="inlineStr"/>
       <c r="G8" t="inlineStr">
         <is>
-          <t>inactivo</t>
+          <t>visita</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>inactivo</t>
-        </is>
-      </c>
-      <c r="I8" t="inlineStr"/>
-      <c r="J8" t="inlineStr"/>
-      <c r="K8" t="inlineStr"/>
-      <c r="L8" t="inlineStr"/>
-      <c r="M8" t="inlineStr"/>
+          <t>activo</t>
+        </is>
+      </c>
+      <c r="I8" s="1" t="inlineStr">
+        <is>
+          <t>Codg. 541 - Praderas del Norte - $95 - Inmob. Primv -</t>
+        </is>
+      </c>
+      <c r="J8" s="1" t="inlineStr">
+        <is>
+          <t>Tipos: Casa | Precio: 0 - 119000000</t>
+        </is>
+      </c>
+      <c r="K8" t="inlineStr">
+        <is>
+          <t>Crédito</t>
+        </is>
+      </c>
+      <c r="L8" s="2" t="n">
+        <v>119000000</v>
+      </c>
+      <c r="M8" t="inlineStr">
+        <is>
+          <t>semanal</t>
+        </is>
+      </c>
       <c r="N8" t="n">
-        <v>0</v>
-      </c>
-      <c r="O8" t="inlineStr"/>
-      <c r="P8" t="inlineStr">
-        <is>
-          <t>{"id":1777676783626,"fecha":"2026-06-03T15:06:47.576Z","nombre":"María Angelica Valderrama","celular":"311 2042459","tipo":"cliente","estado":"inactivo","etiqueta":"inactivo","notas":""}</t>
+        <v>3</v>
+      </c>
+      <c r="O8" s="1" t="inlineStr">
+        <is>
+          <t>2026-05-08 (3)</t>
+        </is>
+      </c>
+      <c r="P8" s="1" t="inlineStr">
+        <is>
+          <t>{"id": "U-1778329096171811", "tipo": "cliente", "nombre": "✅Carlos Medina", "celular": "3132476032", "notas": "Codg. 541 - Praderas del Norte - $95 - Inmob. Primv - ", "metodoPago": ["Crédito"], "estado": "visita", "etiqueta": "activo", "filtros": {"tipoInmueble": ["Casa"], "rangoPrecio": [], "zona": [], "habitaciones": [], "garaje": [], "pisos": [], "ubicacion": [], "piscina": [], "cocina": [], "barrio": [], "conjunto": [], "buscar": "", "maxPrice": 119000000}, "frecuencia": "semanal", "maxPorEnvio": 4, "nombreInmobiliaria": "", "nombreAgente": "", "propsFiltradas": ["325", "766", "541"], "propsEnviadas": ["325", "766", "541"], "proximosEnvios": [{"fecha": "2026-05-15", "codigos": [], "enviado": false, "esCheck": true}], "historialEnvios": [{"fecha": "2026-05-08", "codigos": ["325", "766", "541"], "totalCods": 3, "tipoEnvio": "silencioso", "notas": "Filtros actualizados (propiedades marcadas como vistas sin enviar WhatsApp)"}], "visitas": [], "creadoEn": "2026-05-04T12:03:00.347Z", "feedback": {}, "fromCloud": true, "_localEditedAt": "2026-06-06T00:42:49.491Z"}</t>
         </is>
       </c>
     </row>
     <row r="9">
-      <c r="A9" t="n">
-        <v>1777575405797</v>
-      </c>
-      <c r="B9" t="inlineStr">
-        <is>
-          <t>2026-06-05T16:51:28.298Z</t>
+      <c r="A9" s="1" t="inlineStr">
+        <is>
+          <t>U-1779752457678956</t>
+        </is>
+      </c>
+      <c r="B9" s="1" t="inlineStr">
+        <is>
+          <t>2026-05-25T23:40:57.679Z</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Jazmin -Luis</t>
-        </is>
-      </c>
-      <c r="D9" t="n">
-        <v>3112189519</v>
+          <t>Clara vidal</t>
+        </is>
+      </c>
+      <c r="D9" s="1" t="inlineStr">
+        <is>
+          <t>3112261104</t>
+        </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
@@ -949,113 +1015,141 @@
       <c r="F9" t="inlineStr"/>
       <c r="G9" t="inlineStr">
         <is>
+          <t>enviando</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>activo</t>
+        </is>
+      </c>
+      <c r="I9" s="1" t="inlineStr"/>
+      <c r="J9" s="1" t="inlineStr">
+        <is>
+          <t>Tipos: Casa lote | Precio: 179000000 - 507000000</t>
+        </is>
+      </c>
+      <c r="K9" t="inlineStr">
+        <is>
+          <t>Efectivo</t>
+        </is>
+      </c>
+      <c r="L9" s="2" t="n">
+        <v>507000000</v>
+      </c>
+      <c r="M9" t="inlineStr">
+        <is>
+          <t>semanal</t>
+        </is>
+      </c>
+      <c r="N9" t="n">
+        <v>5</v>
+      </c>
+      <c r="O9" s="1" t="inlineStr">
+        <is>
+          <t>2026-05-25 (5)</t>
+        </is>
+      </c>
+      <c r="P9" s="1" t="inlineStr">
+        <is>
+          <t>{"id": "U-1779752457678956", "tipo": "cliente", "nombre": "Clara vidal", "celular": "3112261104", "notas": "", "metodoPago": ["Efectivo"], "estado": "enviando", "etiqueta": "activo", "filtros": {"tipoInmueble": ["Casa lote"], "rangoPrecio": [], "zona": [], "habitaciones": [], "garaje": [], "pisos": [], "ubicacion": [], "piscina": [], "cocina": [], "barrio": [], "conjunto": [], "minPrice": 179000000, "maxPrice": 507000000, "kmzCategory": [], "buscar": ""}, "frecuencia": "semanal", "maxPorEnvio": 4, "nombreInmobiliaria": "", "nombreAgente": "", "propsFiltradas": ["220", "357", "079", "1308"], "propsEnviadas": ["1376", "352", "220", "357", "079"], "proximosEnvios": [{"fecha": "2026-06-01", "codigos": [], "enviado": false, "esCheck": true}], "historialEnvios": [{"fecha": "2026-05-25", "codigos": ["1376", "352", "220", "357", "079"], "totalCods": 5, "tipoEnvio": "individual", "notas": "Envío selección individual"}], "visitas": [], "creadoEn": "2026-05-25T23:40:57.679Z"}</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="1" t="inlineStr">
+        <is>
+          <t>1777992799064</t>
+        </is>
+      </c>
+      <c r="B10" s="1" t="inlineStr">
+        <is>
+          <t>2026-05-05T14:53:19.064Z</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>Comis. Jauqeline</t>
+        </is>
+      </c>
+      <c r="D10" s="1" t="inlineStr">
+        <is>
+          <t>3182198358</t>
+        </is>
+      </c>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>inmobiliaria</t>
+        </is>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>Comis. Jaqueline</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
           <t>inactivo</t>
         </is>
       </c>
-      <c r="H9" t="inlineStr">
+      <c r="H10" t="inlineStr">
         <is>
           <t>inactivo</t>
         </is>
       </c>
-      <c r="I9" t="inlineStr"/>
-      <c r="J9" t="inlineStr"/>
-      <c r="K9" t="inlineStr"/>
-      <c r="L9" t="inlineStr"/>
-      <c r="M9" t="inlineStr"/>
-      <c r="N9" t="n">
+      <c r="I10" s="1" t="inlineStr">
+        <is>
+          <t>Codg. 223 CR. Los Cambulos - Disponible. Visita hoy martes 2:30 pm. Don Ignacio notificado.</t>
+        </is>
+      </c>
+      <c r="J10" s="1" t="inlineStr">
+        <is>
+          <t>Precio: 0 - 403000000</t>
+        </is>
+      </c>
+      <c r="K10" t="inlineStr">
+        <is>
+          <t>Efectivo, Crédito</t>
+        </is>
+      </c>
+      <c r="L10" s="2" t="n">
+        <v>403000000</v>
+      </c>
+      <c r="M10" t="inlineStr">
+        <is>
+          <t>semanal</t>
+        </is>
+      </c>
+      <c r="N10" t="n">
         <v>0</v>
       </c>
-      <c r="O9" t="inlineStr"/>
-      <c r="P9" t="inlineStr">
-        <is>
-          <t>{"id":1777575405797,"fecha":"2026-06-04T16:13:29.738Z","nombre":"Jazmin -Luis","celular":3112189519,"tipo":"cliente","estado":"inactivo","etiqueta":"inactivo","notas":""}</t>
-        </is>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" t="inlineStr">
-        <is>
-          <t>U-1779752457678956</t>
-        </is>
-      </c>
-      <c r="B10" t="inlineStr">
-        <is>
-          <t>2026-06-05T16:49:29.714Z</t>
-        </is>
-      </c>
-      <c r="C10" t="inlineStr">
-        <is>
-          <t>Clara vidal</t>
-        </is>
-      </c>
-      <c r="D10" t="n">
-        <v>3112261104</v>
-      </c>
-      <c r="E10" t="inlineStr">
-        <is>
-          <t>cliente</t>
-        </is>
-      </c>
-      <c r="F10" t="inlineStr"/>
-      <c r="G10" t="inlineStr">
-        <is>
-          <t>enviando</t>
-        </is>
-      </c>
-      <c r="H10" t="inlineStr">
-        <is>
-          <t>activo</t>
-        </is>
-      </c>
-      <c r="I10" t="inlineStr"/>
-      <c r="J10" t="inlineStr">
-        <is>
-          <t>Tipos: Casa lote | Precio: 179000000 - 507000000</t>
-        </is>
-      </c>
-      <c r="K10" t="inlineStr">
-        <is>
-          <t>Efectivo</t>
-        </is>
-      </c>
-      <c r="L10" t="n">
-        <v>507000000</v>
-      </c>
-      <c r="M10" t="inlineStr">
-        <is>
-          <t>semanal</t>
-        </is>
-      </c>
-      <c r="N10" t="n">
-        <v>5</v>
-      </c>
-      <c r="O10" t="inlineStr">
-        <is>
-          <t>2026-05-25 (5)</t>
-        </is>
-      </c>
-      <c r="P10" t="inlineStr">
-        <is>
-          <t>{"id":"U-1779752457678956","tipo":"cliente","nombre":"Clara vidal","celular":"3112261104","notas":"","metodoPago":["Efectivo"],"estado":"enviando","etiqueta":"activo","filtros":{"tipoInmueble":["Casa lote"],"rangoPrecio":[],"zona":[],"habitaciones":[],"garaje":[],"pisos":[],"ubicacion":[],"piscina":[],"cocina":[],"barrio":[],"conjunto":[],"minPrice":179000000,"maxPrice":507000000,"kmzCategory":[],"buscar":""},"frecuencia":"semanal","maxPorEnvio":4,"nombreInmobiliaria":"","nombreAgente":"","propsFiltradas":["220","357","079","1308"],"propsEnviadas":["1376","352","220","357","079"],"proximosEnvios":[{"fecha":"2026-06-01","codigos":[],"enviado":false,"esCheck":true}],"historialEnvios":[{"fecha":"2026-05-25","codigos":["1376","352","220","357","079"],"totalCods":5,"tipoEnvio":"individual","notas":"Envío selección individual"}],"visitas":[],"creadoEn":"2026-05-25T23:40:57.679Z"}</t>
+      <c r="O10" s="1" t="inlineStr"/>
+      <c r="P10" s="1" t="inlineStr">
+        <is>
+          <t>{"id": "1777992799064", "tipo": "inmobiliaria", "nombre": "Comis. Jauqeline", "celular": "3182198358", "notas": "Codg. 223 CR. Los Cambulos - Disponible. Visita hoy martes 2:30 pm. Don Ignacio notificado.", "metodoPago": ["Efectivo", "Crédito"], "estado": "inactivo", "etiqueta": "inactivo", "filtros": {"tipoInmueble": [], "rangoPrecio": [], "zona": [], "habitaciones": [], "garaje": [], "pisos": [], "ubicacion": [], "piscina": [], "cocina": [], "barrio": [], "conjunto": [], "buscar": "", "maxPrice": 403000000}, "frecuencia": "semanal", "maxPorEnvio": 4, "nombreInmobiliaria": "Comis. Jaqueline", "nombreAgente": "3182198358", "propsFiltradas": ["016", "1187", "541", "1744", "464", "642", "837", "844", "588", "779", "823", "1036", "1090", "739", "723", "1644", "693", "783", "143", "1231", "1464", "1646", "1647", "167"], "propsEnviadas": [], "proximosEnvios": [{"fecha": "2026-05-12", "codigos": [], "enviado": false, "esCheck": true}], "historialEnvios": [], "visitas": [], "creadoEn": "2026-05-05T14:53:19.064Z", "feedback": {}}</t>
         </is>
       </c>
     </row>
     <row r="11">
-      <c r="A11" t="n">
-        <v>1777600630249</v>
-      </c>
-      <c r="B11" t="inlineStr">
-        <is>
-          <t>2026-06-05T16:48:21.881Z</t>
+      <c r="A11" s="1" t="inlineStr">
+        <is>
+          <t>U-177832909617130</t>
+        </is>
+      </c>
+      <c r="B11" s="1" t="inlineStr">
+        <is>
+          <t>2026-05-06T14:12:56.783Z</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Bibiana Andrade</t>
-        </is>
-      </c>
-      <c r="D11" t="n">
-        <v>3112339422</v>
+          <t>David Cataño</t>
+        </is>
+      </c>
+      <c r="D11" s="1" t="inlineStr">
+        <is>
+          <t>3215696084</t>
+        </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
@@ -1065,7 +1159,7 @@
       <c r="F11" t="inlineStr"/>
       <c r="G11" t="inlineStr">
         <is>
-          <t>enviando</t>
+          <t>inactivo</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
@@ -1073,57 +1167,53 @@
           <t>tibio</t>
         </is>
       </c>
-      <c r="I11" t="inlineStr"/>
-      <c r="J11" t="inlineStr">
-        <is>
-          <t>Tipos: Casa | Zonas: Norte | Precio: 0 - 203000000</t>
-        </is>
-      </c>
+      <c r="I11" s="1" t="inlineStr">
+        <is>
+          <t>YA INVIRTIO EN IBAGUE. Codg. 844 - Apto Bosques San Juis - $87-Inmb. S. Primv - Disponible - Pago Caja Honor. Comprador del Cauca. La Inmb. Ya está encontacto con el comprador y le enseñará otro. En el catálogo $87 - Panel $100...???</t>
+        </is>
+      </c>
+      <c r="J11" s="1" t="inlineStr"/>
       <c r="K11" t="inlineStr">
         <is>
-          <t>Efectivo, Crédito</t>
-        </is>
-      </c>
-      <c r="L11" t="n">
-        <v>203000000</v>
-      </c>
+          <t>Caja Honor</t>
+        </is>
+      </c>
+      <c r="L11" t="inlineStr"/>
       <c r="M11" t="inlineStr">
         <is>
           <t>semanal</t>
         </is>
       </c>
       <c r="N11" t="n">
-        <v>9</v>
-      </c>
-      <c r="O11" t="inlineStr">
-        <is>
-          <t>2026-05-01 (9)</t>
-        </is>
-      </c>
-      <c r="P11" t="inlineStr">
-        <is>
-          <t>{"id":"1777600630249","tipo":"cliente","nombre":"Bibiana Andrade","celular":"3112339422","notas":"","metodoPago":["Efectivo","Crédito"],"estado":"enviando","etiqueta":"tibio","filtros":{"tipoInmueble":["Casa"],"rangoPrecio":[],"zona":["Norte"],"habitaciones":[],"garaje":[],"pisos":["1"],"ubicacion":[],"piscina":[],"cocina":[],"barrio":[],"conjunto":[],"buscar":"","maxPrice":203000000},"frecuencia":"semanal","maxPorEnvio":4,"nombreInmobiliaria":"","nombreAgente":"","propsFiltradas":["078","262","496","511","541","622","625","713","766"],"propsEnviadas":["078","262","496","511","541","622","625","713","766"],"proximosEnvios":[{"fecha":"2026-05-08","codigos":[],"enviado":false,"esCheck":true}],"historialEnvios":[{"fecha":"2026-05-01","codigos":["078","262","496","511","541","622","625","713","766"],"totalCods":9,"tipoEnvio":"link","notas":"Envío de link catálogo"}],"visitas":[],"creadoEn":"2026-05-01T01:57:10.249Z"}</t>
+        <v>0</v>
+      </c>
+      <c r="O11" s="1" t="inlineStr"/>
+      <c r="P11" s="1" t="inlineStr">
+        <is>
+          <t>{"id": "U-177832909617130", "tipo": "cliente", "nombre": "David Cataño", "celular": "3215696084", "notas": "YA INVIRTIO EN IBAGUE. Codg. 844 - Apto Bosques San Juis - $87-Inmb. S. Primv - Disponible - Pago Caja Honor. Comprador del Cauca. La Inmb. Ya está encontacto con el comprador y le enseñará otro. En el catálogo $87 - Panel $100...???", "metodoPago": ["Caja Honor"], "estado": "inactivo", "etiqueta": "tibio", "filtros": {"tipoInmueble": [], "rangoPrecio": [], "zona": [], "habitaciones": [], "garaje": [], "pisos": [], "ubicacion": [], "piscina": [], "cocina": [], "barrio": [], "conjunto": [], "buscar": "844"}, "frecuencia": "semanal", "maxPorEnvio": 4, "nombreInmobiliaria": "", "nombreAgente": "", "propsFiltradas": ["844"], "propsEnviadas": [], "proximosEnvios": [{"fecha": "2026-05-13", "codigos": [], "enviado": false, "esCheck": true}], "historialEnvios": [], "visitas": [], "creadoEn": "2026-05-06T14:12:56.783Z", "feedback": {}}</t>
         </is>
       </c>
     </row>
     <row r="12">
-      <c r="A12" t="inlineStr">
-        <is>
-          <t>U-1778884294544703</t>
-        </is>
-      </c>
-      <c r="B12" t="inlineStr">
-        <is>
-          <t>2026-06-05T16:52:27.995Z</t>
+      <c r="A12" s="1" t="inlineStr">
+        <is>
+          <t>U-1778702372993384</t>
+        </is>
+      </c>
+      <c r="B12" s="1" t="inlineStr">
+        <is>
+          <t>2026-06-04T23:08:17.369Z</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Mauricio Garzón  y Yuly Solorzano</t>
-        </is>
-      </c>
-      <c r="D12" t="n">
-        <v>3113316364</v>
+          <t>Diego Tello</t>
+        </is>
+      </c>
+      <c r="D12" s="1" t="inlineStr">
+        <is>
+          <t>3168049568</t>
+        </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
@@ -1133,67 +1223,57 @@
       <c r="F12" t="inlineStr"/>
       <c r="G12" t="inlineStr">
         <is>
-          <t>inactivo</t>
+          <t>enviando</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>inactivo</t>
-        </is>
-      </c>
-      <c r="I12" t="inlineStr">
-        <is>
-          <t>Compra casa lote - Presupuesto $300 mlls - Interesado Codg. 220.</t>
-        </is>
-      </c>
-      <c r="J12" t="inlineStr">
-        <is>
-          <t>Tipos: Casa lote | Zonas: Centro, Norte</t>
-        </is>
-      </c>
-      <c r="K12" t="inlineStr">
-        <is>
-          <t>Efectivo, Crédito</t>
-        </is>
-      </c>
+          <t>tibio</t>
+        </is>
+      </c>
+      <c r="I12" s="1" t="inlineStr">
+        <is>
+          <t>Compra casa rentable para el hijo EEUU . $400 mlls. No sur. AUN BUSCANDO LA CASA.</t>
+        </is>
+      </c>
+      <c r="J12" s="1" t="inlineStr"/>
+      <c r="K12" t="inlineStr"/>
       <c r="L12" t="inlineStr"/>
       <c r="M12" t="inlineStr">
         <is>
-          <t>semanal</t>
+          <t>manual</t>
         </is>
       </c>
       <c r="N12" t="n">
-        <v>2</v>
-      </c>
-      <c r="O12" t="inlineStr">
-        <is>
-          <t>2026-05-15 (2)</t>
-        </is>
-      </c>
-      <c r="P12" t="inlineStr">
-        <is>
-          <t>{"id":"U-1778884294544703","tipo":"cliente","nombre":"Mauricio Garzón  y Yuly Solorzano","celular":"3113316364","notas":"Compra casa lote - Presupuesto $300 mlls - Interesado Codg. 220.","metodoPago":["Efectivo","Crédito"],"estado":"inactivo","etiqueta":"inactivo","filtros":{"tipoInmueble":["Casa lote"],"rangoPrecio":[],"zona":["Centro","Norte"],"habitaciones":[],"garaje":[],"pisos":[],"ubicacion":[],"piscina":[],"cocina":[],"barrio":[],"conjunto":[],"minPrice":null,"maxPrice":null,"kmzCategory":[],"buscar":"","mapActive":false},"frecuencia":"semanal","maxPorEnvio":4,"nombreInmobiliaria":"","nombreAgente":"","propsFiltradas":["013","220","079","1268","738"],"propsEnviadas":["220","079"],"proximosEnvios":[{"fecha":"2026-05-22","codigos":[],"enviado":false,"esCheck":true}],"historialEnvios":[{"fecha":"2026-05-15","codigos":["220","079"],"totalCods":2,"tipoEnvio":"link","notas":"Envío de link catálogo"}],"visitas":[],"creadoEn":"2026-05-15T22:31:34.544Z","feedback":{}}</t>
+        <v>0</v>
+      </c>
+      <c r="O12" s="1" t="inlineStr"/>
+      <c r="P12" s="1" t="inlineStr">
+        <is>
+          <t>{"id": "U-1778702372993384", "fecha": "2026-06-04T23:08:17.369Z", "nombre": "Diego Tello", "celular": "3168049568", "tipo": "cliente", "estado": "enviando", "etiqueta": "tibio", "notas": "Compra casa rentable para el hijo EEUU . $400 mlls. No sur. AUN BUSCANDO LA CASA."}</t>
         </is>
       </c>
     </row>
     <row r="13">
-      <c r="A13" t="inlineStr">
-        <is>
-          <t>U-1778872679106678</t>
-        </is>
-      </c>
-      <c r="B13" t="inlineStr">
-        <is>
-          <t>2026-06-02T21:13:58.861Z</t>
+      <c r="A13" s="1" t="inlineStr">
+        <is>
+          <t>U-1779811520619231</t>
+        </is>
+      </c>
+      <c r="B13" s="1" t="inlineStr">
+        <is>
+          <t>2026-05-26T16:05:20.620Z</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Sindy Cabrera</t>
-        </is>
-      </c>
-      <c r="D13" t="n">
-        <v>3113330927</v>
+          <t>ELENA</t>
+        </is>
+      </c>
+      <c r="D13" s="1" t="inlineStr">
+        <is>
+          <t>3148518555</t>
+        </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
@@ -1203,49 +1283,71 @@
       <c r="F13" t="inlineStr"/>
       <c r="G13" t="inlineStr">
         <is>
-          <t>inactivo</t>
+          <t>enviando</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>inactivo</t>
-        </is>
-      </c>
-      <c r="I13" t="inlineStr">
-        <is>
-          <t>Codg. 078 Cocli- Disponible - ICDE.  Compra casa o Apto en el norte. Pendiente del  presupuesto y forma de pago.</t>
-        </is>
-      </c>
-      <c r="J13" t="inlineStr">
-        <is>
-          <t>{"id":"U-1778872679106678","tipo":"cliente","nombre":"Sindy Cabrera","celular":"3113330927","notas":"Codg. 078 Cocli- Disponible - ICDE.  Compra casa o Apto en el norte. Pendiente del  presupuesto y forma de pago.","metodoPago":[],"estado":"inactivo","etiqueta":"inactivo","filtros":{"tipoInmueble":[],"rangoPrecio":[],"zona":[],"habitaciones":[],"garaje":[],"pisos":[],"ubicacion":[],"piscina":[],"cocina":[],"barrio":[],"conjunto":[],"minPrice":null,"maxPrice":null,"kmzCategory":[],"buscar":"078"},"frecuencia":"semanal","maxPorEnvio":4,"nombreInmobiliaria":"","nombreAgente":"","propsFiltradas":["781","078"],"propsEnviadas":["078"],"proximosEnvios":[{"fecha":"2026-05-22","codigos":[],"enviado":false,"esCheck":true}],"historialEnvios":[{"fecha":"2026-05-15","codigos":["078"],"notas":"Se marcaron 1 propiedades como enviadas (sin WhatsApp)."}],"visitas":[{"id":"1778874888238","codigo":"078","fecha":"2026-05-19","hora":"11:00","estado":"agendada","oferto":"no","oferta":"","notas":"Visitará la casa 078 - No ha inicado forma de pago. Enseñará don Yirben.","cliente":"Sindy Cabrera","celular":"3113330927","inmobiliaria":""}],"creadoEn":"2026-05-15T19:17:59.106Z","feedback":{}}</t>
-        </is>
-      </c>
-      <c r="K13" t="inlineStr"/>
-      <c r="L13" t="inlineStr"/>
-      <c r="M13" t="inlineStr"/>
-      <c r="N13" t="inlineStr"/>
-      <c r="O13" t="inlineStr"/>
-      <c r="P13" t="inlineStr"/>
+          <t>tibio</t>
+        </is>
+      </c>
+      <c r="I13" s="1" t="inlineStr">
+        <is>
+          <t>Compra casa económica hasta $110mlls.</t>
+        </is>
+      </c>
+      <c r="J13" s="1" t="inlineStr">
+        <is>
+          <t>Tipos: Casa | Precio: 70000000 - 154000000</t>
+        </is>
+      </c>
+      <c r="K13" t="inlineStr">
+        <is>
+          <t>Efectivo, Crédito</t>
+        </is>
+      </c>
+      <c r="L13" s="2" t="n">
+        <v>154000000</v>
+      </c>
+      <c r="M13" t="inlineStr">
+        <is>
+          <t>semanal</t>
+        </is>
+      </c>
+      <c r="N13" t="n">
+        <v>22</v>
+      </c>
+      <c r="O13" s="1" t="inlineStr">
+        <is>
+          <t>2026-05-26 (22)</t>
+        </is>
+      </c>
+      <c r="P13" s="1" t="inlineStr">
+        <is>
+          <t>{"id": "U-1779811520619231", "tipo": "cliente", "nombre": "ELENA", "celular": "3148518555", "notas": "Compra casa económica hasta $110mlls.", "metodoPago": ["Efectivo", "Crédito"], "estado": "enviando", "etiqueta": "tibio", "filtros": {"tipoInmueble": ["Casa"], "rangoPrecio": [], "zona": [], "habitaciones": [], "garaje": [], "pisos": [], "ubicacion": [], "piscina": [], "cocina": [], "barrio": [], "conjunto": [], "minPrice": 70000000, "maxPrice": 154000000, "kmzCategory": [], "buscar": ""}, "frecuencia": "semanal", "maxPorEnvio": 4, "nombreInmobiliaria": "", "nombreAgente": "", "propsFiltradas": ["541", "449", "514", "5224", "991", "325", "851", "939", "1285", "282", "706", "716"], "propsEnviadas": ["496", "078", "106", "622", "713", "933", "266", "609", "828", "702", "541", "449", "514", "5224", "991", "325", "851", "939", "1285", "282", "706", "716"], "proximosEnvios": [{"fecha": "2026-06-02", "codigos": [], "enviado": false, "esCheck": true}], "historialEnvios": [{"fecha": "2026-05-26", "codigos": ["496", "078", "106", "622", "713", "933", "266", "609", "828", "702", "541", "449", "514", "5224", "991", "325", "851", "939", "1285", "282", "706", "716"], "totalCods": 22, "tipoEnvio": "individual", "notas": "Envío selección individual"}], "visitas": [], "creadoEn": "2026-05-26T16:05:20.620Z"}</t>
+        </is>
+      </c>
     </row>
     <row r="14">
-      <c r="A14" t="inlineStr">
-        <is>
-          <t>U-1778329096171654</t>
-        </is>
-      </c>
-      <c r="B14" t="inlineStr">
-        <is>
-          <t>2026-06-05T16:48:03.947Z</t>
+      <c r="A14" s="1" t="inlineStr">
+        <is>
+          <t>U-1778271567218168</t>
+        </is>
+      </c>
+      <c r="B14" s="1" t="inlineStr">
+        <is>
+          <t>2026-04-30T15:34:12.578Z</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Andres Silva</t>
-        </is>
-      </c>
-      <c r="D14" t="n">
-        <v>3116181559</v>
+          <t>Fransua Chaux</t>
+        </is>
+      </c>
+      <c r="D14" s="1" t="inlineStr">
+        <is>
+          <t>322 399 3035</t>
+        </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
@@ -1260,26 +1362,22 @@
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>tibio</t>
-        </is>
-      </c>
-      <c r="I14" t="inlineStr">
-        <is>
-          <t>Compra casa rentable en Las Granjas $250mlls.</t>
-        </is>
-      </c>
-      <c r="J14" t="inlineStr">
-        <is>
-          <t>Tipos: Casa, Casa rentable | Zonas: Norte | Precio: 0 - 303000000</t>
+          <t>activo</t>
+        </is>
+      </c>
+      <c r="I14" s="1" t="inlineStr"/>
+      <c r="J14" s="1" t="inlineStr">
+        <is>
+          <t>Tipos: Apartamento en conjunto | Precio: 101000000 - 164000000</t>
         </is>
       </c>
       <c r="K14" t="inlineStr">
         <is>
-          <t>Efectivo, Crédito</t>
-        </is>
-      </c>
-      <c r="L14" t="n">
-        <v>303000000</v>
+          <t>Efectivo</t>
+        </is>
+      </c>
+      <c r="L14" s="2" t="n">
+        <v>164000000</v>
       </c>
       <c r="M14" t="inlineStr">
         <is>
@@ -1287,37 +1385,39 @@
         </is>
       </c>
       <c r="N14" t="n">
-        <v>8</v>
-      </c>
-      <c r="O14" t="inlineStr">
-        <is>
-          <t>2026-04-28 (8)</t>
-        </is>
-      </c>
-      <c r="P14" t="inlineStr">
-        <is>
-          <t>{"id":"U-1778329096171654","tipo":"cliente","nombre":"Andres Silva","celular":"3116181559","notas":"Compra casa rentable en Las Granjas $250mlls.","metodoPago":["Efectivo","Crédito"],"estado":"enviando","etiqueta":"tibio","filtros":{"tipoInmueble":["Casa","Casa rentable"],"rangoPrecio":[],"zona":["Norte"],"habitaciones":[],"garaje":[],"pisos":[],"ubicacion":[],"piscina":[],"cocina":[],"barrio":[],"conjunto":[],"buscar":"granjas","maxPrice":303000000,"minPrice":0},"frecuencia":"semanal","maxPorEnvio":4,"nombreInmobiliaria":"","nombreAgente":"","propsFiltradas":["321","696","038","108","520","591","025","306"],"propsEnviadas":["321","696","038","108","520","591","025","306"],"proximosEnvios":[{"fecha":"2026-05-05","codigos":[],"enviado":false,"esCheck":true}],"historialEnvios":[{"fecha":"2026-04-28","codigos":["321","696","038","108","520","591","025","306"],"notas":"Envío de link catálogo"}],"visitas":[],"creadoEn":"2026-04-28T15:42:57.486Z","feedback":{}}</t>
+        <v>2</v>
+      </c>
+      <c r="O14" s="1" t="inlineStr">
+        <is>
+          <t>2026-04-30 (1) | 2026-05-11 (1)</t>
+        </is>
+      </c>
+      <c r="P14" s="1" t="inlineStr">
+        <is>
+          <t>{"id": "U-1778271567218168", "tipo": "cliente", "nombre": "Fransua Chaux", "celular": "322 399 3035", "notas": "", "metodoPago": ["Efectivo"], "estado": "enviando", "etiqueta": "activo", "filtros": {"tipoInmueble": ["Apartamento en conjunto"], "rangoPrecio": [], "zona": [], "habitaciones": [], "garaje": [], "pisos": [], "ubicacion": [], "piscina": [], "cocina": [], "barrio": [], "conjunto": [], "buscar": "", "maxPrice": 164000000, "minPrice": 101000000}, "frecuencia": "semanal", "maxPorEnvio": 4, "nombreInmobiliaria": "", "nombreAgente": "", "propsFiltradas": ["105", "465", "4597", "1728", "1383", "647", "656", "360", "920"], "propsEnviadas": ["105", "1728"], "proximosEnvios": [{"fecha": "2026-05-18", "codigos": [], "enviado": false, "esCheck": true}], "historialEnvios": [{"fecha": "2026-04-30", "codigos": ["105"], "totalCods": 1, "tipoEnvio": "individual", "notas": ""}, {"fecha": "2026-05-11", "codigos": ["1728"], "totalCods": 1, "tipoEnvio": "silencioso", "notas": "Filtros actualizados (propiedades marcadas como vistas sin enviar WhatsApp)"}], "visitas": [{"id": "1778532779440", "codigo": "1728", "fecha": "2026-05-11", "hora": "", "estado": "realizada", "oferto": "si", "oferta": "147.000.000", "notas": "El dueño dijo 147 y ofertaron 147, C&amp;C esperando a ver si ofrecen más.", "cliente": "Fransua Chaux", "celular": "322 399 3035", "inmobiliaria": ""}, {"id": "1779026220071", "codigo": "105", "fecha": "2026-05-17", "hora": "", "estado": "realizada", "oferto": "no", "oferta": "", "notas": "", "cliente": "Fransua Chaux", "celular": "322 399 3035", "inmobiliaria": ""}], "creadoEn": "2026-04-30T15:34:12.578Z"}</t>
         </is>
       </c>
     </row>
     <row r="15">
-      <c r="A15" t="inlineStr">
-        <is>
-          <t>U-1779365901250514</t>
-        </is>
-      </c>
-      <c r="B15" t="inlineStr">
-        <is>
-          <t>2026-06-02T21:22:01.768Z</t>
+      <c r="A15" s="1" t="inlineStr">
+        <is>
+          <t>U-1780081837240957</t>
+        </is>
+      </c>
+      <c r="B15" s="1" t="inlineStr">
+        <is>
+          <t>2026-06-04T19:35:58.826Z</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Valentina  Villarreal Pinzón</t>
-        </is>
-      </c>
-      <c r="D15" t="n">
-        <v>3118014180</v>
+          <t>Germán Arevalo</t>
+        </is>
+      </c>
+      <c r="D15" s="1" t="inlineStr">
+        <is>
+          <t>3203259635</t>
+        </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
@@ -1335,41 +1435,49 @@
           <t>inactivo</t>
         </is>
       </c>
-      <c r="I15" t="inlineStr">
-        <is>
-          <t>Compra casa rentable, económica.</t>
-        </is>
-      </c>
-      <c r="J15" t="inlineStr">
-        <is>
-          <t>{"id":"U-1779365901250514","tipo":"cliente","nombre":"Valentina  Villarreal Pinzón","celular":"3118014180","notas":"Compra casa rentable, económica.","metodoPago":["Efectivo","Crédito"],"estado":"inactivo","etiqueta":"inactivo","filtros":{"tipoInmueble":[],"rangoPrecio":[],"zona":[],"habitaciones":[],"garaje":[],"pisos":[],"ubicacion":[],"piscina":[],"cocina":[],"barrio":[],"conjunto":[],"minPrice":null,"maxPrice":null,"kmzCategory":["APTO Y APTO EN CONJUNTO 🏢","CASA EN CONJUNTO, CAMPESTRE IND Y EN CONJUNTO⛳","CASA LOTE, LOTE Y LOTE EN CONJUNTO ⛳","CASAS Y EDIFICIOS RENTABLES💲","CASAS 🏡","LOCAL, BODEGA Y OFICINA 🏪"],"buscar":"223"},"frecuencia":"semanal","maxPorEnvio":4,"nombreInmobiliaria":"","nombreAgente":"","propsFiltradas":["223"],"propsEnviadas":[],"proximosEnvios":[{"fecha":"2026-05-28","codigos":[],"enviado":false,"esCheck":true}],"historialEnvios":[],"visitas":[{"id":"1779366011043","codigo":"223","fecha":"2026-05-21","hora":"15:00","estado":"agendada","oferto":"no","oferta":"","notas":"Ya se informó a  propietario Ignacio. Pendiente reconfirmar.","cliente":"Valentina","celular":"3118014180","inmobiliaria":"","updatedAt":1779366011043}],"creadoEn":"2026-05-21T12:18:21.251Z","feedback":{}}</t>
-        </is>
-      </c>
+      <c r="I15" s="1" t="inlineStr">
+        <is>
+          <t>Compra casalote- Codg. 220. - Cliente SILENCIOSO.</t>
+        </is>
+      </c>
+      <c r="J15" s="1" t="inlineStr"/>
       <c r="K15" t="inlineStr"/>
       <c r="L15" t="inlineStr"/>
-      <c r="M15" t="inlineStr"/>
-      <c r="N15" t="inlineStr"/>
-      <c r="O15" t="inlineStr"/>
-      <c r="P15" t="inlineStr"/>
+      <c r="M15" t="inlineStr">
+        <is>
+          <t>manual</t>
+        </is>
+      </c>
+      <c r="N15" t="n">
+        <v>0</v>
+      </c>
+      <c r="O15" s="1" t="inlineStr"/>
+      <c r="P15" s="1" t="inlineStr">
+        <is>
+          <t>{"id": "U-1780081837240957", "fecha": "2026-06-04T19:35:58.826Z", "nombre": "Germán Arevalo", "celular": "3203259635", "tipo": "cliente", "estado": "inactivo", "etiqueta": "inactivo", "notas": "Compra casalote- Codg. 220. - Cliente SILENCIOSO."}</t>
+        </is>
+      </c>
     </row>
     <row r="16">
-      <c r="A16" t="inlineStr">
-        <is>
-          <t>U-1780001855681844</t>
-        </is>
-      </c>
-      <c r="B16" t="inlineStr">
-        <is>
-          <t>2026-06-05T16:52:59.995Z</t>
+      <c r="A16" s="1" t="inlineStr">
+        <is>
+          <t>U-1778271567218463</t>
+        </is>
+      </c>
+      <c r="B16" s="1" t="inlineStr">
+        <is>
+          <t>2026-05-04T11:45:19.556Z</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Oscar Luis Suarez Cubillos</t>
-        </is>
-      </c>
-      <c r="D16" t="n">
-        <v>3118571606</v>
+          <t>Hector</t>
+        </is>
+      </c>
+      <c r="D16" s="1" t="inlineStr">
+        <is>
+          <t>3159057825</t>
+        </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
@@ -1387,46 +1495,52 @@
           <t>activo</t>
         </is>
       </c>
-      <c r="I16" t="inlineStr">
-        <is>
-          <t>Compra casa rentable económica - Norte $200mlls.</t>
-        </is>
-      </c>
-      <c r="J16" t="inlineStr"/>
+      <c r="I16" s="1" t="inlineStr">
+        <is>
+          <t>Solicita visita Codg. 622 Villa Milena - $190 - Inmb. RK</t>
+        </is>
+      </c>
+      <c r="J16" s="1" t="inlineStr">
+        <is>
+          <t>Tipos: Casa | Precio: 0 - 221000000</t>
+        </is>
+      </c>
       <c r="K16" t="inlineStr">
         <is>
           <t>Efectivo</t>
         </is>
       </c>
-      <c r="L16" t="inlineStr"/>
+      <c r="L16" s="2" t="n">
+        <v>221000000</v>
+      </c>
       <c r="M16" t="inlineStr">
         <is>
           <t>semanal</t>
         </is>
       </c>
       <c r="N16" t="n">
-        <v>588</v>
-      </c>
-      <c r="O16" t="inlineStr">
-        <is>
-          <t>2026-05-28 (593)</t>
-        </is>
-      </c>
-      <c r="P16" t="inlineStr">
-        <is>
-          <t>{"id":"U-1780001855681844","tipo":"cliente","nombre":"Oscar Luis Suarez Cubillos","celular":"3118571606","notas":"Compra casa rentable económica - Norte $200mlls.","metodoPago":["Efectivo"],"estado":"visita","etiqueta":"activo","filtros":{"tipoInmueble":[],"rangoPrecio":[],"zona":[],"habitaciones":[],"garaje":[],"pisos":[],"ubicacion":[],"piscina":[],"cocina":[],"barrio":[],"conjunto":[],"minPrice":null,"maxPrice":null,"kmzCategory":["APTO Y APTO EN CONJUNTO 🏢","CASA EN CONJUNTO, CAMPESTRE IND Y EN CONJUNTO⛳","CASA LOTE, LOTE Y LOTE EN CONJUNTO ⛳","CASAS Y EDIFICIOS RENTABLES💲","CASAS 🏡","LOCAL, BODEGA Y OFICINA 🏪"],"buscar":""},"frecuencia":"semanal","maxPorEnvio":4,"nombreInmobiliaria":"","nombreAgente":"","propsFiltradas":["1376","352","1384","800","746","833","074","1757","1366","1329","1773","291","1758","1295","808","473","1284","4911","767","809","1265","694","1104","810","1370","1718","4750","1060","1034","4864","469","593","988","859","432","661","4817","796","781","845","045","328","892","1251","535","567","1249","806","795","1356","153","198","253","605","829","807","1433","450","1776","1351","1141","544","579","478","775","799","018","1133","425","447","483","839","1338","1327","427","472","509","646","824","1170","1246","1139","631","193","679","887","627","119","114","430","013","279","448","678","900","032","265","620","1713","277","440","454","284","350","320","805","629","698","604","308","130","1800","252","695","667","935","1026","1739","764","103","1778","714","1660","1357","155","797","912","073","226","374","813","812","501","1100","1499","677","773","075","1687","346","506","543","1337","1341","560","902","637","648","1266","080","433","1379","1381","518","1158","1754","704","1509","397","595","017","861","1274","754","852","633","1196","638","682","659","5110","829","765","466","220","015","1300","1785","863","1294","061","1258","1471","1771","1795","426","546","836","972","978","832","1004","1168","670","1710","510","1260","1354","816","860","1253","1725","711","821","1343","1321","1352","1375","205","280","507","741","1374","4658","1347","906","5353","363","1099","1150","1189","1254","1297","1314","1568","1755","240","442","453","650","687","815","865","1682","087","1328","1588","4927","1363","369","743","582","491","818","086","1230","1311","1318","1648","942","423","634","1362","1365","1081","1167","1342","1678","393","443","4613","5058","596","877","1332","256","1790","357","1287","1714","1767","270","830","862","089","115","102","404","042","1062","1245","1276","1331","1378","1379","162","1689","335","455","4948","758","855","882","843","1108","1271","475","373","039","014","046","1330","411","867","463","505","422","179","093","111","1325","1482","660","854","876","760","1709","079","1140","171","487","019","028","066","1206","1316","1344","1542","1560","1762","1796","5145","550","632","734","752","883","067","184","321","132","696","052","1470","888","1666","1281","857","038","246","347","644","026","1055","108","1084","1119","1323","1324","134","1372","1373","1430","431","444","5017","520","587","761","874","884","970","725","594","1345","1786","382","1371","467","680","691","1110","754","1209","1419","1531","1763","348","384","4682","1487","306","070","654","745","1193","121","1224","1625","1685","1722","1766","289","296","490","611","623","692","759","772","814","834","864","873","4972","387","615","303","602","866","871","878","1360","869","703","020","1511","1690","1727","309","410","702","726","879","109","185","827","1267","1667","609","828","486","030","1005","1669","266","4552","1358","1308","733","947","1073","1721","713","933","100","078","106","1382","1772","495","621","622","1756","802","136","496","562","564","662","736","569","221","872","223","339","1541","1794","345","511","262","539","853","1242","1549","288","554","763","1010","1781","215","228","868","1112","137","552","592","690","1003","105","607","798","847","517","4597","625","720","880","1326","282","362","672","716","1285","1383","1728","548","706","809","647","792","1340","1359","360","601","674","953","1364","489","1413","856","1451","1730","325","343","606","609","727","851","939","1268","671","118","514","5224","5342","916","1369","920","991","449","522","1368","738","849","1198","788","016","1187","541","1744","464","642","837","844","779","823","588","1036","1090","739","723","1644","693","783","143","1231","1464","1646","1647","167","113","581","409","036","468","540","529","744","499","940","966","125"],"propsEnviadas":["1376","352","1384","800","746","833","074","1757","1366","1329","1773","291","1758","1295","808","473","1284","4911","767","809","1265","694","1104","810","1370","1718","4750","1060","1034","4864","469","593","988","859","432","661","4817","796","781","845","045","328","892","1251","535","567","1249","806","795","1356","153","198","253","605","829","807","1433","450","1776","1351","1141","544","579","478","775","799","018","1133","425","447","483","839","1338","1327","427","472","509","646","824","1170","1246","1139","631","193","679","887","627","119","114","430","013","279","448","678","900","032","265","620","1713","277","440","454","284","350","320","805","629","698","604","308","130","1800","252","695","667","935","1026","1739","764","103","1778","714","1660","1357","155","797","912","073","226","374","813","812","501","1100","1499","677","773","075","1687","346","506","543","1337","1341","560","902","637","648","1266","080","433","1379","1381","518","1158","1754","704","1509","397","595","017","861","1274","754","852","633","1196","638","682","659","5110","765","466","220","015","1300","1785","863","1294","061","1258","1471","1771","1795","426","546","836","972","978","832","1004","1168","670","1710","510","1260","1354","816","860","1253","1725","711","821","1343","1321","1352","1375","205","280","507","741","1374","4658","1347","906","5353","363","1099","1150","1189","1254","1297","1314","1568","1755","240","442","453","650","687","815","865","1682","087","1328","1588","4927","1363","369","743","582","491","818","086","1230","1311","1318","1648","942","423","634","1362","1365","1081","1167","1342","1678","393","443","4613","5058","596","877","1332","256","1790","357","1287","1714","1767","270","830","862","089","115","102","404","042","1062","1245","1276","1331","1378","162","1689","335","455","4948","758","855","882","843","1108","1271","475","373","039","014","046","1330","411","867","463","505","422","179","093","111","1325","1482","660","854","876","760","1709","079","1140","171","487","019","028","066","1206","1316","1344","1542","1560","1762","1796","5145","550","632","734","752","883","067","184","321","132","696","052","1470","888","1666","1281","857","038","246","347","644","026","1055","108","1084","1119","1323","1324","134","1372","1373","1430","431","444","5017","520","587","761","874","884","970","725","594","1345","1786","382","1371","467","680","691","1110","1209","1419","1531","1763","348","384","4682","1487","306","070","654","745","1193","121","1224","1625","1685","1722","1766","289","296","490","611","623","692","759","772","814","834","864","873","4972","387","615","303","602","866","871","878","1360","869","703","020","1511","1690","1727","309","410","702","726","879","109","185","827","1267","1667","609","828","486","030","1005","1669","266","4552","1358","1308","733","947","1073","1721","713","933","100","078","106","1382","1772","495","621","622","1756","802","136","496","562","564","662","736","569","221","872","223","339","1541","1794","345","511","262","539","853","1242","1549","288","554","763","1010","1781","215","228","868","1112","137","552","592","690","1003","105","607","798","847","517","4597","625","720","880","1326","282","362","672","716","1285","1383","1728","548","706","647","792","1340","1359","360","601","674","953","1364","489","1413","856","1451","1730","325","343","606","727","851","939","1268","671","118","514","5224","5342","916","1369","920","991","449","522","1368","738","849","1198","788","016","1187","541","1744","464","642","837","844","779","823","588","1036","1090","739","723","1644","693","783","143","1231","1464","1646","1647","167","113","581","409","036","468","540","529","744","499","940","966","125"],"proximosEnvios":[{"fecha":"2026-06-04","codigos":[],"enviado":false,"esCheck":true}],"historialEnvios":[{"fecha":"2026-05-28","codigos":["1376","352","1384","800","746","833","074","1757","1366","1329","1773","291","1758","1295","808","473","1284","4911","767","809","1265","694","1104","810","1370","1718","4750","1060","1034","4864","469","593","988","859","432","661","4817","796","781","845","045","328","892","1251","535","567","1249","806","795","1356","153","198","253","605","829","807","1433","450","1776","1351","1141","544","579","478","775","799","018","1133","425","447","483","839","1338","1327","427","472","509","646","824","1170","1246","1139","631","193","679","887","627","119","114","430","013","279","448","678","900","032","265","620","1713","277","440","454","284","350","320","805","629","698","604","308","130","1800","252","695","667","935","1026","1739","764","103","1778","714","1660","1357","155","797","912","073","226","374","813","812","501","1100","1499","677","773","075","1687","346","506","543","1337","1341","560","902","637","648","1266","080","433","1379","1381","518","1158","1754","704","1509","397","595","017","861","1274","754","852","633","1196","638","682","659","5110","829","765","466","220","015","1300","1785","863","1294","061","1258","1471","1771","1795","426","546","836","972","978","832","1004","1168","670","1710","510","1260","1354","816","860","1253","1725","711","821","1343","1321","1352","1375","205","280","507","741","1374","4658","1347","906","5353","363","1099","1150","1189","1254","1297","1314","1568","1755","240","442","453","650","687","815","865","1682","087","1328","1588","4927","1363","369","743","582","491","818","086","1230","1311","1318","1648","942","423","634","1362","1365","1081","1167","1342","1678","393","443","4613","5058","596","877","1332","256","1790","357","1287","1714","1767","270","830","862","089","115","102","404","042","1062","1245","1276","1331","1378","1379","162","1689","335","455","4948","758","855","882","843","1108","1271","475","373","039","014","046","1330","411","867","463","505","422","179","093","111","1325","1482","660","854","876","760","1709","079","1140","171","487","019","028","066","1206","1316","1344","1542","1560","1762","1796","5145","550","632","734","752","883","067","184","321","132","696","052","1470","888","1666","1281","857","038","246","347","644","026","1055","108","1084","1119","1323","1324","134","1372","1373","1430","431","444","5017","520","587","761","874","884","970","725","594","1345","1786","382","1371","467","680","691","1110","754","1209","1419","1531","1763","348","384","4682","1487","306","070","654","745","1193","121","1224","1625","1685","1722","1766","289","296","490","611","623","692","759","772","814","834","864","873","4972","387","615","303","602","866","871","878","1360","869","703","020","1511","1690","1727","309","410","702","726","879","109","185","827","1267","1667","609","828","486","030","1005","1669","266","4552","1358","1308","733","947","1073","1721","713","933","100","078","106","1382","1772","495","621","622","1756","802","136","496","562","564","662","736","569","221","872","223","339","1541","1794","345","511","262","539","853","1242","1549","288","554","763","1010","1781","215","228","868","1112","137","552","592","690","1003","105","607","798","847","517","4597","625","720","880","1326","282","362","672","716","1285","1383","1728","548","706","809","647","792","1340","1359","360","601","674","953","1364","489","1413","856","1451","1730","325","343","606","609","727","851","939","1268","671","118","514","5224","5342","916","1369","920","991","449","522","1368","738","849","1198","788","016","1187","541","1744","464","642","837","844","779","823","588","1036","1090","739","723","1644","693","783","143","1231","1464","1646","1647","167","113","581","409","036","468","540","529","744","499","940","966","125"],"totalCods":593,"tipoEnvio":"link","notas":"Envío de link catálogo"}],"visitas":[],"creadoEn":"2026-05-28T20:57:35.681Z"}</t>
+        <v>39</v>
+      </c>
+      <c r="O16" s="1" t="inlineStr">
+        <is>
+          <t>2026-05-10 (39)</t>
+        </is>
+      </c>
+      <c r="P16" s="1" t="inlineStr">
+        <is>
+          <t>{"id": "U-1778271567218463", "tipo": "cliente", "nombre": "Hector", "celular": "3159057825", "notas": "Solicita visita Codg. 622 Villa Milena - $190 - Inmb. RK", "metodoPago": ["Efectivo"], "estado": "visita", "etiqueta": "activo", "filtros": {"tipoInmueble": ["Casa"], "rangoPrecio": [], "zona": [], "habitaciones": [], "garaje": [], "pisos": [], "ubicacion": [], "piscina": [], "cocina": [], "barrio": [], "conjunto": [], "buscar": "", "maxPrice": 221000000}, "frecuencia": "semanal", "maxPorEnvio": 4, "nombreInmobiliaria": "", "nombreAgente": "", "propsFiltradas": ["828", "486", "1667", "609", "266", "713", "100", "933", "078", "622", "106", "562", "496", "569", "339", "345", "511", "288", "262", "1242", "1010", "592", "690", "552", "607", "798", "1003", "625", "1285", "282", "716", "706", "939", "5224", "991", "514", "325", "766", "541"], "propsEnviadas": ["828", "486", "1667", "609", "266", "713", "100", "933", "078", "622", "106", "562", "496", "569", "339", "345", "511", "288", "262", "1242", "1010", "592", "690", "552", "607", "798", "1003", "625", "1285", "282", "716", "706", "939", "5224", "991", "514", "325", "766", "541"], "proximosEnvios": [{"fecha": "2026-05-17", "codigos": [], "enviado": false, "esCheck": true}], "historialEnvios": [{"fecha": "2026-05-10", "codigos": ["828", "486", "1667", "609", "266", "713", "100", "933", "078", "622", "106", "562", "496", "569", "339", "345", "511", "288", "262", "1242", "1010", "592", "690", "552", "607", "798", "1003", "625", "1285", "282", "716", "706", "939", "5224", "991", "514", "325", "766", "541"], "totalCods": 39, "tipoEnvio": "silencioso", "notas": "Filtros actualizados (propiedades marcadas como vistas sin enviar WhatsApp)"}], "visitas": [{"id": "1777996776453", "codigo": "622", "fecha": "2026-05-09", "hora": "", "estado": "agendada", "oferto": "no", "oferta": "", "notas": "Inmueble de Rustika. Desocupada. Propietario viajando. hasta el sábado en la tarde la visita. No se ha coordinado la hora.", "cliente": "Hector", "celular": "3159057825", "inmobiliaria": ""}], "creadoEn": "2026-05-04T11:45:19.556Z"}</t>
         </is>
       </c>
     </row>
     <row r="17">
-      <c r="A17" t="inlineStr">
+      <c r="A17" s="1" t="inlineStr">
         <is>
           <t>U-1778329096171630</t>
         </is>
       </c>
-      <c r="B17" t="inlineStr">
-        <is>
-          <t>2026-06-05T16:50:42.437Z</t>
+      <c r="B17" s="1" t="inlineStr">
+        <is>
+          <t>2026-04-30T16:32:32.970Z</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
@@ -1434,8 +1548,10 @@
           <t>Hector Fabio</t>
         </is>
       </c>
-      <c r="D17" t="n">
-        <v>3122144224</v>
+      <c r="D17" s="1" t="inlineStr">
+        <is>
+          <t>3122144224</t>
+        </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
@@ -1453,12 +1569,12 @@
           <t>activo</t>
         </is>
       </c>
-      <c r="I17" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Pendiente visitar Codg. 1326 -J - Lote la Primavera $150 mlls. con tercerría Jennifer.  Cliente, ya está en contacto  con Jennifer. En caso de venta con terceria. J-Jennifer e ICDE. </t>
-        </is>
-      </c>
-      <c r="J17" t="inlineStr">
+      <c r="I17" s="1" t="inlineStr">
+        <is>
+          <t>Pendiente visitar Codg. 1326 -J - Lote la Primavera $150 mlls. con tercerría Jennifer. Cliente, ya está en contacto con Jennifer. En caso de venta con terceria. J-Jennifer e ICDE.</t>
+        </is>
+      </c>
+      <c r="J17" s="1" t="inlineStr">
         <is>
           <t>Tipos: Casa | Zonas: Oriente, Sur | Precio: 0 - 200000000</t>
         </is>
@@ -1468,7 +1584,7 @@
           <t>Efectivo</t>
         </is>
       </c>
-      <c r="L17" t="n">
+      <c r="L17" s="2" t="n">
         <v>200000000</v>
       </c>
       <c r="M17" t="inlineStr">
@@ -1479,35 +1595,37 @@
       <c r="N17" t="n">
         <v>16</v>
       </c>
-      <c r="O17" t="inlineStr">
+      <c r="O17" s="1" t="inlineStr">
         <is>
           <t>2026-04-30 (16)</t>
         </is>
       </c>
-      <c r="P17" t="inlineStr">
-        <is>
-          <t>{"id":"U-1778329096171630","tipo":"cliente","nombre":"Hector Fabio","celular":"3122144224","notas":"Pendiente visitar Codg. 1326 -J - Lote la Primavera $150 mlls. con tercerría Jennifer.  Cliente, ya está en contacto  con Jennifer. En caso de venta con terceria. J-Jennifer e ICDE. ","metodoPago":["Efectivo"],"estado":"visita","etiqueta":"activo","filtros":{"tipoInmueble":["Casa"],"rangoPrecio":[],"zona":["Oriente","Sur"],"habitaciones":[],"garaje":[],"pisos":[],"ubicacion":[],"piscina":[],"cocina":[],"barrio":[],"conjunto":[],"buscar":"","maxPrice":200000000},"frecuencia":"semanal","maxPorEnvio":4,"nombreInmobiliaria":"","nombreAgente":"","propsFiltradas":["562","569","1242","1010","1003","552","607","690","798","1285","716","706","939","5224","991","325"],"propsEnviadas":["562","569","1242","1010","1003","552","607","690","798","1285","716","706","939","5224","991","325"],"proximosEnvios":[{"fecha":"2026-05-07","codigos":[],"enviado":false,"esCheck":true}],"historialEnvios":[{"fecha":"2026-04-30","codigos":["562","569","1242","1010","1003","552","607","690","798","1285","716","706","939","5224","991","325"],"totalCods":16,"tipoEnvio":"link","notas":"Envío de link catálogo"}],"visitas":[],"creadoEn":"2026-04-30T16:32:32.970Z","feedback":{}}</t>
+      <c r="P17" s="1" t="inlineStr">
+        <is>
+          <t>{"id": "U-1778329096171630", "tipo": "cliente", "nombre": "Hector Fabio", "celular": "3122144224", "notas": "Pendiente visitar Codg. 1326 -J - Lote la Primavera $150 mlls. con tercerría Jennifer. Cliente, ya está en contacto con Jennifer. En caso de venta con terceria. J-Jennifer e ICDE. ", "metodoPago": ["Efectivo"], "estado": "visita", "etiqueta": "activo", "filtros": {"tipoInmueble": ["Casa"], "rangoPrecio": [], "zona": ["Oriente", "Sur"], "habitaciones": [], "garaje": [], "pisos": [], "ubicacion": [], "piscina": [], "cocina": [], "barrio": [], "conjunto": [], "buscar": "", "maxPrice": 200000000}, "frecuencia": "semanal", "maxPorEnvio": 4, "nombreInmobiliaria": "", "nombreAgente": "", "propsFiltradas": ["562", "569", "1242", "1010", "1003", "552", "607", "690", "798", "1285", "716", "706", "939", "5224", "991", "325"], "propsEnviadas": ["562", "569", "1242", "1010", "1003", "552", "607", "690", "798", "1285", "716", "706", "939", "5224", "991", "325"], "proximosEnvios": [{"fecha": "2026-05-07", "codigos": [], "enviado": false, "esCheck": true}], "historialEnvios": [{"fecha": "2026-04-30", "codigos": ["562", "569", "1242", "1010", "1003", "552", "607", "690", "798", "1285", "716", "706", "939", "5224", "991", "325"], "totalCods": 16, "tipoEnvio": "link", "notas": "Envío de link catálogo"}], "visitas": [], "creadoEn": "2026-04-30T16:32:32.970Z", "feedback": {}}</t>
         </is>
       </c>
     </row>
     <row r="18">
-      <c r="A18" t="inlineStr">
-        <is>
-          <t>U-1779061841119543</t>
-        </is>
-      </c>
-      <c r="B18" t="inlineStr">
-        <is>
-          <t>2026-06-05T16:51:56.903Z</t>
+      <c r="A18" s="1" t="inlineStr">
+        <is>
+          <t>U-1779750679001688</t>
+        </is>
+      </c>
+      <c r="B18" s="1" t="inlineStr">
+        <is>
+          <t>2026-05-25T23:11:19.001Z</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>María Nohora  Rojas</t>
-        </is>
-      </c>
-      <c r="D18" t="n">
-        <v>3124797922</v>
+          <t>Iasias Chaux</t>
+        </is>
+      </c>
+      <c r="D18" s="1" t="inlineStr">
+        <is>
+          <t>3152445222</t>
+        </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
@@ -1522,26 +1640,26 @@
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>tibio</t>
-        </is>
-      </c>
-      <c r="I18" t="inlineStr">
-        <is>
-          <t>Compra Apto conjunto. Yessica solicita para la tía Ma. Nohora.</t>
-        </is>
-      </c>
-      <c r="J18" t="inlineStr">
-        <is>
-          <t>Tipos: Apartamento en conjunto, Apartamento | Zonas: Norte, Centro | Precio: 161000000 - 336000000</t>
+          <t>activo</t>
+        </is>
+      </c>
+      <c r="I18" s="1" t="inlineStr">
+        <is>
+          <t>Don Isais Chaux . . El papá de Frnasua Chaux. Compra por inversión Apto en conjunto economico $140mlls.</t>
+        </is>
+      </c>
+      <c r="J18" s="1" t="inlineStr">
+        <is>
+          <t>Tipos: Apartamento en conjunto | Precio: 83000000 - 153000000</t>
         </is>
       </c>
       <c r="K18" t="inlineStr">
         <is>
-          <t>Efectivo, Crédito</t>
-        </is>
-      </c>
-      <c r="L18" t="n">
-        <v>336000000</v>
+          <t>Efectivo</t>
+        </is>
+      </c>
+      <c r="L18" s="2" t="n">
+        <v>153000000</v>
       </c>
       <c r="M18" t="inlineStr">
         <is>
@@ -1549,37 +1667,39 @@
         </is>
       </c>
       <c r="N18" t="n">
-        <v>18</v>
-      </c>
-      <c r="O18" t="inlineStr">
-        <is>
-          <t>2026-05-17 (18)</t>
-        </is>
-      </c>
-      <c r="P18" t="inlineStr">
-        <is>
-          <t>{"id":"U-1779061841119543","tipo":"cliente","nombre":"María Nohora  Rojas","celular":"3124797922","notas":"Compra Apto conjunto. Yessica solicita para la tía Ma. Nohora.","metodoPago":["Efectivo","Crédito"],"estado":"enviando","etiqueta":"tibio","filtros":{"tipoInmueble":["Apartamento en conjunto","Apartamento"],"rangoPrecio":[],"zona":["Norte","Centro"],"habitaciones":[],"garaje":[],"pisos":[],"ubicacion":[],"piscina":[],"cocina":[],"barrio":[],"conjunto":[],"minPrice":161000000,"maxPrice":336000000,"kmzCategory":["APTO Y APTO EN CONJUNTO 🏢","CASA EN CONJUNTO, CAMPESTRE IND Y EN CONJUNTO⛳","CASA LOTE, LOTE Y LOTE EN CONJUNTO ⛳","CASAS Y EDIFICIOS RENTABLES💲","CASAS 🏡","LOCAL, BODEGA Y OFICINA 🏪"],"buscar":""},"frecuencia":"semanal","maxPorEnvio":4,"nombreInmobiliaria":"","nombreAgente":"","propsFiltradas":["1781","228","215","1549","662","1382","1721","1358","4552","185","726","1690","309","1360","834","067","1316","019","373"],"propsEnviadas":["1781","228","215","1549","662","1382","1721","1358","4552","726","1690","309","834","067","1316","019","373","1360"],"proximosEnvios":[{"fecha":"2026-05-24","codigos":[],"enviado":false,"esCheck":true}],"historialEnvios":[{"fecha":"2026-05-17","codigos":["1781","228","215","1549","662","1382","1721","1358","4552","726","1690","309","834","067","1316","019","373","1360"],"totalCods":18,"tipoEnvio":"link","notas":"Envío de link catálogo"}],"visitas":[{"id":"1779119510834","codigo":"662","fecha":"2026-05-18","hora":"","estado":"agendada","oferto":"no","oferta":"","notas":"","cliente":"María Nohora  Rojas","celular":"3124797922","inmobiliaria":""}],"creadoEn":"2026-05-17T23:50:41.120Z"}</t>
+        <v>11</v>
+      </c>
+      <c r="O18" s="1" t="inlineStr">
+        <is>
+          <t>2026-05-25 (11)</t>
+        </is>
+      </c>
+      <c r="P18" s="1" t="inlineStr">
+        <is>
+          <t>{"id": "U-1779750679001688", "tipo": "cliente", "nombre": "Iasias Chaux", "celular": "3152445222", "notas": "Don Isais Chaux . . El papá de Frnasua Chaux. Compra por inversión Apto en conjunto economico $140mlls.", "metodoPago": ["Efectivo"], "estado": "enviando", "etiqueta": "activo", "filtros": {"tipoInmueble": ["Apartamento en conjunto"], "rangoPrecio": [], "zona": [], "habitaciones": [], "garaje": [], "pisos": [], "ubicacion": [], "piscina": [], "cocina": [], "barrio": [], "conjunto": [], "minPrice": 83000000, "maxPrice": 153000000, "kmzCategory": ["APTO Y APTO EN CONJUNTO 🏢", "CASA EN CONJUNTO, CAMPESTRE IND Y EN CONJUNTO⛳", "CASA LOTE, LOTE Y LOTE EN CONJUNTO ⛳", "CASAS Y EDIFICIOS RENTABLES💲", "CASAS 🏡", "LOCAL, BODEGA Y OFICINA 🏪"], "buscar": ""}, "frecuencia": "semanal", "maxPorEnvio": 4, "nombreInmobiliaria": "", "nombreAgente": "", "propsFiltradas": ["1383", "1728", "647", "360", "489", "856", "1369", "920", "844", "588", "548"], "propsEnviadas": ["1383", "1728", "647", "360", "489", "856", "1369", "920", "844", "588", "548"], "proximosEnvios": [{"fecha": "2026-06-01", "codigos": [], "enviado": false, "esCheck": true}], "historialEnvios": [{"fecha": "2026-05-25", "codigos": ["1383", "1728", "647", "360", "489", "856", "1369", "920", "844", "588", "548"], "totalCods": 11, "tipoEnvio": "link", "notas": "Envío de link catálogo"}], "visitas": [], "creadoEn": "2026-05-25T23:11:19.001Z"}</t>
         </is>
       </c>
     </row>
     <row r="19">
-      <c r="A19" t="inlineStr">
-        <is>
-          <t>U-178035156168992</t>
-        </is>
-      </c>
-      <c r="B19" t="inlineStr">
-        <is>
-          <t>2026-06-04T23:06:29.311Z</t>
+      <c r="A19" s="1" t="inlineStr">
+        <is>
+          <t>1777994227586</t>
+        </is>
+      </c>
+      <c r="B19" s="1" t="inlineStr">
+        <is>
+          <t>2026-06-03T15:39:35.409Z</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Sandra Liliana Murcia</t>
-        </is>
-      </c>
-      <c r="D19" t="n">
-        <v>3125246887</v>
+          <t>Jaison Roldando Gonzalez</t>
+        </is>
+      </c>
+      <c r="D19" s="1" t="inlineStr">
+        <is>
+          <t>3214939473</t>
+        </is>
       </c>
       <c r="E19" t="inlineStr">
         <is>
@@ -1589,55 +1709,57 @@
       <c r="F19" t="inlineStr"/>
       <c r="G19" t="inlineStr">
         <is>
-          <t>visita</t>
+          <t>enviando</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>activo</t>
-        </is>
-      </c>
-      <c r="I19" t="inlineStr">
-        <is>
-          <t>Compra lote en conjunto 1710 $445mlls- C&amp;C.</t>
-        </is>
-      </c>
-      <c r="J19" t="inlineStr"/>
-      <c r="K19" t="inlineStr">
-        <is>
-          <t>Efectivo</t>
-        </is>
-      </c>
+          <t>tibio</t>
+        </is>
+      </c>
+      <c r="I19" s="1" t="inlineStr">
+        <is>
+          <t>Busca lote o casa lote central - presupuesto $200 mlls .</t>
+        </is>
+      </c>
+      <c r="J19" s="1" t="inlineStr"/>
+      <c r="K19" t="inlineStr"/>
       <c r="L19" t="inlineStr"/>
-      <c r="M19" t="inlineStr"/>
+      <c r="M19" t="inlineStr">
+        <is>
+          <t>manual</t>
+        </is>
+      </c>
       <c r="N19" t="n">
         <v>0</v>
       </c>
-      <c r="O19" t="inlineStr"/>
-      <c r="P19" t="inlineStr">
-        <is>
-          <t>{"id":"U-178035156168992","fecha":"2026-06-04T19:54:31.263Z","nombre":"Sandra Liliana Murcia","celular":3125246887,"tipo":"cliente","estado":"visita","etiqueta":"activo","notas":"Compra lote en conjunto 1710 $445mlls- C&amp;C.","metodoPago":["Efectivo"],"fromCloud":true}</t>
+      <c r="O19" s="1" t="inlineStr"/>
+      <c r="P19" s="1" t="inlineStr">
+        <is>
+          <t>{"id": 1777994227586, "fecha": "2026-06-03T15:39:35.409Z", "nombre": "Jaison Roldando Gonzalez", "celular": "3214939473", "tipo": "cliente", "estado": "enviando", "etiqueta": "tibio", "notas": "Busca lote o casa lote central - presupuesto $200 mlls ."}</t>
         </is>
       </c>
     </row>
     <row r="20">
-      <c r="A20" t="inlineStr">
-        <is>
-          <t>U-1778329096171811</t>
-        </is>
-      </c>
-      <c r="B20" t="inlineStr">
-        <is>
-          <t>2026-06-05T16:49:10.905Z</t>
+      <c r="A20" s="1" t="inlineStr">
+        <is>
+          <t>1777575405797</t>
+        </is>
+      </c>
+      <c r="B20" s="1" t="inlineStr">
+        <is>
+          <t>2026-06-04T16:13:29.738Z</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Carlos Medina</t>
-        </is>
-      </c>
-      <c r="D20" t="n">
-        <v>3132476032</v>
+          <t>Jazmin -Luis</t>
+        </is>
+      </c>
+      <c r="D20" s="1" t="inlineStr">
+        <is>
+          <t>3112189519</t>
+        </is>
       </c>
       <c r="E20" t="inlineStr">
         <is>
@@ -1647,67 +1769,53 @@
       <c r="F20" t="inlineStr"/>
       <c r="G20" t="inlineStr">
         <is>
-          <t>enviando</t>
+          <t>inactivo</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>tibio</t>
-        </is>
-      </c>
-      <c r="I20" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Codg. 541 - Praderas del Norte - $95 - Inmob. Primv -  </t>
-        </is>
-      </c>
-      <c r="J20" t="inlineStr">
-        <is>
-          <t>Tipos: Casa | Precio: 0 - 119000000</t>
-        </is>
-      </c>
-      <c r="K20" t="inlineStr">
-        <is>
-          <t>Crédito</t>
-        </is>
-      </c>
-      <c r="L20" t="n">
-        <v>119000000</v>
-      </c>
+          <t>inactivo</t>
+        </is>
+      </c>
+      <c r="I20" s="1" t="inlineStr"/>
+      <c r="J20" s="1" t="inlineStr"/>
+      <c r="K20" t="inlineStr"/>
+      <c r="L20" t="inlineStr"/>
       <c r="M20" t="inlineStr">
         <is>
-          <t>semanal</t>
+          <t>manual</t>
         </is>
       </c>
       <c r="N20" t="n">
-        <v>3</v>
-      </c>
-      <c r="O20" t="inlineStr">
-        <is>
-          <t>2026-05-08 (3)</t>
-        </is>
-      </c>
-      <c r="P20" t="inlineStr">
-        <is>
-          <t>{"id":"U-1778329096171811","tipo":"cliente","nombre":"Carlos Medina","celular":"3132476032","notas":"Codg. 541 - Praderas del Norte - $95 - Inmob. Primv -  ","metodoPago":["Crédito"],"estado":"enviando","etiqueta":"tibio","filtros":{"tipoInmueble":["Casa"],"rangoPrecio":[],"zona":[],"habitaciones":[],"garaje":[],"pisos":[],"ubicacion":[],"piscina":[],"cocina":[],"barrio":[],"conjunto":[],"buscar":"","maxPrice":119000000},"frecuencia":"semanal","maxPorEnvio":4,"nombreInmobiliaria":"","nombreAgente":"","propsFiltradas":["325","766","541"],"propsEnviadas":["325","766","541"],"proximosEnvios":[{"fecha":"2026-05-15","codigos":[],"enviado":false,"esCheck":true}],"historialEnvios":[{"fecha":"2026-05-08","codigos":["325","766","541"],"totalCods":3,"tipoEnvio":"silencioso","notas":"Filtros actualizados (propiedades marcadas como vistas sin enviar WhatsApp)"}],"visitas":[],"creadoEn":"2026-05-04T12:03:00.347Z","feedback":{}}</t>
+        <v>0</v>
+      </c>
+      <c r="O20" s="1" t="inlineStr"/>
+      <c r="P20" s="1" t="inlineStr">
+        <is>
+          <t>{"id": 1777575405797, "fecha": "2026-06-04T16:13:29.738Z", "nombre": "Jazmin -Luis", "celular": "3112189519", "tipo": "cliente", "estado": "inactivo", "etiqueta": "inactivo", "notas": ""}</t>
         </is>
       </c>
     </row>
     <row r="21">
-      <c r="A21" t="n">
-        <v>1777922884952</v>
-      </c>
-      <c r="B21" t="inlineStr">
-        <is>
-          <t>2026-06-05T16:51:47.242Z</t>
+      <c r="A21" s="1" t="inlineStr">
+        <is>
+          <t>1777767356975</t>
+        </is>
+      </c>
+      <c r="B21" s="1" t="inlineStr">
+        <is>
+          <t>2026-05-03T00:15:56.979Z</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>María Angelica</t>
-        </is>
-      </c>
-      <c r="D21" t="n">
-        <v>3133223758</v>
+          <t>Jessica Martinez</t>
+        </is>
+      </c>
+      <c r="D21" s="1" t="inlineStr">
+        <is>
+          <t>3166491597</t>
+        </is>
       </c>
       <c r="E21" t="inlineStr">
         <is>
@@ -1725,14 +1833,10 @@
           <t>tibio</t>
         </is>
       </c>
-      <c r="I21" t="inlineStr">
-        <is>
-          <t>Cliente del mcpio de Tello . Casa economica de $75 mlls con garaje.</t>
-        </is>
-      </c>
-      <c r="J21" t="inlineStr">
-        <is>
-          <t>Tipos: Casa | Precio: 0 - 159000000</t>
+      <c r="I21" s="1" t="inlineStr"/>
+      <c r="J21" s="1" t="inlineStr">
+        <is>
+          <t>Tipos: Casa en conjunto | Zonas: Norte, Oriente | Precio: 0 - 253000000</t>
         </is>
       </c>
       <c r="K21" t="inlineStr">
@@ -1740,8 +1844,8 @@
           <t>Efectivo</t>
         </is>
       </c>
-      <c r="L21" t="n">
-        <v>159000000</v>
+      <c r="L21" s="2" t="n">
+        <v>253000000</v>
       </c>
       <c r="M21" t="inlineStr">
         <is>
@@ -1749,33 +1853,39 @@
         </is>
       </c>
       <c r="N21" t="n">
-        <v>0</v>
-      </c>
-      <c r="O21" t="inlineStr"/>
-      <c r="P21" t="inlineStr">
-        <is>
-          <t>{"id":"1777922884952","tipo":"cliente","nombre":"María Angelica","celular":"3133223758","notas":"Cliente del mcpio de Tello . Casa economica de $75 mlls con garaje.","metodoPago":["Efectivo"],"estado":"enviando","etiqueta":"tibio","filtros":{"tipoInmueble":["Casa"],"rangoPrecio":[],"zona":[],"habitaciones":[],"garaje":[],"pisos":[],"ubicacion":[],"piscina":[],"cocina":[],"barrio":[],"conjunto":[],"buscar":"","maxPrice":159000000},"frecuencia":"semanal","maxPorEnvio":4,"nombreInmobiliaria":"","nombreAgente":"","propsFiltradas":["541"],"propsEnviadas":[],"proximosEnvios":[{"fecha":"2026-05-11","codigos":[],"enviado":false,"esCheck":true}],"historialEnvios":[],"visitas":[],"creadoEn":"2026-05-04T19:28:04.953Z","feedback":{}}</t>
+        <v>1</v>
+      </c>
+      <c r="O21" s="1" t="inlineStr">
+        <is>
+          <t>2026-05-03 (2)</t>
+        </is>
+      </c>
+      <c r="P21" s="1" t="inlineStr">
+        <is>
+          <t>{"id": "1777767356975", "tipo": "cliente", "nombre": "Jessica Martinez", "celular": "3166491597", "notas": "", "metodoPago": ["Efectivo"], "estado": "enviando", "etiqueta": "tibio", "filtros": {"tipoInmueble": ["Casa en conjunto"], "rangoPrecio": [], "zona": ["Norte", "Oriente"], "habitaciones": [], "garaje": [], "pisos": [], "ubicacion": [], "piscina": [], "cocina": [], "barrio": [], "conjunto": [], "buscar": "", "maxPrice": 253000000}, "frecuencia": "semanal", "maxPorEnvio": 4, "nombreInmobiliaria": "", "nombreAgente": "", "propsFiltradas": ["", ""], "propsEnviadas": [""], "proximosEnvios": [{"fecha": "2026-05-10", "codigos": [], "enviado": false, "esCheck": true}], "historialEnvios": [{"fecha": "2026-05-03", "codigos": ["", ""], "totalCods": 2, "tipoEnvio": "link", "notas": "Envío de link catálogo"}], "visitas": [], "creadoEn": "2026-05-03T00:15:56.979Z", "feedback": {}}</t>
         </is>
       </c>
     </row>
     <row r="22">
-      <c r="A22" t="inlineStr">
-        <is>
-          <t>U-1780007032409870</t>
-        </is>
-      </c>
-      <c r="B22" t="inlineStr">
-        <is>
-          <t>2026-06-05T16:52:50.686Z</t>
+      <c r="A22" s="1" t="inlineStr">
+        <is>
+          <t>U-1779050115953215</t>
+        </is>
+      </c>
+      <c r="B22" s="1" t="inlineStr">
+        <is>
+          <t>2026-05-17T20:35:15.953Z</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Nelson</t>
-        </is>
-      </c>
-      <c r="D22" t="n">
-        <v>3138314537</v>
+          <t>Jorge Enrique Ossa Hernandez</t>
+        </is>
+      </c>
+      <c r="D22" s="1" t="inlineStr">
+        <is>
+          <t>3164254862</t>
+        </is>
       </c>
       <c r="E22" t="inlineStr">
         <is>
@@ -1790,17 +1900,17 @@
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>activo</t>
-        </is>
-      </c>
-      <c r="I22" t="inlineStr">
-        <is>
-          <t>Compra casa rentable $400mlls-Norte-Efectivo.</t>
-        </is>
-      </c>
-      <c r="J22" t="inlineStr">
-        <is>
-          <t>Tipos: Casa rentable | Zonas: Norte | Precio: 303000000 - 451000000</t>
+          <t>tibio</t>
+        </is>
+      </c>
+      <c r="I22" s="1" t="inlineStr">
+        <is>
+          <t>Casa o casa lote - Centro - $200mlls</t>
+        </is>
+      </c>
+      <c r="J22" s="1" t="inlineStr">
+        <is>
+          <t>Tipos: Casa, Casa lote | Zonas: Centro | Precio: 159000000 - 326000000</t>
         </is>
       </c>
       <c r="K22" t="inlineStr">
@@ -1808,8 +1918,8 @@
           <t>Efectivo</t>
         </is>
       </c>
-      <c r="L22" t="n">
-        <v>451000000</v>
+      <c r="L22" s="2" t="n">
+        <v>326000000</v>
       </c>
       <c r="M22" t="inlineStr">
         <is>
@@ -1817,89 +1927,111 @@
         </is>
       </c>
       <c r="N22" t="n">
-        <v>15</v>
-      </c>
-      <c r="O22" t="inlineStr">
-        <is>
-          <t>2026-05-28 (15)</t>
-        </is>
-      </c>
-      <c r="P22" t="inlineStr">
-        <is>
-          <t>{"id":"U-1780007032409870","tipo":"cliente","nombre":"Nelson","celular":"3138314537","notas":"Compra casa rentable $400mlls-Norte-Efectivo.","metodoPago":["Efectivo"],"estado":"enviando","etiqueta":"activo","filtros":{"tipoInmueble":["Casa rentable"],"rangoPrecio":[],"zona":["Norte"],"habitaciones":[],"garaje":[],"pisos":[],"ubicacion":[],"piscina":[],"cocina":[],"barrio":[],"conjunto":[],"minPrice":303000000,"maxPrice":451000000,"kmzCategory":["APTO Y APTO EN CONJUNTO 🏢","CASA EN CONJUNTO, CAMPESTRE IND Y EN CONJUNTO⛳","CASA LOTE, LOTE Y LOTE EN CONJUNTO ⛳","CASAS Y EDIFICIOS RENTABLES💲","CASAS 🏡","LOCAL, BODEGA Y OFICINA 🏪"],"buscar":""},"frecuencia":"semanal","maxPorEnvio":4,"nombreInmobiliaria":"","nombreAgente":"","propsFiltradas":["978","1189","240","1682","818","1230","1648","423","1332","1378","455","758","014","179","1709"],"propsEnviadas":["978","1189","240","1682","818","1230","1648","423","1332","1378","455","758","014","179","1709"],"proximosEnvios":[{"fecha":"2026-06-04","codigos":[],"enviado":false,"esCheck":true}],"historialEnvios":[{"fecha":"2026-05-28","codigos":["978","1189","240","1682","818","1230","1648","423","1332","1378","455","758","014","179","1709"],"totalCods":15,"tipoEnvio":"link","notas":"Envío de link catálogo"}],"visitas":[],"creadoEn":"2026-05-28T22:23:52.409Z"}</t>
+        <v>4</v>
+      </c>
+      <c r="O22" s="1" t="inlineStr">
+        <is>
+          <t>2026-05-17 (4)</t>
+        </is>
+      </c>
+      <c r="P22" s="1" t="inlineStr">
+        <is>
+          <t>{"id": "U-1779050115953215", "tipo": "cliente", "nombre": "Jorge Enrique Ossa Hernandez", "celular": "3164254862", "notas": "Casa o casa lote - Centro - $200mlls", "metodoPago": ["Efectivo"], "estado": "enviando", "etiqueta": "tibio", "filtros": {"tipoInmueble": ["Casa", "Casa lote"], "rangoPrecio": [], "zona": ["Centro"], "habitaciones": [], "garaje": [], "pisos": [], "ubicacion": [], "piscina": [], "cocina": [], "barrio": [], "conjunto": [], "minPrice": 159000000, "maxPrice": 326000000, "kmzCategory": [], "buscar": ""}, "frecuencia": "semanal", "maxPorEnvio": 4, "nombreInmobiliaria": "", "nombreAgente": "", "propsFiltradas": ["1344", "1140", "079", "486", "100"], "propsEnviadas": ["1344", "1140", "079", "100"], "proximosEnvios": [{"fecha": "2026-05-24", "codigos": [], "enviado": false, "esCheck": true}], "historialEnvios": [{"fecha": "2026-05-17", "codigos": ["1344", "1140", "079", "100"], "totalCods": 4, "tipoEnvio": "link", "notas": "Envío de link catálogo"}], "visitas": [], "creadoEn": "2026-05-17T20:35:15.953Z"}</t>
         </is>
       </c>
     </row>
     <row r="23">
-      <c r="A23" t="n">
-        <v>1777895245612</v>
-      </c>
-      <c r="B23" t="inlineStr">
-        <is>
-          <t>2026-06-04T19:36:32.762Z</t>
+      <c r="A23" s="1" t="inlineStr">
+        <is>
+          <t>U-1778271567218833</t>
+        </is>
+      </c>
+      <c r="B23" s="1" t="inlineStr">
+        <is>
+          <t>2026-05-05T14:29:10.587Z</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Sandra</t>
-        </is>
-      </c>
-      <c r="D23" t="n">
-        <v>3142014730</v>
+          <t>Jovel Muñoz</t>
+        </is>
+      </c>
+      <c r="D23" s="1" t="inlineStr">
+        <is>
+          <t>3232391020</t>
+        </is>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>cliente</t>
-        </is>
-      </c>
-      <c r="F23" t="inlineStr"/>
+          <t>inmobiliaria</t>
+        </is>
+      </c>
+      <c r="F23" t="inlineStr">
+        <is>
+          <t>Jovel Muñoz</t>
+        </is>
+      </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>inactivo</t>
+          <t>visita</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>inactivo</t>
-        </is>
-      </c>
-      <c r="I23" t="inlineStr">
-        <is>
-          <t>Solicita cita  Codg. 1010 - sector sur - $165 - Jennifer . . . No fue posible coordinar la cita. Arrendatarios complicados. Se suspende la publicación hasta que entreguen la casa.</t>
-        </is>
-      </c>
-      <c r="J23" t="inlineStr"/>
-      <c r="K23" t="inlineStr"/>
+          <t>tibio</t>
+        </is>
+      </c>
+      <c r="I23" s="1" t="inlineStr">
+        <is>
+          <t>Codg. 221 CJ. Portal del Salitre . Pendiente de visitarla cuando terminen las obras locativas.</t>
+        </is>
+      </c>
+      <c r="J23" s="1" t="inlineStr">
+        <is>
+          <t>Tipos: Casa en conjunto</t>
+        </is>
+      </c>
+      <c r="K23" t="inlineStr">
+        <is>
+          <t>Efectivo, Crédito</t>
+        </is>
+      </c>
       <c r="L23" t="inlineStr"/>
-      <c r="M23" t="inlineStr"/>
+      <c r="M23" t="inlineStr">
+        <is>
+          <t>semanal</t>
+        </is>
+      </c>
       <c r="N23" t="n">
         <v>0</v>
       </c>
-      <c r="O23" t="inlineStr"/>
-      <c r="P23" t="inlineStr">
-        <is>
-          <t>{"id":"1777895245612","fecha":"2026-06-03T16:01:58.640Z","nombre":"Sandra","celular":3142014730,"tipo":"cliente","estado":"inactivo","etiqueta":"inactivo","notas":"Solicita cita  Codg. 1010 - sector sur - $165 - Jennifer . . . No fue posible coordinar la cita. Arrendatarios complicados. Se suspende la publicación hasta que entreguen la casa.","fromCloud":true}</t>
+      <c r="O23" s="1" t="inlineStr"/>
+      <c r="P23" s="1" t="inlineStr">
+        <is>
+          <t>{"id": "U-1778271567218833", "tipo": "inmobiliaria", "nombre": "Jovel Muñoz", "celular": "3232391020", "notas": "Codg. 221 CJ. Portal del Salitre . Pendiente de visitarla cuando terminen las obras locativas.", "metodoPago": ["Efectivo", "Crédito"], "estado": "visita", "etiqueta": "tibio", "filtros": {"tipoInmueble": ["Casa en conjunto"], "rangoPrecio": [], "zona": [], "habitaciones": [], "garaje": [], "pisos": [], "ubicacion": [], "piscina": [], "cocina": [], "barrio": [], "conjunto": [], "buscar": "221"}, "frecuencia": "semanal", "maxPorEnvio": 4, "nombreInmobiliaria": "Jovel Muñoz", "nombreAgente": "3232391020", "propsFiltradas": ["221"], "propsEnviadas": [], "proximosEnvios": [{"fecha": "2026-05-12", "codigos": [], "enviado": false, "esCheck": true}], "historialEnvios": [], "visitas": [], "creadoEn": "2026-05-05T14:29:10.587Z"}</t>
         </is>
       </c>
     </row>
     <row r="24">
-      <c r="A24" t="inlineStr">
-        <is>
-          <t>U-1779811520619231</t>
-        </is>
-      </c>
-      <c r="B24" t="inlineStr">
-        <is>
-          <t>2026-06-05T16:50:00.153Z</t>
+      <c r="A24" s="1" t="inlineStr">
+        <is>
+          <t>1778196950123</t>
+        </is>
+      </c>
+      <c r="B24" s="1" t="inlineStr">
+        <is>
+          <t>2026-06-04T16:17:37.257Z</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>ELENA</t>
-        </is>
-      </c>
-      <c r="D24" t="n">
-        <v>3148518555</v>
+          <t>Justiniano Monje Cortes</t>
+        </is>
+      </c>
+      <c r="D24" s="1" t="inlineStr">
+        <is>
+          <t>3204666321</t>
+        </is>
       </c>
       <c r="E24" t="inlineStr">
         <is>
@@ -1909,69 +2041,57 @@
       <c r="F24" t="inlineStr"/>
       <c r="G24" t="inlineStr">
         <is>
-          <t>enviando</t>
+          <t>inactivo</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>tibio</t>
-        </is>
-      </c>
-      <c r="I24" t="inlineStr">
-        <is>
-          <t>Compra casa económica hasta $110mlls.</t>
-        </is>
-      </c>
-      <c r="J24" t="inlineStr">
-        <is>
-          <t>Tipos: Casa | Precio: 70000000 - 154000000</t>
-        </is>
-      </c>
-      <c r="K24" t="inlineStr">
-        <is>
-          <t>Efectivo, Crédito</t>
-        </is>
-      </c>
-      <c r="L24" t="n">
-        <v>154000000</v>
-      </c>
+          <t>inactivo</t>
+        </is>
+      </c>
+      <c r="I24" s="1" t="inlineStr">
+        <is>
+          <t>Codg. 223 - Los Cambulos II-$175mlls - Disponible. Efectivo. YA INVIRTIO.</t>
+        </is>
+      </c>
+      <c r="J24" s="1" t="inlineStr"/>
+      <c r="K24" t="inlineStr"/>
+      <c r="L24" t="inlineStr"/>
       <c r="M24" t="inlineStr">
         <is>
-          <t>semanal</t>
+          <t>manual</t>
         </is>
       </c>
       <c r="N24" t="n">
-        <v>22</v>
-      </c>
-      <c r="O24" t="inlineStr">
-        <is>
-          <t>2026-05-26 (22)</t>
-        </is>
-      </c>
-      <c r="P24" t="inlineStr">
-        <is>
-          <t>{"id":"U-1779811520619231","tipo":"cliente","nombre":"ELENA","celular":"3148518555","notas":"Compra casa económica hasta $110mlls.","metodoPago":["Efectivo","Crédito"],"estado":"enviando","etiqueta":"tibio","filtros":{"tipoInmueble":["Casa"],"rangoPrecio":[],"zona":[],"habitaciones":[],"garaje":[],"pisos":[],"ubicacion":[],"piscina":[],"cocina":[],"barrio":[],"conjunto":[],"minPrice":70000000,"maxPrice":154000000,"kmzCategory":[],"buscar":""},"frecuencia":"semanal","maxPorEnvio":4,"nombreInmobiliaria":"","nombreAgente":"","propsFiltradas":["541","449","514","5224","991","325","851","939","1285","282","706","716"],"propsEnviadas":["496","078","106","622","713","933","266","609","828","702","541","449","514","5224","991","325","851","939","1285","282","706","716"],"proximosEnvios":[{"fecha":"2026-06-02","codigos":[],"enviado":false,"esCheck":true}],"historialEnvios":[{"fecha":"2026-05-26","codigos":["496","078","106","622","713","933","266","609","828","702","541","449","514","5224","991","325","851","939","1285","282","706","716"],"totalCods":22,"tipoEnvio":"individual","notas":"Envío selección individual"}],"visitas":[],"creadoEn":"2026-05-26T16:05:20.620Z"}</t>
+        <v>0</v>
+      </c>
+      <c r="O24" s="1" t="inlineStr"/>
+      <c r="P24" s="1" t="inlineStr">
+        <is>
+          <t>{"id": 1778196950123, "fecha": "2026-06-04T16:17:37.257Z", "nombre": "Justiniano Monje Cortes", "celular": "3204666321", "tipo": "cliente", "estado": "inactivo", "etiqueta": "inactivo", "notas": "Codg. 223 - Los Cambulos II-$175mlls - Disponible. Efectivo. YA INVIRTIO.\n"}</t>
         </is>
       </c>
     </row>
     <row r="25">
-      <c r="A25" t="inlineStr">
-        <is>
-          <t>U-1779750679001688</t>
-        </is>
-      </c>
-      <c r="B25" t="inlineStr">
-        <is>
-          <t>2026-06-05T16:50:58.779Z</t>
+      <c r="A25" s="1" t="inlineStr">
+        <is>
+          <t>1777922884952</t>
+        </is>
+      </c>
+      <c r="B25" s="1" t="inlineStr">
+        <is>
+          <t>2026-05-04T19:28:04.953Z</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Iasias Chaux</t>
-        </is>
-      </c>
-      <c r="D25" t="n">
-        <v>3152445222</v>
+          <t>María Angelica</t>
+        </is>
+      </c>
+      <c r="D25" s="1" t="inlineStr">
+        <is>
+          <t>3133223758</t>
+        </is>
       </c>
       <c r="E25" t="inlineStr">
         <is>
@@ -1986,17 +2106,17 @@
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>activo</t>
-        </is>
-      </c>
-      <c r="I25" t="inlineStr">
-        <is>
-          <t>Don Isais Chaux . . El papá de Frnasua Chaux. Compra por inversión Apto  en conjunto economico $140mlls.</t>
-        </is>
-      </c>
-      <c r="J25" t="inlineStr">
-        <is>
-          <t>Tipos: Apartamento en conjunto | Precio: 83000000 - 153000000</t>
+          <t>tibio</t>
+        </is>
+      </c>
+      <c r="I25" s="1" t="inlineStr">
+        <is>
+          <t>Cliente del mcpio de Tello . Casa economica de $75 mlls con garaje.</t>
+        </is>
+      </c>
+      <c r="J25" s="1" t="inlineStr">
+        <is>
+          <t>Tipos: Casa | Precio: 0 - 159000000</t>
         </is>
       </c>
       <c r="K25" t="inlineStr">
@@ -2004,8 +2124,8 @@
           <t>Efectivo</t>
         </is>
       </c>
-      <c r="L25" t="n">
-        <v>153000000</v>
+      <c r="L25" s="2" t="n">
+        <v>159000000</v>
       </c>
       <c r="M25" t="inlineStr">
         <is>
@@ -2013,37 +2133,35 @@
         </is>
       </c>
       <c r="N25" t="n">
-        <v>11</v>
-      </c>
-      <c r="O25" t="inlineStr">
-        <is>
-          <t>2026-05-25 (11)</t>
-        </is>
-      </c>
-      <c r="P25" t="inlineStr">
-        <is>
-          <t>{"id":"U-1779750679001688","tipo":"cliente","nombre":"Iasias Chaux","celular":"3152445222","notas":"Don Isais Chaux . . El papá de Frnasua Chaux. Compra por inversión Apto  en conjunto economico $140mlls.","metodoPago":["Efectivo"],"estado":"enviando","etiqueta":"activo","filtros":{"tipoInmueble":["Apartamento en conjunto"],"rangoPrecio":[],"zona":[],"habitaciones":[],"garaje":[],"pisos":[],"ubicacion":[],"piscina":[],"cocina":[],"barrio":[],"conjunto":[],"minPrice":83000000,"maxPrice":153000000,"kmzCategory":["APTO Y APTO EN CONJUNTO 🏢","CASA EN CONJUNTO, CAMPESTRE IND Y EN CONJUNTO⛳","CASA LOTE, LOTE Y LOTE EN CONJUNTO ⛳","CASAS Y EDIFICIOS RENTABLES💲","CASAS 🏡","LOCAL, BODEGA Y OFICINA 🏪"],"buscar":""},"frecuencia":"semanal","maxPorEnvio":4,"nombreInmobiliaria":"","nombreAgente":"","propsFiltradas":["1383","1728","647","360","489","856","1369","920","844","588","548"],"propsEnviadas":["1383","1728","647","360","489","856","1369","920","844","588","548"],"proximosEnvios":[{"fecha":"2026-06-01","codigos":[],"enviado":false,"esCheck":true}],"historialEnvios":[{"fecha":"2026-05-25","codigos":["1383","1728","647","360","489","856","1369","920","844","588","548"],"totalCods":11,"tipoEnvio":"link","notas":"Envío de link catálogo"}],"visitas":[],"creadoEn":"2026-05-25T23:11:19.001Z"}</t>
+        <v>0</v>
+      </c>
+      <c r="O25" s="1" t="inlineStr"/>
+      <c r="P25" s="1" t="inlineStr">
+        <is>
+          <t>{"id": "1777922884952", "tipo": "cliente", "nombre": "María Angelica", "celular": "3133223758", "notas": "Cliente del mcpio de Tello . Casa economica de $75 mlls con garaje.", "metodoPago": ["Efectivo"], "estado": "enviando", "etiqueta": "tibio", "filtros": {"tipoInmueble": ["Casa"], "rangoPrecio": [], "zona": [], "habitaciones": [], "garaje": [], "pisos": [], "ubicacion": [], "piscina": [], "cocina": [], "barrio": [], "conjunto": [], "buscar": "", "maxPrice": 159000000}, "frecuencia": "semanal", "maxPorEnvio": 4, "nombreInmobiliaria": "", "nombreAgente": "", "propsFiltradas": ["541"], "propsEnviadas": [], "proximosEnvios": [{"fecha": "2026-05-11", "codigos": [], "enviado": false, "esCheck": true}], "historialEnvios": [], "visitas": [], "creadoEn": "2026-05-04T19:28:04.953Z", "feedback": {}}</t>
         </is>
       </c>
     </row>
     <row r="26">
-      <c r="A26" t="inlineStr">
-        <is>
-          <t>U-1780352084268612</t>
-        </is>
-      </c>
-      <c r="B26" t="inlineStr">
-        <is>
-          <t>2026-06-05T16:47:57.365Z</t>
+      <c r="A26" s="1" t="inlineStr">
+        <is>
+          <t>1777676783626</t>
+        </is>
+      </c>
+      <c r="B26" s="1" t="inlineStr">
+        <is>
+          <t>2026-06-03T15:06:47.576Z</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Andrea</t>
-        </is>
-      </c>
-      <c r="D26" t="n">
-        <v>3157094054</v>
+          <t>María Angelica Valderrama</t>
+        </is>
+      </c>
+      <c r="D26" s="1" t="inlineStr">
+        <is>
+          <t>311 2042459</t>
+        </is>
       </c>
       <c r="E26" t="inlineStr">
         <is>
@@ -2053,51 +2171,53 @@
       <c r="F26" t="inlineStr"/>
       <c r="G26" t="inlineStr">
         <is>
-          <t>proceso</t>
+          <t>inactivo</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>activo</t>
-        </is>
-      </c>
-      <c r="I26" t="inlineStr">
-        <is>
-          <t>Compra Apto en conjunto codg. 864 Bosques de Tamarindo  - Jennifer y Codg. 1669 Tierra alta C&amp;C . . Ya se solicito verificación y visita. Ha tomado la decisión de comprar Codg. 864 Bosques de Tamarindo $250 - $230 - Jennifer.</t>
-        </is>
-      </c>
-      <c r="J26" t="inlineStr"/>
+          <t>inactivo</t>
+        </is>
+      </c>
+      <c r="I26" s="1" t="inlineStr"/>
+      <c r="J26" s="1" t="inlineStr"/>
       <c r="K26" t="inlineStr"/>
       <c r="L26" t="inlineStr"/>
-      <c r="M26" t="inlineStr"/>
+      <c r="M26" t="inlineStr">
+        <is>
+          <t>manual</t>
+        </is>
+      </c>
       <c r="N26" t="n">
         <v>0</v>
       </c>
-      <c r="O26" t="inlineStr"/>
-      <c r="P26" t="inlineStr">
-        <is>
-          <t>{"id":"U-1780352084268612","fecha":"2026-06-04T23:06:06.370Z","nombre":"Andrea","celular":3157094054,"tipo":"cliente","estado":"proceso","etiqueta":"activo","notas":"Compra Apto en conjunto codg. 864 Bosques de Tamarindo  - Jennifer y Codg. 1669 Tierra alta C&amp;C . . Ya se solicito verificación y visita. Ha tomado la decisión de comprar Codg. 864 Bosques de Tamarindo $250 - $230 - Jennifer."}</t>
+      <c r="O26" s="1" t="inlineStr"/>
+      <c r="P26" s="1" t="inlineStr">
+        <is>
+          <t>{"id": 1777676783626, "fecha": "2026-06-03T15:06:47.576Z", "nombre": "María Angelica Valderrama", "celular": "311 2042459", "tipo": "cliente", "estado": "inactivo", "etiqueta": "inactivo", "notas": ""}</t>
         </is>
       </c>
     </row>
     <row r="27">
-      <c r="A27" t="inlineStr">
-        <is>
-          <t>U-1778271567218463</t>
-        </is>
-      </c>
-      <c r="B27" t="inlineStr">
-        <is>
-          <t>2026-06-05T16:50:20.388Z</t>
+      <c r="A27" s="1" t="inlineStr">
+        <is>
+          <t>U-1780347580789325</t>
+        </is>
+      </c>
+      <c r="B27" s="1" t="inlineStr">
+        <is>
+          <t>2026-06-03T16:01:32.987Z</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Hector</t>
-        </is>
-      </c>
-      <c r="D27" t="n">
-        <v>3159057825</v>
+          <t>María Mosquera</t>
+        </is>
+      </c>
+      <c r="D27" s="1" t="inlineStr">
+        <is>
+          <t>3177253538</t>
+        </is>
       </c>
       <c r="E27" t="inlineStr">
         <is>
@@ -2107,69 +2227,57 @@
       <c r="F27" t="inlineStr"/>
       <c r="G27" t="inlineStr">
         <is>
-          <t>visita</t>
+          <t>inactivo</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>activo</t>
-        </is>
-      </c>
-      <c r="I27" t="inlineStr">
-        <is>
-          <t>Solicita visita  Codg. 622  Villa Milena - $190 - Inmb. RK</t>
-        </is>
-      </c>
-      <c r="J27" t="inlineStr">
-        <is>
-          <t>Tipos: Casa | Precio: 0 - 221000000</t>
-        </is>
-      </c>
-      <c r="K27" t="inlineStr">
-        <is>
-          <t>Efectivo</t>
-        </is>
-      </c>
-      <c r="L27" t="n">
-        <v>221000000</v>
-      </c>
+          <t>inactivo</t>
+        </is>
+      </c>
+      <c r="I27" s="1" t="inlineStr">
+        <is>
+          <t>Compra -casa norte-4 hab-cred-carta pre. C&amp;C ha manifestado que el cliente ya lo tiene ella.</t>
+        </is>
+      </c>
+      <c r="J27" s="1" t="inlineStr"/>
+      <c r="K27" t="inlineStr"/>
+      <c r="L27" t="inlineStr"/>
       <c r="M27" t="inlineStr">
         <is>
-          <t>semanal</t>
+          <t>manual</t>
         </is>
       </c>
       <c r="N27" t="n">
-        <v>39</v>
-      </c>
-      <c r="O27" t="inlineStr">
-        <is>
-          <t>2026-05-10 (39)</t>
-        </is>
-      </c>
-      <c r="P27" t="inlineStr">
-        <is>
-          <t>{"id":"U-1778271567218463","tipo":"cliente","nombre":"Hector","celular":"3159057825","notas":"Solicita visita  Codg. 622  Villa Milena - $190 - Inmb. RK","metodoPago":["Efectivo"],"estado":"visita","etiqueta":"activo","filtros":{"tipoInmueble":["Casa"],"rangoPrecio":[],"zona":[],"habitaciones":[],"garaje":[],"pisos":[],"ubicacion":[],"piscina":[],"cocina":[],"barrio":[],"conjunto":[],"buscar":"","maxPrice":221000000},"frecuencia":"semanal","maxPorEnvio":4,"nombreInmobiliaria":"","nombreAgente":"","propsFiltradas":["828","486","1667","609","266","713","100","933","078","622","106","562","496","569","339","345","511","288","262","1242","1010","592","690","552","607","798","1003","625","1285","282","716","706","939","5224","991","514","325","766","541"],"propsEnviadas":["828","486","1667","609","266","713","100","933","078","622","106","562","496","569","339","345","511","288","262","1242","1010","592","690","552","607","798","1003","625","1285","282","716","706","939","5224","991","514","325","766","541"],"proximosEnvios":[{"fecha":"2026-05-17","codigos":[],"enviado":false,"esCheck":true}],"historialEnvios":[{"fecha":"2026-05-10","codigos":["828","486","1667","609","266","713","100","933","078","622","106","562","496","569","339","345","511","288","262","1242","1010","592","690","552","607","798","1003","625","1285","282","716","706","939","5224","991","514","325","766","541"],"totalCods":39,"tipoEnvio":"silencioso","notas":"Filtros actualizados (propiedades marcadas como vistas sin enviar WhatsApp)"}],"visitas":[{"id":"1777996776453","codigo":"622","fecha":"2026-05-09","hora":"","estado":"agendada","oferto":"no","oferta":"","notas":"Inmueble de Rustika. Desocupada. Propietario viajando. hasta el sábado en la tarde  la visita. No se ha coordinado la hora.","cliente":"Hector","celular":"3159057825","inmobiliaria":""}],"creadoEn":"2026-05-04T11:45:19.556Z"}</t>
+        <v>0</v>
+      </c>
+      <c r="O27" s="1" t="inlineStr"/>
+      <c r="P27" s="1" t="inlineStr">
+        <is>
+          <t>{"id": "U-1780347580789325", "fecha": "2026-06-03T16:01:32.987Z", "nombre": "María Mosquera", "celular": "3177253538", "tipo": "cliente", "estado": "inactivo", "etiqueta": "inactivo", "notas": "Compra -casa norte-4 hab-cred-carta pre. C&amp;C ha manifestado que el cliente ya lo tiene ella."}</t>
         </is>
       </c>
     </row>
     <row r="28">
-      <c r="A28" t="inlineStr">
-        <is>
-          <t>U-1778271567218351</t>
-        </is>
-      </c>
-      <c r="B28" t="inlineStr">
-        <is>
-          <t>2026-06-05T16:48:53.932Z</t>
+      <c r="A28" s="1" t="inlineStr">
+        <is>
+          <t>U-1779061841119543</t>
+        </is>
+      </c>
+      <c r="B28" s="1" t="inlineStr">
+        <is>
+          <t>2026-05-17T23:50:41.120Z</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Bladimir</t>
-        </is>
-      </c>
-      <c r="D28" t="n">
-        <v>3162653365</v>
+          <t>María Nohora Rojas</t>
+        </is>
+      </c>
+      <c r="D28" s="1" t="inlineStr">
+        <is>
+          <t>3124797922</t>
+        </is>
       </c>
       <c r="E28" t="inlineStr">
         <is>
@@ -2179,22 +2287,22 @@
       <c r="F28" t="inlineStr"/>
       <c r="G28" t="inlineStr">
         <is>
-          <t>visita</t>
+          <t>enviando</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>activo</t>
-        </is>
-      </c>
-      <c r="I28" t="inlineStr">
-        <is>
-          <t>Busca : Casa en conjunto con 4 ha bitaciones.  Presupuesto $350 mlls.</t>
-        </is>
-      </c>
-      <c r="J28" t="inlineStr">
-        <is>
-          <t>Tipos: Casa en conjunto, Casa campestre en conjunto | Precio: 200000000 - 404000000 | Hab: 4, 6</t>
+          <t>tibio</t>
+        </is>
+      </c>
+      <c r="I28" s="1" t="inlineStr">
+        <is>
+          <t>Compra Apto conjunto. Yessica solicita para la tía Ma. Nohora.</t>
+        </is>
+      </c>
+      <c r="J28" s="1" t="inlineStr">
+        <is>
+          <t>Tipos: Apartamento en conjunto, Apartamento | Zonas: Norte, Centro | Precio: 161000000 - 336000000</t>
         </is>
       </c>
       <c r="K28" t="inlineStr">
@@ -2202,8 +2310,8 @@
           <t>Efectivo, Crédito</t>
         </is>
       </c>
-      <c r="L28" t="n">
-        <v>404000000</v>
+      <c r="L28" s="2" t="n">
+        <v>336000000</v>
       </c>
       <c r="M28" t="inlineStr">
         <is>
@@ -2211,37 +2319,39 @@
         </is>
       </c>
       <c r="N28" t="n">
-        <v>6</v>
-      </c>
-      <c r="O28" t="inlineStr">
-        <is>
-          <t>2026-05-06 (6)</t>
-        </is>
-      </c>
-      <c r="P28" t="inlineStr">
-        <is>
-          <t>{"id":"U-1778271567218351","tipo":"cliente","nombre":"Bladimir","celular":"3162653365","notas":"Busca : Casa en conjunto con 4 ha bitaciones.  Presupuesto $350 mlls.","metodoPago":["Efectivo","Crédito"],"estado":"visita","etiqueta":"activo","filtros":{"tipoInmueble":["Casa en conjunto","Casa campestre en conjunto"],"rangoPrecio":[],"zona":[],"habitaciones":["4","6"],"garaje":[],"pisos":[],"ubicacion":[],"piscina":[],"cocina":[],"barrio":[],"conjunto":[],"buscar":"","maxPrice":404000000,"minPrice":200000000},"frecuencia":"semanal","maxPorEnvio":4,"nombreInmobiliaria":"","nombreAgente":"","propsFiltradas":["1307","1311","1714","1062","636","111"],"propsEnviadas":["1307","1311","1714","1062","636","111"],"proximosEnvios":[{"fecha":"2026-05-13","codigos":[],"enviado":false,"esCheck":true}],"historialEnvios":[{"fecha":"2026-05-06","codigos":["1307","1311","1714","1062","636","111"],"totalCods":6,"tipoEnvio":"silencioso","notas":"Filtros actualizados (propiedades marcadas como vistas sin enviar WhatsApp)"}],"visitas":[{"id":"1778191741569","codigo":"1311","fecha":"2026-05-08","hora":"17:00","estado":"realizada","oferto":"no","oferta":"","notas":"Inmobiliaria Jovel. Disponible, Con Terceria.  Conj. Res. Yahaira. Carrera 18 No. 45-04. Pendiente reconfirmar.","cliente":"Bladimir","celular":"3162653365","inmobiliaria":""}],"creadoEn":"2026-05-04T23:00:04.712Z"}</t>
+        <v>18</v>
+      </c>
+      <c r="O28" s="1" t="inlineStr">
+        <is>
+          <t>2026-05-17 (18)</t>
+        </is>
+      </c>
+      <c r="P28" s="1" t="inlineStr">
+        <is>
+          <t>{"id": "U-1779061841119543", "tipo": "cliente", "nombre": "María Nohora Rojas", "celular": "3124797922", "notas": "Compra Apto conjunto. Yessica solicita para la tía Ma. Nohora.", "metodoPago": ["Efectivo", "Crédito"], "estado": "enviando", "etiqueta": "tibio", "filtros": {"tipoInmueble": ["Apartamento en conjunto", "Apartamento"], "rangoPrecio": [], "zona": ["Norte", "Centro"], "habitaciones": [], "garaje": [], "pisos": [], "ubicacion": [], "piscina": [], "cocina": [], "barrio": [], "conjunto": [], "minPrice": 161000000, "maxPrice": 336000000, "kmzCategory": ["APTO Y APTO EN CONJUNTO 🏢", "CASA EN CONJUNTO, CAMPESTRE IND Y EN CONJUNTO⛳", "CASA LOTE, LOTE Y LOTE EN CONJUNTO ⛳", "CASAS Y EDIFICIOS RENTABLES💲", "CASAS 🏡", "LOCAL, BODEGA Y OFICINA 🏪"], "buscar": ""}, "frecuencia": "semanal", "maxPorEnvio": 4, "nombreInmobiliaria": "", "nombreAgente": "", "propsFiltradas": ["1781", "228", "215", "1549", "662", "1382", "1721", "1358", "4552", "185", "726", "1690", "309", "1360", "834", "067", "1316", "019", "373"], "propsEnviadas": ["1781", "228", "215", "1549", "662", "1382", "1721", "1358", "4552", "726", "1690", "309", "834", "067", "1316", "019", "373", "1360"], "proximosEnvios": [{"fecha": "2026-05-24", "codigos": [], "enviado": false, "esCheck": true}], "historialEnvios": [{"fecha": "2026-05-17", "codigos": ["1781", "228", "215", "1549", "662", "1382", "1721", "1358", "4552", "726", "1690", "309", "834", "067", "1316", "019", "373", "1360"], "totalCods": 18, "tipoEnvio": "link", "notas": "Envío de link catálogo"}], "visitas": [{"id": "1779119510834", "codigo": "662", "fecha": "2026-05-18", "hora": "", "estado": "agendada", "oferto": "no", "oferta": "", "notas": "", "cliente": "María Nohora Rojas", "celular": "3124797922", "inmobiliaria": ""}], "creadoEn": "2026-05-17T23:50:41.120Z"}</t>
         </is>
       </c>
     </row>
     <row r="29">
-      <c r="A29" t="inlineStr">
-        <is>
-          <t>U-1779050115953215</t>
-        </is>
-      </c>
-      <c r="B29" t="inlineStr">
-        <is>
-          <t>2026-06-05T16:51:33.342Z</t>
+      <c r="A29" s="1" t="inlineStr">
+        <is>
+          <t>U-1780355426553551</t>
+        </is>
+      </c>
+      <c r="B29" s="1" t="inlineStr">
+        <is>
+          <t>2026-06-03T15:44:18.888Z</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Jorge Enrique Ossa Hernandez</t>
-        </is>
-      </c>
-      <c r="D29" t="n">
-        <v>3164254862</v>
+          <t>María Sildana Arango</t>
+        </is>
+      </c>
+      <c r="D29" s="1" t="inlineStr">
+        <is>
+          <t>3248276336</t>
+        </is>
       </c>
       <c r="E29" t="inlineStr">
         <is>
@@ -2251,67 +2361,57 @@
       <c r="F29" t="inlineStr"/>
       <c r="G29" t="inlineStr">
         <is>
-          <t>enviando</t>
+          <t>inactivo</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>tibio</t>
-        </is>
-      </c>
-      <c r="I29" t="inlineStr">
-        <is>
-          <t>Casa o casa lote - Centro - $200mlls</t>
-        </is>
-      </c>
-      <c r="J29" t="inlineStr">
-        <is>
-          <t>Tipos: Casa, Casa lote | Zonas: Centro | Precio: 159000000 - 326000000</t>
-        </is>
-      </c>
-      <c r="K29" t="inlineStr">
-        <is>
-          <t>Efectivo</t>
-        </is>
-      </c>
-      <c r="L29" t="n">
-        <v>326000000</v>
-      </c>
+          <t>inactivo</t>
+        </is>
+      </c>
+      <c r="I29" s="1" t="inlineStr">
+        <is>
+          <t>Interesada Codg, 625 Luis Carlos Galán - $155mll-Jennifer. Verificando la disponibilidad y Solicito visita. Inmueble NO DISPONIBLE. Desea en este sector.</t>
+        </is>
+      </c>
+      <c r="J29" s="1" t="inlineStr"/>
+      <c r="K29" t="inlineStr"/>
+      <c r="L29" t="inlineStr"/>
       <c r="M29" t="inlineStr">
         <is>
-          <t>semanal</t>
+          <t>manual</t>
         </is>
       </c>
       <c r="N29" t="n">
-        <v>4</v>
-      </c>
-      <c r="O29" t="inlineStr">
-        <is>
-          <t>2026-05-17 (4)</t>
-        </is>
-      </c>
-      <c r="P29" t="inlineStr">
-        <is>
-          <t>{"id":"U-1779050115953215","tipo":"cliente","nombre":"Jorge Enrique Ossa Hernandez","celular":"3164254862","notas":"Casa o casa lote - Centro - $200mlls","metodoPago":["Efectivo"],"estado":"enviando","etiqueta":"tibio","filtros":{"tipoInmueble":["Casa","Casa lote"],"rangoPrecio":[],"zona":["Centro"],"habitaciones":[],"garaje":[],"pisos":[],"ubicacion":[],"piscina":[],"cocina":[],"barrio":[],"conjunto":[],"minPrice":159000000,"maxPrice":326000000,"kmzCategory":[],"buscar":""},"frecuencia":"semanal","maxPorEnvio":4,"nombreInmobiliaria":"","nombreAgente":"","propsFiltradas":["1344","1140","079","486","100"],"propsEnviadas":["1344","1140","079","100"],"proximosEnvios":[{"fecha":"2026-05-24","codigos":[],"enviado":false,"esCheck":true}],"historialEnvios":[{"fecha":"2026-05-17","codigos":["1344","1140","079","100"],"totalCods":4,"tipoEnvio":"link","notas":"Envío de link catálogo"}],"visitas":[],"creadoEn":"2026-05-17T20:35:15.953Z"}</t>
+        <v>0</v>
+      </c>
+      <c r="O29" s="1" t="inlineStr"/>
+      <c r="P29" s="1" t="inlineStr">
+        <is>
+          <t>{"id": "U-1780355426553551", "fecha": "2026-06-03T15:44:18.888Z", "nombre": "María Sildana Arango", "celular": "3248276336", "tipo": "cliente", "estado": "inactivo", "etiqueta": "inactivo", "notas": "Interesada Codg, 625 Luis Carlos Galán - $155mll-Jennifer. Verificando la disponibilidad y Solicito visita. Inmueble NO DISPONIBLE. Desea en este sector."}</t>
         </is>
       </c>
     </row>
     <row r="30">
-      <c r="A30" t="n">
-        <v>1777767356975</v>
-      </c>
-      <c r="B30" t="inlineStr">
-        <is>
-          <t>2026-06-05T16:51:30.614Z</t>
+      <c r="A30" s="1" t="inlineStr">
+        <is>
+          <t>U-1778683524865214</t>
+        </is>
+      </c>
+      <c r="B30" s="1" t="inlineStr">
+        <is>
+          <t>2026-05-13T14:45:24.869Z</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Jessica Martinez</t>
-        </is>
-      </c>
-      <c r="D30" t="n">
-        <v>3166491597</v>
+          <t>Martha Cecilia Medina</t>
+        </is>
+      </c>
+      <c r="D30" s="1" t="inlineStr">
+        <is>
+          <t>3106186681</t>
+        </is>
       </c>
       <c r="E30" t="inlineStr">
         <is>
@@ -2329,19 +2429,23 @@
           <t>tibio</t>
         </is>
       </c>
-      <c r="I30" t="inlineStr"/>
-      <c r="J30" t="inlineStr">
-        <is>
-          <t>Tipos: Casa en conjunto | Zonas: Norte, Oriente | Precio: 0 - 253000000</t>
+      <c r="I30" s="1" t="inlineStr">
+        <is>
+          <t>Compra casa de un piso, cerca a la iglesia Sta. María - Alamos norte. Precio $120. Se envio propuestas de casa y Aptos en cj hasta $209 mlls. Proceso INICIAL crédito.</t>
+        </is>
+      </c>
+      <c r="J30" s="1" t="inlineStr">
+        <is>
+          <t>Tipos: Casa, Apartamento en conjunto | Zonas: Norte | Precio: 0 - 209000000</t>
         </is>
       </c>
       <c r="K30" t="inlineStr">
         <is>
-          <t>Efectivo</t>
-        </is>
-      </c>
-      <c r="L30" t="n">
-        <v>253000000</v>
+          <t>Crédito</t>
+        </is>
+      </c>
+      <c r="L30" s="2" t="n">
+        <v>209000000</v>
       </c>
       <c r="M30" t="inlineStr">
         <is>
@@ -2349,37 +2453,39 @@
         </is>
       </c>
       <c r="N30" t="n">
-        <v>1</v>
-      </c>
-      <c r="O30" t="inlineStr">
-        <is>
-          <t>2026-05-03 (2)</t>
-        </is>
-      </c>
-      <c r="P30" t="inlineStr">
-        <is>
-          <t>{"id":"1777767356975","tipo":"cliente","nombre":"Jessica Martinez","celular":"3166491597","notas":"","metodoPago":["Efectivo"],"estado":"enviando","etiqueta":"tibio","filtros":{"tipoInmueble":["Casa en conjunto"],"rangoPrecio":[],"zona":["Norte","Oriente"],"habitaciones":[],"garaje":[],"pisos":[],"ubicacion":[],"piscina":[],"cocina":[],"barrio":[],"conjunto":[],"buscar":"","maxPrice":253000000},"frecuencia":"semanal","maxPorEnvio":4,"nombreInmobiliaria":"","nombreAgente":"","propsFiltradas":["",""],"propsEnviadas":[""],"proximosEnvios":[{"fecha":"2026-05-10","codigos":[],"enviado":false,"esCheck":true}],"historialEnvios":[{"fecha":"2026-05-03","codigos":["",""],"totalCods":2,"tipoEnvio":"link","notas":"Envío de link catálogo"}],"visitas":[],"creadoEn":"2026-05-03T00:15:56.979Z","feedback":{}}</t>
+        <v>22</v>
+      </c>
+      <c r="O30" s="1" t="inlineStr">
+        <is>
+          <t>2026-05-13 (22) | 2026-05-13 (22)</t>
+        </is>
+      </c>
+      <c r="P30" s="1" t="inlineStr">
+        <is>
+          <t>{"id": "U-1778683524865214", "tipo": "cliente", "nombre": "Martha Cecilia Medina", "celular": "3106186681", "notas": "Compra casa de un piso, cerca a la iglesia Sta. María - Alamos norte. Precio $120. Se envio propuestas de casa y Aptos en cj hasta $209 mlls. Proceso INICIAL crédito.", "metodoPago": ["Crédito"], "estado": "enviando", "etiqueta": "tibio", "filtros": {"tipoInmueble": ["Casa", "Apartamento en conjunto"], "rangoPrecio": [], "zona": ["Norte"], "habitaciones": [], "garaje": [], "pisos": [], "ubicacion": [], "piscina": [], "cocina": [], "barrio": [], "conjunto": [], "minPrice": null, "maxPrice": 209000000, "kmzCategory": [], "buscar": "", "mapActive": false}, "frecuencia": "semanal", "maxPorEnvio": 4, "nombreInmobiliaria": "", "nombreAgente": "", "propsFiltradas": ["1721", "933", "713", "106", "078", "622", "496", "662", "511", "1549", "262", "1781", "215", "592", "105", "625", "1728", "282", "1383", "920", "766", "541"], "propsEnviadas": ["1721", "078", "622", "496", "1383", "933", "713", "106", "662", "511", "1549", "262", "1781", "215", "592", "105", "625", "1728", "282", "920", "766", "541"], "proximosEnvios": [{"fecha": "2026-05-20", "codigos": [], "enviado": false, "esCheck": true}], "historialEnvios": [{"fecha": "2026-05-13", "codigos": ["1721", "933", "713", "106", "078", "622", "496", "662", "511", "1549", "262", "1781", "215", "592", "105", "625", "1728", "282", "1383", "920", "766", "541"], "totalCods": 22, "tipoEnvio": "link", "notas": "Envío de link catálogo"}, {"fecha": "2026-05-13", "codigos": ["1721", "933", "713", "106", "078", "622", "496", "662", "511", "1549", "262", "1781", "215", "592", "105", "625", "1728", "282", "1383", "920", "766", "541"], "totalCods": 22, "tipoEnvio": "silencioso", "notas": "Filtros actualizados (propiedades marcadas como vistas sin enviar WhatsApp)"}], "visitas": [], "creadoEn": "2026-05-13T14:45:24.869Z"}</t>
         </is>
       </c>
     </row>
     <row r="31">
-      <c r="A31" t="inlineStr">
-        <is>
-          <t>U-1778702372993384</t>
-        </is>
-      </c>
-      <c r="B31" t="inlineStr">
-        <is>
-          <t>2026-06-05T16:49:55.216Z</t>
+      <c r="A31" s="1" t="inlineStr">
+        <is>
+          <t>U-1780001088409490</t>
+        </is>
+      </c>
+      <c r="B31" s="1" t="inlineStr">
+        <is>
+          <t>2026-05-28T20:44:48.411Z</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Diego Tello</t>
-        </is>
-      </c>
-      <c r="D31" t="n">
-        <v>3168049568</v>
+          <t>Martha Cubillos</t>
+        </is>
+      </c>
+      <c r="D31" s="1" t="inlineStr">
+        <is>
+          <t>3209029142</t>
+        </is>
       </c>
       <c r="E31" t="inlineStr">
         <is>
@@ -2389,51 +2495,65 @@
       <c r="F31" t="inlineStr"/>
       <c r="G31" t="inlineStr">
         <is>
-          <t>enviando</t>
+          <t>visita</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>tibio</t>
-        </is>
-      </c>
-      <c r="I31" t="inlineStr">
-        <is>
-          <t>Compra casa rentable para el hijo EEUU . $400 mlls. No sur. AUN BUSCANDO LA CASA.</t>
-        </is>
-      </c>
-      <c r="J31" t="inlineStr"/>
-      <c r="K31" t="inlineStr"/>
+          <t>activo</t>
+        </is>
+      </c>
+      <c r="I31" s="1" t="inlineStr">
+        <is>
+          <t>Compra casa $200 norte</t>
+        </is>
+      </c>
+      <c r="J31" s="1" t="inlineStr"/>
+      <c r="K31" t="inlineStr">
+        <is>
+          <t>Efectivo</t>
+        </is>
+      </c>
       <c r="L31" t="inlineStr"/>
-      <c r="M31" t="inlineStr"/>
+      <c r="M31" t="inlineStr">
+        <is>
+          <t>semanal</t>
+        </is>
+      </c>
       <c r="N31" t="n">
-        <v>0</v>
-      </c>
-      <c r="O31" t="inlineStr"/>
-      <c r="P31" t="inlineStr">
-        <is>
-          <t>{"id":"U-1778702372993384","fecha":"2026-06-04T23:08:17.369Z","nombre":"Diego Tello","celular":3168049568,"tipo":"cliente","estado":"enviando","etiqueta":"tibio","notas":"Compra casa rentable para el hijo EEUU . $400 mlls. No sur. AUN BUSCANDO LA CASA."}</t>
+        <v>1</v>
+      </c>
+      <c r="O31" s="1" t="inlineStr">
+        <is>
+          <t>2026-05-28 (1)</t>
+        </is>
+      </c>
+      <c r="P31" s="1" t="inlineStr">
+        <is>
+          <t>{"id": "U-1780001088409490", "tipo": "cliente", "nombre": "Martha Cubillos", "celular": "3209029142", "notas": "Compra casa $200 norte", "metodoPago": ["Efectivo"], "estado": "visita", "etiqueta": "activo", "filtros": {"tipoInmueble": [], "rangoPrecio": [], "zona": [], "habitaciones": [], "garaje": [], "pisos": [], "ubicacion": [], "piscina": [], "cocina": [], "barrio": [], "conjunto": [], "minPrice": null, "maxPrice": null, "kmzCategory": ["APTO Y APTO EN CONJUNTO 🏢", "CASA EN CONJUNTO, CAMPESTRE IND Y EN CONJUNTO⛳", "CASA LOTE, LOTE Y LOTE EN CONJUNTO ⛳", "CASAS Y EDIFICIOS RENTABLES💲", "CASAS 🏡", "LOCAL, BODEGA Y OFICINA 🏪"], "buscar": "078"}, "frecuencia": "semanal", "maxPorEnvio": 4, "nombreInmobiliaria": "", "nombreAgente": "", "propsFiltradas": ["781", "478", "678", "698", "1778", "1785", "978", "1678", "256", "1378", "422", "1786", "878", "933", "078", "1781", "690", "991", "849", "788", "1644", "783"], "propsEnviadas": ["078"], "proximosEnvios": [{"fecha": "2026-06-04", "codigos": [], "enviado": false, "esCheck": true}], "historialEnvios": [{"fecha": "2026-05-28", "codigos": ["078"], "totalCods": 1, "tipoEnvio": "individual", "notas": "Envío selección individual"}], "visitas": [], "creadoEn": "2026-05-28T20:44:48.411Z"}</t>
         </is>
       </c>
     </row>
     <row r="32">
-      <c r="A32" t="inlineStr">
-        <is>
-          <t>U-1778622246028103</t>
-        </is>
-      </c>
-      <c r="B32" t="inlineStr">
-        <is>
-          <t>2026-06-04T15:44:58.363Z</t>
+      <c r="A32" s="1" t="inlineStr">
+        <is>
+          <t>U-1778884294544703</t>
+        </is>
+      </c>
+      <c r="B32" s="1" t="inlineStr">
+        <is>
+          <t>2026-05-15T22:31:34.544Z</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Roger Martínez .</t>
-        </is>
-      </c>
-      <c r="D32" t="n">
-        <v>3175179466</v>
+          <t>Mauricio Garzón y Yuly Solorzano</t>
+        </is>
+      </c>
+      <c r="D32" s="1" t="inlineStr">
+        <is>
+          <t>3113316364</t>
+        </is>
       </c>
       <c r="E32" t="inlineStr">
         <is>
@@ -2451,43 +2571,61 @@
           <t>inactivo</t>
         </is>
       </c>
-      <c r="I32" t="inlineStr">
-        <is>
-          <t>Inf 038  -  07 9 - 591 - YA INVIRTIO.</t>
-        </is>
-      </c>
-      <c r="J32" t="inlineStr"/>
-      <c r="K32" t="inlineStr"/>
+      <c r="I32" s="1" t="inlineStr">
+        <is>
+          <t>Compra casa lote - Presupuesto $300 mlls - Interesado Codg. 220.</t>
+        </is>
+      </c>
+      <c r="J32" s="1" t="inlineStr">
+        <is>
+          <t>Tipos: Casa lote | Zonas: Centro, Norte</t>
+        </is>
+      </c>
+      <c r="K32" t="inlineStr">
+        <is>
+          <t>Efectivo, Crédito</t>
+        </is>
+      </c>
       <c r="L32" t="inlineStr"/>
-      <c r="M32" t="inlineStr"/>
+      <c r="M32" t="inlineStr">
+        <is>
+          <t>semanal</t>
+        </is>
+      </c>
       <c r="N32" t="n">
-        <v>0</v>
-      </c>
-      <c r="O32" t="inlineStr"/>
-      <c r="P32" t="inlineStr">
-        <is>
-          <t>{"id":"U-1778622246028103","fecha":"2026-06-04T15:38:28.622Z","nombre":"Roger Martínez .","celular":3175179466,"tipo":"cliente","estado":"inactivo","etiqueta":"inactivo","notas":"Inf 038  -  07 9 - 591 - YA INVIRTIO.","fromCloud":true}</t>
+        <v>2</v>
+      </c>
+      <c r="O32" s="1" t="inlineStr">
+        <is>
+          <t>2026-05-15 (2)</t>
+        </is>
+      </c>
+      <c r="P32" s="1" t="inlineStr">
+        <is>
+          <t>{"id": "U-1778884294544703", "tipo": "cliente", "nombre": "Mauricio Garzón y Yuly Solorzano", "celular": "3113316364", "notas": "Compra casa lote - Presupuesto $300 mlls - Interesado Codg. 220.", "metodoPago": ["Efectivo", "Crédito"], "estado": "inactivo", "etiqueta": "inactivo", "filtros": {"tipoInmueble": ["Casa lote"], "rangoPrecio": [], "zona": ["Centro", "Norte"], "habitaciones": [], "garaje": [], "pisos": [], "ubicacion": [], "piscina": [], "cocina": [], "barrio": [], "conjunto": [], "minPrice": null, "maxPrice": null, "kmzCategory": [], "buscar": "", "mapActive": false}, "frecuencia": "semanal", "maxPorEnvio": 4, "nombreInmobiliaria": "", "nombreAgente": "", "propsFiltradas": ["013", "220", "079", "1268", "738"], "propsEnviadas": ["220", "079"], "proximosEnvios": [{"fecha": "2026-05-22", "codigos": [], "enviado": false, "esCheck": true}], "historialEnvios": [{"fecha": "2026-05-15", "codigos": ["220", "079"], "totalCods": 2, "tipoEnvio": "link", "notas": "Envío de link catálogo"}], "visitas": [], "creadoEn": "2026-05-15T22:31:34.544Z", "feedback": {}}</t>
         </is>
       </c>
     </row>
     <row r="33">
-      <c r="A33" t="inlineStr">
-        <is>
-          <t>U-1780347580789325</t>
-        </is>
-      </c>
-      <c r="B33" t="inlineStr">
-        <is>
-          <t>2026-06-05T16:51:53.745Z</t>
+      <c r="A33" s="1" t="inlineStr">
+        <is>
+          <t>1777896083201</t>
+        </is>
+      </c>
+      <c r="B33" s="1" t="inlineStr">
+        <is>
+          <t>2026-06-03T13:04:35.970Z</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>María Mosquera</t>
-        </is>
-      </c>
-      <c r="D33" t="n">
-        <v>3177253538</v>
+          <t>Mercy Calderon Perdomo</t>
+        </is>
+      </c>
+      <c r="D33" s="1" t="inlineStr">
+        <is>
+          <t>3186345106</t>
+        </is>
       </c>
       <c r="E33" t="inlineStr">
         <is>
@@ -2505,52 +2643,56 @@
           <t>inactivo</t>
         </is>
       </c>
-      <c r="I33" t="inlineStr">
-        <is>
-          <t>Compra -casa norte-4 hab-cred-carta pre. C&amp;C ha manifestado que el cliente  ya lo tiene ella.</t>
-        </is>
-      </c>
-      <c r="J33" t="inlineStr"/>
+      <c r="I33" s="1" t="inlineStr">
+        <is>
+          <t>Codg. 541 - Praderas del Norte - $95 - Inmb. Primav - Solicita visita del 4-10 Mayo.</t>
+        </is>
+      </c>
+      <c r="J33" s="1" t="inlineStr"/>
       <c r="K33" t="inlineStr"/>
       <c r="L33" t="inlineStr"/>
-      <c r="M33" t="inlineStr"/>
+      <c r="M33" t="inlineStr">
+        <is>
+          <t>manual</t>
+        </is>
+      </c>
       <c r="N33" t="n">
         <v>0</v>
       </c>
-      <c r="O33" t="inlineStr"/>
-      <c r="P33" t="inlineStr">
-        <is>
-          <t>{"id":"U-1780347580789325","fecha":"2026-06-03T16:01:32.987Z","nombre":"María Mosquera","celular":3177253538,"tipo":"cliente","estado":"inactivo","etiqueta":"inactivo","notas":"Compra -casa norte-4 hab-cred-carta pre. C&amp;C ha manifestado que el cliente  ya lo tiene ella."}</t>
+      <c r="O33" s="1" t="inlineStr"/>
+      <c r="P33" s="1" t="inlineStr">
+        <is>
+          <t>{"id": 1777896083201, "fecha": "2026-06-03T13:04:35.970Z", "nombre": "Mercy Calderon Perdomo", "celular": "3186345106", "tipo": "cliente", "estado": "inactivo", "etiqueta": "inactivo", "notas": "Codg. 541 - Praderas del Norte - $95 - Inmb. Primav - Solicita visita del 4-10 Mayo."}</t>
         </is>
       </c>
     </row>
     <row r="34">
-      <c r="A34" t="n">
-        <v>1777992799064</v>
-      </c>
-      <c r="B34" t="inlineStr">
-        <is>
-          <t>2026-06-05T16:49:32.499Z</t>
+      <c r="A34" s="1" t="inlineStr">
+        <is>
+          <t>1777895403747</t>
+        </is>
+      </c>
+      <c r="B34" s="1" t="inlineStr">
+        <is>
+          <t>2026-06-03T13:30:40.811Z</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Comis. Jauqeline</t>
-        </is>
-      </c>
-      <c r="D34" t="n">
-        <v>3182198358</v>
+          <t>Mónica Ramírez</t>
+        </is>
+      </c>
+      <c r="D34" s="1" t="inlineStr">
+        <is>
+          <t>3105635811</t>
+        </is>
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>inmobiliaria</t>
-        </is>
-      </c>
-      <c r="F34" t="inlineStr">
-        <is>
-          <t>Comis. Jaqueline</t>
-        </is>
-      </c>
+          <t>cliente</t>
+        </is>
+      </c>
+      <c r="F34" t="inlineStr"/>
       <c r="G34" t="inlineStr">
         <is>
           <t>inactivo</t>
@@ -2561,55 +2703,49 @@
           <t>inactivo</t>
         </is>
       </c>
-      <c r="I34" t="inlineStr">
-        <is>
-          <t>Codg. 223 CR. Los Cambulos -  Disponible. Visita hoy martes 2:30 pm. Don Ignacio notificado.</t>
-        </is>
-      </c>
-      <c r="J34" t="inlineStr">
-        <is>
-          <t>Precio: 0 - 403000000</t>
-        </is>
-      </c>
-      <c r="K34" t="inlineStr">
-        <is>
-          <t>Efectivo, Crédito</t>
-        </is>
-      </c>
-      <c r="L34" t="n">
-        <v>403000000</v>
-      </c>
+      <c r="I34" s="1" t="inlineStr">
+        <is>
+          <t>Codg. 221 - 4170 - Solicita visita - inmueble en obra. cita del 4 al 10 mayo.</t>
+        </is>
+      </c>
+      <c r="J34" s="1" t="inlineStr"/>
+      <c r="K34" t="inlineStr"/>
+      <c r="L34" t="inlineStr"/>
       <c r="M34" t="inlineStr">
         <is>
-          <t>semanal</t>
+          <t>manual</t>
         </is>
       </c>
       <c r="N34" t="n">
         <v>0</v>
       </c>
-      <c r="O34" t="inlineStr"/>
-      <c r="P34" t="inlineStr">
-        <is>
-          <t>{"id":"1777992799064","tipo":"inmobiliaria","nombre":"Comis. Jauqeline","celular":"3182198358","notas":"Codg. 223 CR. Los Cambulos -  Disponible. Visita hoy martes 2:30 pm. Don Ignacio notificado.","metodoPago":["Efectivo","Crédito"],"estado":"inactivo","etiqueta":"inactivo","filtros":{"tipoInmueble":[],"rangoPrecio":[],"zona":[],"habitaciones":[],"garaje":[],"pisos":[],"ubicacion":[],"piscina":[],"cocina":[],"barrio":[],"conjunto":[],"buscar":"","maxPrice":403000000},"frecuencia":"semanal","maxPorEnvio":4,"nombreInmobiliaria":"Comis. Jaqueline","nombreAgente":"3182198358","propsFiltradas":["016","1187","541","1744","464","642","837","844","588","779","823","1036","1090","739","723","1644","693","783","143","1231","1464","1646","1647","167"],"propsEnviadas":[],"proximosEnvios":[{"fecha":"2026-05-12","codigos":[],"enviado":false,"esCheck":true}],"historialEnvios":[],"visitas":[],"creadoEn":"2026-05-05T14:53:19.064Z","feedback":{}}</t>
+      <c r="O34" s="1" t="inlineStr"/>
+      <c r="P34" s="1" t="inlineStr">
+        <is>
+          <t>{"id": 1777895403747, "fecha": "2026-06-03T13:30:40.811Z", "nombre": "Mónica Ramírez", "celular": "3105635811", "tipo": "cliente", "estado": "inactivo", "etiqueta": "inactivo", "notas": "Codg. 221 - 4170 - Solicita visita - inmueble en obra. cita del 4 al 10 mayo."}</t>
         </is>
       </c>
     </row>
     <row r="35">
-      <c r="A35" t="n">
-        <v>1777896083201</v>
-      </c>
-      <c r="B35" t="inlineStr">
-        <is>
-          <t>2026-06-05T16:52:30.361Z</t>
+      <c r="A35" s="1" t="inlineStr">
+        <is>
+          <t>U-1780093548365515</t>
+        </is>
+      </c>
+      <c r="B35" s="1" t="inlineStr">
+        <is>
+          <t>2026-05-29T22:25:48.366Z</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Mercy Calderon Perdomo</t>
-        </is>
-      </c>
-      <c r="D35" t="n">
-        <v>3186345106</v>
+          <t>Natalia Cerquera</t>
+        </is>
+      </c>
+      <c r="D35" s="1" t="inlineStr">
+        <is>
+          <t>3102739529</t>
+        </is>
       </c>
       <c r="E35" t="inlineStr">
         <is>
@@ -2619,51 +2755,71 @@
       <c r="F35" t="inlineStr"/>
       <c r="G35" t="inlineStr">
         <is>
-          <t>inactivo</t>
+          <t>enviando</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>inactivo</t>
-        </is>
-      </c>
-      <c r="I35" t="inlineStr">
-        <is>
-          <t>Codg. 541 - Praderas del Norte - $95 -  Inmb. Primav - Solicita visita del  4-10  Mayo.</t>
-        </is>
-      </c>
-      <c r="J35" t="inlineStr"/>
-      <c r="K35" t="inlineStr"/>
-      <c r="L35" t="inlineStr"/>
-      <c r="M35" t="inlineStr"/>
+          <t>tibio</t>
+        </is>
+      </c>
+      <c r="I35" s="1" t="inlineStr">
+        <is>
+          <t>Compra casa -con garaje-Norte-Créd. Hip. $260mlls</t>
+        </is>
+      </c>
+      <c r="J35" s="1" t="inlineStr">
+        <is>
+          <t>Tipos: Casa | Zonas: Norte | Precio: 150000000 - 266000000</t>
+        </is>
+      </c>
+      <c r="K35" t="inlineStr">
+        <is>
+          <t>Crédito, Efectivo</t>
+        </is>
+      </c>
+      <c r="L35" s="2" t="n">
+        <v>266000000</v>
+      </c>
+      <c r="M35" t="inlineStr">
+        <is>
+          <t>semanal</t>
+        </is>
+      </c>
       <c r="N35" t="n">
-        <v>0</v>
-      </c>
-      <c r="O35" t="inlineStr"/>
-      <c r="P35" t="inlineStr">
-        <is>
-          <t>{"id":1777896083201,"fecha":"2026-06-03T13:04:35.970Z","nombre":"Mercy Calderon Perdomo","celular":3186345106,"tipo":"cliente","estado":"inactivo","etiqueta":"inactivo","notas":"Codg. 541 - Praderas del Norte - $95 -  Inmb. Primav - Solicita visita del  4-10  Mayo."}</t>
+        <v>8</v>
+      </c>
+      <c r="O35" s="1" t="inlineStr">
+        <is>
+          <t>2026-05-29 (8)</t>
+        </is>
+      </c>
+      <c r="P35" s="1" t="inlineStr">
+        <is>
+          <t>{"id": "U-1780093548365515", "tipo": "cliente", "nombre": "Natalia Cerquera", "celular": "3102739529", "notas": "Compra casa -con garaje-Norte-Créd. Hip. $260mlls", "metodoPago": ["Crédito", "Efectivo"], "estado": "enviando", "etiqueta": "tibio", "filtros": {"tipoInmueble": ["Casa"], "rangoPrecio": [], "zona": ["Norte"], "habitaciones": [], "garaje": ["1"], "pisos": [], "ubicacion": [], "piscina": [], "cocina": [], "barrio": [], "conjunto": [], "minPrice": 150000000, "maxPrice": 266000000, "kmzCategory": [], "buscar": ""}, "frecuencia": "semanal", "maxPorEnvio": 4, "nombreInmobiliaria": "", "nombreAgente": "", "propsFiltradas": ["625", "496", "078", "106", "622", "713", "933", "266", "828", "303", "1193", "623", "692", "4682"], "propsEnviadas": ["078", "933", "266", "303", "1193", "623", "692", "4682"], "proximosEnvios": [{"fecha": "2026-06-05", "codigos": [], "enviado": false, "esCheck": true}], "historialEnvios": [{"fecha": "2026-05-29", "codigos": ["078", "933", "266", "303", "1193", "623", "692", "4682"], "totalCods": 8, "tipoEnvio": "individual", "notas": "Envío selección individual"}], "visitas": [], "creadoEn": "2026-05-29T22:25:48.366Z"}</t>
         </is>
       </c>
     </row>
     <row r="36">
-      <c r="A36" t="inlineStr">
-        <is>
-          <t>U-177948344535126</t>
-        </is>
-      </c>
-      <c r="B36" t="inlineStr">
-        <is>
-          <t>2026-06-01T22:09:01.492Z</t>
+      <c r="A36" s="1" t="inlineStr">
+        <is>
+          <t>U-1780007032409870</t>
+        </is>
+      </c>
+      <c r="B36" s="1" t="inlineStr">
+        <is>
+          <t>2026-05-28T22:23:52.409Z</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Roberto Pascuas</t>
-        </is>
-      </c>
-      <c r="D36" t="n">
-        <v>3186938925</v>
+          <t>Nelson</t>
+        </is>
+      </c>
+      <c r="D36" s="1" t="inlineStr">
+        <is>
+          <t>3138314537</t>
+        </is>
       </c>
       <c r="E36" t="inlineStr">
         <is>
@@ -2673,49 +2829,71 @@
       <c r="F36" t="inlineStr"/>
       <c r="G36" t="inlineStr">
         <is>
-          <t>inactivo</t>
+          <t>enviando</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>inactivo</t>
-        </is>
-      </c>
-      <c r="I36" t="inlineStr">
-        <is>
-          <t>Compra casa para la hija.</t>
-        </is>
-      </c>
-      <c r="J36" t="inlineStr">
-        <is>
-          <t>{"id":"U-177948344535126","tipo":"cliente","nombre":"Roberto Pascuas","celular":"3186938925","notas":"Compra casa para la hija.","metodoPago":["Efectivo","Crédito"],"estado":"inactivo","etiqueta":"inactivo","filtros":{"tipoInmueble":[],"rangoPrecio":[],"zona":[],"habitaciones":[],"garaje":[],"pisos":[],"ubicacion":[],"piscina":[],"cocina":[],"barrio":[],"conjunto":[],"minPrice":null,"maxPrice":null,"kmzCategory":["APTO Y APTO EN CONJUNTO 🏢","CASA EN CONJUNTO, CAMPESTRE IND Y EN CONJUNTO⛳","CASA LOTE, LOTE Y LOTE EN CONJUNTO ⛳","CASAS Y EDIFICIOS RENTABLES💲","CASAS 🏡","LOCAL, BODEGA Y OFICINA 🏪"],"buscar":"223"},"frecuencia":"semanal","maxPorEnvio":4,"nombreInmobiliaria":"","nombreAgente":"","propsFiltradas":["223"],"propsEnviadas":[],"proximosEnvios":[{"fecha":"2026-05-29","codigos":[],"enviado":false,"esCheck":true}],"historialEnvios":[],"visitas":[{"id":"1779485819832","codigo":"223","fecha":"2026-05-23","hora":"10:00","estado":"agendada","oferto":"no","oferta":"","notas":"Don Ignacio el propietario ya tiene conocimiento del cliente y la cita.","cliente":"Roberto Pascuas","celular":"3186938925","inmobiliaria":"","updatedAt":1779485902389}],"creadoEn":"2026-05-22T20:57:25.351Z","feedback":{}}</t>
-        </is>
-      </c>
-      <c r="K36" t="inlineStr"/>
-      <c r="L36" t="inlineStr"/>
-      <c r="M36" t="inlineStr"/>
-      <c r="N36" t="inlineStr"/>
-      <c r="O36" t="inlineStr"/>
-      <c r="P36" t="inlineStr"/>
+          <t>activo</t>
+        </is>
+      </c>
+      <c r="I36" s="1" t="inlineStr">
+        <is>
+          <t>Compra casa rentable $400mlls-Norte-Efectivo.</t>
+        </is>
+      </c>
+      <c r="J36" s="1" t="inlineStr">
+        <is>
+          <t>Tipos: Casa rentable | Zonas: Norte | Precio: 303000000 - 451000000</t>
+        </is>
+      </c>
+      <c r="K36" t="inlineStr">
+        <is>
+          <t>Efectivo</t>
+        </is>
+      </c>
+      <c r="L36" s="2" t="n">
+        <v>451000000</v>
+      </c>
+      <c r="M36" t="inlineStr">
+        <is>
+          <t>semanal</t>
+        </is>
+      </c>
+      <c r="N36" t="n">
+        <v>15</v>
+      </c>
+      <c r="O36" s="1" t="inlineStr">
+        <is>
+          <t>2026-05-28 (15)</t>
+        </is>
+      </c>
+      <c r="P36" s="1" t="inlineStr">
+        <is>
+          <t>{"id": "U-1780007032409870", "tipo": "cliente", "nombre": "Nelson", "celular": "3138314537", "notas": "Compra casa rentable $400mlls-Norte-Efectivo.", "metodoPago": ["Efectivo"], "estado": "enviando", "etiqueta": "activo", "filtros": {"tipoInmueble": ["Casa rentable"], "rangoPrecio": [], "zona": ["Norte"], "habitaciones": [], "garaje": [], "pisos": [], "ubicacion": [], "piscina": [], "cocina": [], "barrio": [], "conjunto": [], "minPrice": 303000000, "maxPrice": 451000000, "kmzCategory": ["APTO Y APTO EN CONJUNTO 🏢", "CASA EN CONJUNTO, CAMPESTRE IND Y EN CONJUNTO⛳", "CASA LOTE, LOTE Y LOTE EN CONJUNTO ⛳", "CASAS Y EDIFICIOS RENTABLES💲", "CASAS 🏡", "LOCAL, BODEGA Y OFICINA 🏪"], "buscar": ""}, "frecuencia": "semanal", "maxPorEnvio": 4, "nombreInmobiliaria": "", "nombreAgente": "", "propsFiltradas": ["978", "1189", "240", "1682", "818", "1230", "1648", "423", "1332", "1378", "455", "758", "014", "179", "1709"], "propsEnviadas": ["978", "1189", "240", "1682", "818", "1230", "1648", "423", "1332", "1378", "455", "758", "014", "179", "1709"], "proximosEnvios": [{"fecha": "2026-06-04", "codigos": [], "enviado": false, "esCheck": true}], "historialEnvios": [{"fecha": "2026-05-28", "codigos": ["978", "1189", "240", "1682", "818", "1230", "1648", "423", "1332", "1378", "455", "758", "014", "179", "1709"], "totalCods": 15, "tipoEnvio": "link", "notas": "Envío de link catálogo"}], "visitas": [], "creadoEn": "2026-05-28T22:23:52.409Z"}</t>
+        </is>
+      </c>
     </row>
     <row r="37">
-      <c r="A37" t="inlineStr">
-        <is>
-          <t>U-1780081837240957</t>
-        </is>
-      </c>
-      <c r="B37" t="inlineStr">
-        <is>
-          <t>2026-06-05T16:50:15.376Z</t>
+      <c r="A37" s="1" t="inlineStr">
+        <is>
+          <t>U-1780001855681844</t>
+        </is>
+      </c>
+      <c r="B37" s="1" t="inlineStr">
+        <is>
+          <t>2026-05-28T20:57:35.681Z</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Germán Arevalo</t>
-        </is>
-      </c>
-      <c r="D37" t="n">
-        <v>3203259635</v>
+          <t>Oscar Luis Suarez Cubillos</t>
+        </is>
+      </c>
+      <c r="D37" s="1" t="inlineStr">
+        <is>
+          <t>3118571606</t>
+        </is>
       </c>
       <c r="E37" t="inlineStr">
         <is>
@@ -2725,49 +2903,65 @@
       <c r="F37" t="inlineStr"/>
       <c r="G37" t="inlineStr">
         <is>
-          <t>inactivo</t>
+          <t>visita</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>inactivo</t>
-        </is>
-      </c>
-      <c r="I37" t="inlineStr">
-        <is>
-          <t>Compra casalote- Codg. 220. - Cliente SILENCIOSO.</t>
-        </is>
-      </c>
-      <c r="J37" t="inlineStr"/>
-      <c r="K37" t="inlineStr"/>
+          <t>activo</t>
+        </is>
+      </c>
+      <c r="I37" s="1" t="inlineStr">
+        <is>
+          <t>Compra casa rentable económica - Norte $200mlls.</t>
+        </is>
+      </c>
+      <c r="J37" s="1" t="inlineStr"/>
+      <c r="K37" t="inlineStr">
+        <is>
+          <t>Efectivo</t>
+        </is>
+      </c>
       <c r="L37" t="inlineStr"/>
-      <c r="M37" t="inlineStr"/>
+      <c r="M37" t="inlineStr">
+        <is>
+          <t>semanal</t>
+        </is>
+      </c>
       <c r="N37" t="n">
-        <v>0</v>
-      </c>
-      <c r="O37" t="inlineStr"/>
-      <c r="P37" t="inlineStr">
-        <is>
-          <t>{"id":"U-1780081837240957","fecha":"2026-06-04T19:35:58.826Z","nombre":"Germán Arevalo","celular":3203259635,"tipo":"cliente","estado":"inactivo","etiqueta":"inactivo","notas":"Compra casalote- Codg. 220. - Cliente SILENCIOSO."}</t>
+        <v>588</v>
+      </c>
+      <c r="O37" s="1" t="inlineStr">
+        <is>
+          <t>2026-05-28 (593)</t>
+        </is>
+      </c>
+      <c r="P37" s="1" t="inlineStr">
+        <is>
+          <t>{"id": "U-1780001855681844", "tipo": "cliente", "nombre": "Oscar Luis Suarez Cubillos", "celular": "3118571606", "notas": "Compra casa rentable económica - Norte $200mlls.", "metodoPago": ["Efectivo"], "estado": "visita", "etiqueta": "activo", "filtros": {"tipoInmueble": [], "rangoPrecio": [], "zona": [], "habitaciones": [], "garaje": [], "pisos": [], "ubicacion": [], "piscina": [], "cocina": [], "barrio": [], "conjunto": [], "minPrice": null, "maxPrice": null, "kmzCategory": ["APTO Y APTO EN CONJUNTO 🏢", "CASA EN CONJUNTO, CAMPESTRE IND Y EN CONJUNTO⛳", "CASA LOTE, LOTE Y LOTE EN CONJUNTO ⛳", "CASAS Y EDIFICIOS RENTABLES💲", "CASAS 🏡", "LOCAL, BODEGA Y OFICINA 🏪"], "buscar": ""}, "frecuencia": "semanal", "maxPorEnvio": 4, "nombreInmobiliaria": "", "nombreAgente": "", "propsFiltradas": ["1376", "352", "1384", "800", "746", "833", "074", "1757", "1366", "1329", "1773", "291", "1758", "1295", "808", "473", "1284", "4911", "767", "809", "1265", "694", "1104", "810", "1370", "1718", "4750", "1060", "1034", "4864", "469", "593", "988", "859", "432", "661", "4817", "796", "781", "845", "045", "328", "892", "1251", "535", "567", "1249", "806", "795", "1356", "153", "198", "253", "605", "829", "807", "1433", "450", "1776", "1351", "1141", "544", "579", "478", "775", "799", "018", "1133", "425", "447", "483", "839", "1338", "1327", "427", "472", "509", "646", "824", "1170", "1246", "1139", "631", "193", "679", "887", "627", "119", "114", "430", "013", "279", "448", "678", "900", "032", "265", "620", "1713", "277", "440", "454", "284", "350", "320", "805", "629", "698", "604", "308", "130", "1800", "252", "695", "667", "935", "1026", "1739", "764", "103", "1778", "714", "1660", "1357", "155", "797", "912", "073", "226", "374", "813", "812", "501", "1100", "1499", "677", "773", "075", "1687", "346", "506", "543", "1337", "1341", "560", "902", "637", "648", "1266", "080", "433", "1379", "1381", "518", "1158", "1754", "704", "1509", "397", "595", "017", "861", "1274", "754", "852", "633", "1196", "638", "682", "659", "5110", "829", "765", "466", "220", "015", "1300", "1785", "863", "1294", "061", "1258", "1471", "1771", "1795", "426", "546", "836", "972", "978", "832", "1004", "1168", "670", "1710", "510", "1260", "1354", "816", "860", "1253", "1725", "711", "821", "1343", "1321", "1352", "1375", "205", "280", "507", "741", "1374", "4658", "1347", "906", "5353", "363", "1099", "1150", "1189", "1254", "1297", "1314", "1568", "1755", "240", "442", "453", "650", "687", "815", "865", "1682", "087", "1328", "1588", "4927", "1363", "369", "743", "582", "491", "818", "086", "1230", "1311", "1318", "1648", "942", "423", "634", "1362", "1365", "1081", "1167", "1342", "1678", "393", "443", "4613", "5058", "596", "877", "1332", "256", "1790", "357", "1287", "1714", "1767", "270", "830", "862", "089", "115", "102", "404", "042", "1062", "1245", "1276", "1331", "1378", "1379", "162", "1689", "335", "455", "4948", "758", "855", "882", "843", "1108", "1271", "475", "373", "039", "014", "046", "1330", "411", "867", "463", "505", "422", "179", "093", "111", "1325", "1482", "660", "854", "876", "760", "1709", "079", "1140", "171", "487", "019", "028", "066", "1206", "1316", "1344", "1542", "1560", "1762", "1796", "5145", "550", "632", "734", "752", "883", "067", "184", "321", "132", "696", "052", "1470", "888", "1666", "1281", "857", "038", "246", "347", "644", "026", "1055", "108", "1084", "1119", "1323", "1324", "134", "1372", "1373", "1430", "431", "444", "5017", "520", "587", "761", "874", "884", "970", "725", "594", "1345", "1786", "382", "1371", "467", "680", "691", "1110", "754", "1209", "1419", "1531", "1763", "348", "384", "4682", "1487", "306", "070", "654", "745", "1193", "121", "1224", "1625", "1685", "1722", "1766", "289", "296", "490", "611", "623", "692", "759", "772", "814", "834", "864", "873", "4972", "387", "615", "303", "602", "866", "871", "878", "1360", "869", "703", "020", "1511", "1690", "1727", "309", "410", "702", "726", "879", "109", "185", "827", "1267", "1667", "609", "828", "486", "030", "1005", "1669", "266", "4552", "1358", "1308", "733", "947", "1073", "1721", "713", "933", "100", "078", "106", "1382", "1772", "495", "621", "622", "1756", "802", "136", "496", "562", "564", "662", "736", "569", "221", "872", "223", "339", "1541", "1794", "345", "511", "262", "539", "853", "1242", "1549", "288", "554", "763", "1010", "1781", "215", "228", "868", "1112", "137", "552", "592", "690", "1003", "105", "607", "798", "847", "517", "4597", "625", "720", "880", "1326", "282", "362", "672", "716", "1285", "1383", "1728", "548", "706", "809", "647", "792", "1340", "1359", "360", "601", "674", "953", "1364", "489", "1413", "856", "1451", "1730", "325", "343", "606", "609", "727", "851", "939", "1268", "671", "118", "514", "5224", "5342", "916", "1369", "920", "991", "449", "522", "1368", "738", "849", "1198", "788", "016", "1187", "541", "1744", "464", "642", "837", "844", "779", "823", "588", "1036", "1090", "739", "723", "1644", "693", "783", "143", "1231", "1464", "1646", "1647", "167", "113", "581", "409", "036", "468", "540", "529", "744", "499", "940", "966", "125"], "propsEnviadas": ["1376", "352", "1384", "800", "746", "833", "074", "1757", "1366", "1329", "1773", "291", "1758", "1295", "808", "473", "1284", "4911", "767", "809", "1265", "694", "1104", "810", "1370", "1718", "4750", "1060", "1034", "4864", "469", "593", "988", "859", "432", "661", "4817", "796", "781", "845", "045", "328", "892", "1251", "535", "567", "1249", "806", "795", "1356", "153", "198", "253", "605", "829", "807", "1433", "450", "1776", "1351", "1141", "544", "579", "478", "775", "799", "018", "1133", "425", "447", "483", "839", "1338", "1327", "427", "472", "509", "646", "824", "1170", "1246", "1139", "631", "193", "679", "887", "627", "119", "114", "430", "013", "279", "448", "678", "900", "032", "265", "620", "1713", "277", "440", "454", "284", "350", "320", "805", "629", "698", "604", "308", "130", "1800", "252", "695", "667", "935", "1026", "1739", "764", "103", "1778", "714", "1660", "1357", "155", "797", "912", "073", "226", "374", "813", "812", "501", "1100", "1499", "677", "773", "075", "1687", "346", "506", "543", "1337", "1341", "560", "902", "637", "648", "1266", "080", "433", "1379", "1381", "518", "1158", "1754", "704", "1509", "397", "595", "017", "861", "1274", "754", "852", "633", "1196", "638", "682", "659", "5110", "765", "466", "220", "015", "1300", "1785", "863", "1294", "061", "1258", "1471", "1771", "1795", "426", "546", "836", "972", "978", "832", "1004", "1168", "670", "1710", "510", "1260", "1354", "816", "860", "1253", "1725", "711", "821", "1343", "1321", "1352", "1375", "205", "280", "507", "741", "1374", "4658", "1347", "906", "5353", "363", "1099", "1150", "1189", "1254", "1297", "1314", "1568", "1755", "240", "442", "453", "650", "687", "815", "865", "1682", "087", "1328", "1588", "4927", "1363", "369", "743", "582", "491", "818", "086", "1230", "1311", "1318", "1648", "942", "423", "634", "1362", "1365", "1081", "1167", "1342", "1678", "393", "443", "4613", "5058", "596", "877", "1332", "256", "1790", "357", "1287", "1714", "1767", "270", "830", "862", "089", "115", "102", "404", "042", "1062", "1245", "1276", "1331", "1378", "162", "1689", "335", "455", "4948", "758", "855", "882", "843", "1108", "1271", "475", "373", "039", "014", "046", "1330", "411", "867", "463", "505", "422", "179", "093", "111", "1325", "1482", "660", "854", "876", "760", "1709", "079", "1140", "171", "487", "019", "028", "066", "1206", "1316", "1344", "1542", "1560", "1762", "1796", "5145", "550", "632", "734", "752", "883", "067", "184", "321", "132", "696", "052", "1470", "888", "1666", "1281", "857", "038", "246", "347", "644", "026", "1055", "108", "1084", "1119", "1323", "1324", "134", "1372", "1373", "1430", "431", "444", "5017", "520", "587", "761", "874", "884", "970", "725", "594", "1345", "1786", "382", "1371", "467", "680", "691", "1110", "1209", "1419", "1531", "1763", "348", "384", "4682", "1487", "306", "070", "654", "745", "1193", "121", "1224", "1625", "1685", "1722", "1766", "289", "296", "490", "611", "623", "692", "759", "772", "814", "834", "864", "873", "4972", "387", "615", "303", "602", "866", "871", "878", "1360", "869", "703", "020", "1511", "1690", "1727", "309", "410", "702", "726", "879", "109", "185", "827", "1267", "1667", "609", "828", "486", "030", "1005", "1669", "266", "4552", "1358", "1308", "733", "947", "1073", "1721", "713", "933", "100", "078", "106", "1382", "1772", "495", "621", "622", "1756", "802", "136", "496", "562", "564", "662", "736", "569", "221", "872", "223", "339", "1541", "1794", "345", "511", "262", "539", "853", "1242", "1549", "288", "554", "763", "1010", "1781", "215", "228", "868", "1112", "137", "552", "592", "690", "1003", "105", "607", "798", "847", "517", "4597", "625", "720", "880", "1326", "282", "362", "672", "716", "1285", "1383", "1728", "548", "706", "647", "792", "1340", "1359", "360", "601", "674", "953", "1364", "489", "1413", "856", "1451", "1730", "325", "343", "606", "727", "851", "939", "1268", "671", "118", "514", "5224", "5342", "916", "1369", "920", "991", "449", "522", "1368", "738", "849", "1198", "788", "016", "1187", "541", "1744", "464", "642", "837", "844", "779", "823", "588", "1036", "1090", "739", "723", "1644", "693", "783", "143", "1231", "1464", "1646", "1647", "167", "113", "581", "409", "036", "468", "540", "529", "744", "499", "940", "966", "125"], "proximosEnvios": [{"fecha": "2026-06-04", "codigos": [], "enviado": false, "esCheck": true}], "historialEnvios": [{"fecha": "2026-05-28", "codigos": ["1376", "352", "1384", "800", "746", "833", "074", "1757", "1366", "1329", "1773", "291", "1758", "1295", "808", "473", "1284", "4911", "767", "809", "1265", "694", "1104", "810", "1370", "1718", "4750", "1060", "1034", "4864", "469", "593", "988", "859", "432", "661", "4817", "796", "781", "845", "045", "328", "892", "1251", "535", "567", "1249", "806", "795", "1356", "153", "198", "253", "605", "829", "807", "1433", "450", "1776", "1351", "1141", "544", "579", "478", "775", "799", "018", "1133", "425", "447", "483", "839", "1338", "1327", "427", "472", "509", "646", "824", "1170", "1246", "1139", "631", "193", "679", "887", "627", "119", "114", "430", "013", "279", "448", "678", "900", "032", "265", "620", "1713", "277", "440", "454", "284", "350", "320", "805", "629", "698", "604", "308", "130", "1800", "252", "695", "667", "935", "1026", "1739", "764", "103", "1778", "714", "1660", "1357", "155", "797", "912", "073", "226", "374", "813", "812", "501", "1100", "1499", "677", "773", "075", "1687", "346", "506", "543", "1337", "1341", "560", "902", "637", "648", "1266", "080", "433", "1379", "1381", "518", "1158", "1754", "704", "1509", "397", "595", "017", "861", "1274", "754", "852", "633", "1196", "638", "682", "659", "5110", "829", "765", "466", "220", "015", "1300", "1785", "863", "1294", "061", "1258", "1471", "1771", "1795", "426", "546", "836", "972", "978", "832", "1004", "1168", "670", "1710", "510", "1260", "1354", "816", "860", "1253", "1725", "711", "821", "1343", "1321", "1352", "1375", "205", "280", "507", "741", "1374", "4658", "1347", "906", "5353", "363", "1099", "1150", "1189", "1254", "1297", "1314", "1568", "1755", "240", "442", "453", "650", "687", "815", "865", "1682", "087", "1328", "1588", "4927", "1363", "369", "743", "582", "491", "818", "086", "1230", "1311", "1318", "1648", "942", "423", "634", "1362", "1365", "1081", "1167", "1342", "1678", "393", "443", "4613", "5058", "596", "877", "1332", "256", "1790", "357", "1287", "1714", "1767", "270", "830", "862", "089", "115", "102", "404", "042", "1062", "1245", "1276", "1331", "1378", "1379", "162", "1689", "335", "455", "4948", "758", "855", "882", "843", "1108", "1271", "475", "373", "039", "014", "046", "1330", "411", "867", "463", "505", "422", "179", "093", "111", "1325", "1482", "660", "854", "876", "760", "1709", "079", "1140", "171", "487", "019", "028", "066", "1206", "1316", "1344", "1542", "1560", "1762", "1796", "5145", "550", "632", "734", "752", "883", "067", "184", "321", "132", "696", "052", "1470", "888", "1666", "1281", "857", "038", "246", "347", "644", "026", "1055", "108", "1084", "1119", "1323", "1324", "134", "1372", "1373", "1430", "431", "444", "5017", "520", "587", "761", "874", "884", "970", "725", "594", "1345", "1786", "382", "1371", "467", "680", "691", "1110", "754", "1209", "1419", "1531", "1763", "348", "384", "4682", "1487", "306", "070", "654", "745", "1193", "121", "1224", "1625", "1685", "1722", "1766", "289", "296", "490", "611", "623", "692", "759", "772", "814", "834", "864", "873", "4972", "387", "615", "303", "602", "866", "871", "878", "1360", "869", "703", "020", "1511", "1690", "1727", "309", "410", "702", "726", "879", "109", "185", "827", "1267", "1667", "609", "828", "486", "030", "1005", "1669", "266", "4552", "1358", "1308", "733", "947", "1073", "1721", "713", "933", "100", "078", "106", "1382", "1772", "495", "621", "622", "1756", "802", "136", "496", "562", "564", "662", "736", "569", "221", "872", "223", "339", "1541", "1794", "345", "511", "262", "539", "853", "1242", "1549", "288", "554", "763", "1010", "1781", "215", "228", "868", "1112", "137", "552", "592", "690", "1003", "105", "607", "798", "847", "517", "4597", "625", "720", "880", "1326", "282", "362", "672", "716", "1285", "1383", "1728", "548", "706", "809", "647", "792", "1340", "1359", "360", "601", "674", "953", "1364", "489", "1413", "856", "1451", "1730", "325", "343", "606", "609", "727", "851", "939", "1268", "671", "118", "514", "5224", "5342", "916", "1369", "920", "991", "449", "522", "1368", "738", "849", "1198", "788", "016", "1187", "541", "1744", "464", "642", "837", "844", "779", "823", "588", "1036", "1090", "739", "723", "1644", "693", "783", "143", "1231", "1464", "1646", "1647", "167", "113", "581", "409", "036", "468", "540", "529", "744", "499", "940", "966", "125"], "totalCods": 593, "tipoEnvio": "link", "notas": "Envío de link catálogo"}], "visitas": [], "creadoEn": "2026-05-28T20:57:35.681Z"}</t>
         </is>
       </c>
     </row>
     <row r="38">
-      <c r="A38" t="n">
-        <v>1778196950123</v>
-      </c>
-      <c r="B38" t="inlineStr">
-        <is>
-          <t>2026-06-05T16:51:44.476Z</t>
+      <c r="A38" s="1" t="inlineStr">
+        <is>
+          <t>U-1779826133120161</t>
+        </is>
+      </c>
+      <c r="B38" s="1" t="inlineStr">
+        <is>
+          <t>2026-05-26T20:08:53.120Z</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Justiniano  Monje Cortes</t>
-        </is>
-      </c>
-      <c r="D38" t="n">
-        <v>3204666321</v>
+          <t>Rafael Zuñiga</t>
+        </is>
+      </c>
+      <c r="D38" s="1" t="inlineStr">
+        <is>
+          <t>3233277573</t>
+        </is>
       </c>
       <c r="E38" t="inlineStr">
         <is>
@@ -2777,50 +2971,61 @@
       <c r="F38" t="inlineStr"/>
       <c r="G38" t="inlineStr">
         <is>
-          <t>inactivo</t>
+          <t>visita</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>inactivo</t>
-        </is>
-      </c>
-      <c r="I38" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Codg. 223 - Los Cambulos II-$175mlls - Disponible. Efectivo. YA INVIRTIO.
-</t>
-        </is>
-      </c>
-      <c r="J38" t="inlineStr"/>
-      <c r="K38" t="inlineStr"/>
+          <t>activo</t>
+        </is>
+      </c>
+      <c r="I38" s="1" t="inlineStr">
+        <is>
+          <t>Compra local, centro, buena visibilidad, $600 mlls. Desea sobre la calle 7 metropolitano. Está muy bajo el presupuesto. Allí son de aprox. $1.500 mlls - Se le ha ofrecido inmuebles de Felix, Rocha e ICDE. Rocha tiene el contacto.</t>
+        </is>
+      </c>
+      <c r="J38" s="1" t="inlineStr"/>
+      <c r="K38" t="inlineStr">
+        <is>
+          <t>Efectivo</t>
+        </is>
+      </c>
       <c r="L38" t="inlineStr"/>
-      <c r="M38" t="inlineStr"/>
+      <c r="M38" t="inlineStr">
+        <is>
+          <t>semanal</t>
+        </is>
+      </c>
       <c r="N38" t="n">
         <v>0</v>
       </c>
-      <c r="O38" t="inlineStr"/>
-      <c r="P38" t="inlineStr">
-        <is>
-          <t>{"id":1778196950123,"fecha":"2026-06-04T16:17:37.257Z","nombre":"Justiniano  Monje Cortes","celular":3204666321,"tipo":"cliente","estado":"inactivo","etiqueta":"inactivo","notas":"Codg. 223 - Los Cambulos II-$175mlls - Disponible. Efectivo. YA INVIRTIO.\n"}</t>
+      <c r="O38" s="1" t="inlineStr"/>
+      <c r="P38" s="1" t="inlineStr">
+        <is>
+          <t>{"id": "U-1779826133120161", "tipo": "cliente", "nombre": "Rafael Zuñiga", "celular": "3233277573", "notas": "Compra local, centro, buena visibilidad, $600 mlls. Desea sobre la calle 7 metropolitano. Está muy bajo el presupuesto. Allí son de aprox. $1.500 mlls - Se le ha ofrecido inmuebles de Felix, Rocha e ICDE. Rocha tiene el contacto.", "metodoPago": ["Efectivo"], "estado": "visita", "etiqueta": "activo", "filtros": {"tipoInmueble": [], "rangoPrecio": [], "zona": [], "habitaciones": [], "garaje": [], "pisos": [], "ubicacion": [], "piscina": [], "cocina": [], "barrio": [], "conjunto": [], "minPrice": null, "maxPrice": null, "kmzCategory": [], "buscar": ""}, "frecuencia": "semanal", "maxPorEnvio": 4, "nombreInmobiliaria": "", "nombreAgente": "", "propsFiltradas": ["1376", "352", "1384", "800", "746", "833", "074", "1757", "1366", "1329", "1773", "291", "1758", "1295", "808", "473", "1284", "4911", "767", "809", "1265", "1104", "694", "810", "1370", "1718", "4750", "1034", "1060", "469", "4864", "432", "593", "859", "988", "661", "4817", "796", "781", "045", "1251", "328", "845", "892", "1249", "535", "567", "806", "795", "1356", "153", "198", "253", "605", "829", "807", "1433", "450", "1351", "1776", "1141", "478", "544", "579", "775", "018", "799", "1133", "425", "447", "483", "839", "1338", "1327", "1170", "1246", "427", "472", "509", "646", "824", "1139", "193", "631", "679", "887", "119", "627", "114", "430", "013", "032", "265", "279", "448", "620", "678", "900", "1713", "277", "440", "454", "284", "308", "320", "350", "604", "629", "698", "805", "130", "1800", "252", "695", "1026", "103", "1660", "1739", "1778", "667", "714", "764", "935", "1357", "155", "797", "912", "073", "226", "374", "813", "812", "501", "075", "1100", "1337", "1341", "1499", "1687", "346", "506", "543", "560", "637", "648", "677", "773", "902", "080", "1266", "433", "1379", "1158", "1381", "1509", "1754", "397", "518", "595", "704", "1274", "852", "861", "633", "1196", "638", "659", "682", "5110", "829", "466", "765", "015", "1300", "1785", "220", "863", "832", "061", "1004", "1168", "1258", "1294", "1471", "1771", "1795", "426", "546", "670", "836", "972", "978", "1710", "1253", "1260", "1354", "1725", "510", "711", "816", "860", "821", "1321", "1343", "1352", "1374", "1375", "205", "280", "4658", "507", "741", "1347", "906", "5353", "087", "1099", "1150", "1189", "1254", "1297", "1314", "1328", "1568", "1682", "1755", "240", "363", "442", "453", "650", "687", "815", "865", "1363", "1588", "4927", "369", "743", "491", "582", "086", "1230", "1311", "1318", "1648", "176", "423", "634", "818", "1362", "1365", "1081", "1167", "1332", "1342", "1678", "393", "443", "4613", "5058", "596", "877", "256", "089", "1287", "1714", "1767", "1790", "270", "357", "830", "862", "115", "102", "1062", "1245", "1276", "1331", "1378", "1379", "162", "1689", "335", "404", "455", "4948", "758", "855", "882", "843", "1108", "1271", "475", "373", "014", "039", "046", "1330", "411", "867", "422", "463", "505", "093", "111", "1325", "1482", "179", "660", "760", "854", "876", "1709", "019", "028", "066", "067", "079", "1140", "1206", "1316", "132", "1344", "1542", "1560", "171", "1762", "1796", "184", "321", "487", "5145", "550", "632", "734", "752", "883", "696", "052", "1470", "888", "1666", "1281", "857", "026", "038", "1055", "108", "1084", "1119", "1323", "1324", "134", "1372", "1373", "1430", "246", "347", "431", "444", "5017", "520", "587", "644", "725", "761", "874", "884", "970", "594", "1110", "1345", "1371", "1786", "382", "467", "680", "691", "754", "1209", "1419", "1487", "1531", "1763", "348", "384", "4682", "306", "070", "1193", "121", "1224", "1625", "1685", "1722", "1766", "289", "296", "490", "611", "623", "654", "692", "745", "759", "772", "814", "834", "864", "873", "4972", "303", "387", "602", "615", "866", "871", "1360", "869", "878", "020", "1511", "1690", "1727", "309", "410", "702", "703", "726", "879", "109", "1267", "1667", "185", "486", "609", "827", "828", "030", "1005", "1669", "266", "4552", "1358", "100", "1073", "1308", "1721", "713", "733", "933", "947", "078", "106", "1382", "1772", "495", "621", "622", "1756", "136", "496", "562", "564", "569", "662", "736", "802", "221", "872", "1541", "1794", "223", "339", "345", "511", "1242", "1549", "262", "288", "539", "554", "853", "763", "1010", "1781", "215", "228", "868", "847", "1003", "105", "1112", "137", "552", "592", "607", "690", "798", "4597", "465", "625", "880", "1285", "1326", "1383", "1728", "282", "362", "672", "706", "716", "809", "647", "792", "1340", "1359", "1364", "360", "489", "601", "674", "953", "1413", "856", "1268", "1451", "1730", "325", "343", "606", "609", "727", "851", "939", "671", "118", "1369", "514", "5224", "5342", "916", "920", "991", "449", "1368", "738", "849", "1198", "788", "016", "1187", "541", "1744", "464", "642", "837", "844", "588", "779", "823", "1036", "1090", "739", "723", "1644", "693", "783", "143", "1231", "1464", "1646", "1647", "167", "517", "720", "754", "017", "042", "548"], "propsEnviadas": [], "proximosEnvios": [{"fecha": "2026-06-02", "codigos": [], "enviado": false, "esCheck": true}], "historialEnvios": [], "visitas": [], "creadoEn": "2026-05-26T20:08:53.120Z", "feedback": {}}</t>
         </is>
       </c>
     </row>
     <row r="39">
-      <c r="A39" t="n">
-        <v>1777224335719</v>
-      </c>
-      <c r="B39" t="inlineStr">
-        <is>
-          <t>2026-06-05T16:47:36.575Z</t>
+      <c r="A39" s="1" t="inlineStr">
+        <is>
+          <t>1777566252041</t>
+        </is>
+      </c>
+      <c r="B39" s="1" t="inlineStr">
+        <is>
+          <t>2026-04-30T16:24:12.044Z</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Albeiro Prieto</t>
-        </is>
-      </c>
-      <c r="D39" t="n">
-        <v>3208788700</v>
+          <t>Reinaldo Diaz</t>
+        </is>
+      </c>
+      <c r="D39" s="1" t="inlineStr">
+        <is>
+          <t>3102684886</t>
+        </is>
       </c>
       <c r="E39" t="inlineStr">
         <is>
@@ -2830,47 +3035,65 @@
       <c r="F39" t="inlineStr"/>
       <c r="G39" t="inlineStr">
         <is>
-          <t>enviando</t>
+          <t>inactivo</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>tibio</t>
-        </is>
-      </c>
-      <c r="I39" t="inlineStr"/>
-      <c r="J39" t="inlineStr"/>
-      <c r="K39" t="inlineStr"/>
+          <t>inactivo</t>
+        </is>
+      </c>
+      <c r="I39" s="1" t="inlineStr">
+        <is>
+          <t>Visita del 4 al 10 de mayo - Se encuentra en el exterior.</t>
+        </is>
+      </c>
+      <c r="J39" s="1" t="inlineStr">
+        <is>
+          <t>Tipos: Casa rentable</t>
+        </is>
+      </c>
+      <c r="K39" t="inlineStr">
+        <is>
+          <t>Efectivo, Crédito</t>
+        </is>
+      </c>
       <c r="L39" t="inlineStr"/>
-      <c r="M39" t="inlineStr"/>
+      <c r="M39" t="inlineStr">
+        <is>
+          <t>semanal</t>
+        </is>
+      </c>
       <c r="N39" t="n">
         <v>0</v>
       </c>
-      <c r="O39" t="inlineStr"/>
-      <c r="P39" t="inlineStr">
-        <is>
-          <t>{"id":1777224335719,"fecha":"2026-06-03T15:53:56.748Z","nombre":"Albeiro Prieto","celular":3208788700,"tipo":"cliente","estado":"enviando","etiqueta":"tibio","notas":""}</t>
+      <c r="O39" s="1" t="inlineStr"/>
+      <c r="P39" s="1" t="inlineStr">
+        <is>
+          <t>{"id": "1777566252041", "tipo": "cliente", "nombre": "Reinaldo Diaz", "celular": "3102684886", "notas": "Visita del 4 al 10 de mayo - Se encuentra en el exterior.", "metodoPago": ["Efectivo", "Crédito"], "estado": "inactivo", "etiqueta": "inactivo", "filtros": {"tipoInmueble": ["Casa rentable"], "rangoPrecio": [], "zona": [], "habitaciones": [], "garaje": [], "pisos": [], "ubicacion": [], "piscina": [], "cocina": [], "barrio": [], "conjunto": [], "buscar": "223"}, "frecuencia": "semanal", "maxPorEnvio": 4, "nombreInmobiliaria": "", "nombreAgente": "", "propsFiltradas": ["223"], "propsEnviadas": [], "proximosEnvios": [{"fecha": "2026-05-07", "codigos": [], "enviado": false, "esCheck": true}], "historialEnvios": [], "visitas": [], "creadoEn": "2026-04-30T16:24:12.044Z", "fromCloud": true}</t>
         </is>
       </c>
     </row>
     <row r="40">
-      <c r="A40" t="inlineStr">
-        <is>
-          <t>U-1780001088409490</t>
-        </is>
-      </c>
-      <c r="B40" t="inlineStr">
-        <is>
-          <t>2026-06-05T16:52:24.438Z</t>
+      <c r="A40" s="1" t="inlineStr">
+        <is>
+          <t>U-177948344535126</t>
+        </is>
+      </c>
+      <c r="B40" s="1" t="inlineStr">
+        <is>
+          <t>2026-05-22T20:57:25.351Z</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Martha Cubillos</t>
-        </is>
-      </c>
-      <c r="D40" t="n">
-        <v>3209029142</v>
+          <t>Roberto Pascuas</t>
+        </is>
+      </c>
+      <c r="D40" s="1" t="inlineStr">
+        <is>
+          <t>3186938925</t>
+        </is>
       </c>
       <c r="E40" t="inlineStr">
         <is>
@@ -2880,23 +3103,23 @@
       <c r="F40" t="inlineStr"/>
       <c r="G40" t="inlineStr">
         <is>
-          <t>visita</t>
+          <t>inactivo</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>activo</t>
-        </is>
-      </c>
-      <c r="I40" t="inlineStr">
-        <is>
-          <t>Compra casa  $200 norte</t>
-        </is>
-      </c>
-      <c r="J40" t="inlineStr"/>
+          <t>inactivo</t>
+        </is>
+      </c>
+      <c r="I40" s="1" t="inlineStr">
+        <is>
+          <t>Compra casa para la hija.</t>
+        </is>
+      </c>
+      <c r="J40" s="1" t="inlineStr"/>
       <c r="K40" t="inlineStr">
         <is>
-          <t>Efectivo</t>
+          <t>Efectivo, Crédito</t>
         </is>
       </c>
       <c r="L40" t="inlineStr"/>
@@ -2906,35 +3129,35 @@
         </is>
       </c>
       <c r="N40" t="n">
-        <v>1</v>
-      </c>
-      <c r="O40" t="inlineStr">
-        <is>
-          <t>2026-05-28 (1)</t>
-        </is>
-      </c>
-      <c r="P40" t="inlineStr">
-        <is>
-          <t>{"id":"U-1780001088409490","tipo":"cliente","nombre":"Martha Cubillos","celular":"3209029142","notas":"Compra casa  $200 norte","metodoPago":["Efectivo"],"estado":"visita","etiqueta":"activo","filtros":{"tipoInmueble":[],"rangoPrecio":[],"zona":[],"habitaciones":[],"garaje":[],"pisos":[],"ubicacion":[],"piscina":[],"cocina":[],"barrio":[],"conjunto":[],"minPrice":null,"maxPrice":null,"kmzCategory":["APTO Y APTO EN CONJUNTO 🏢","CASA EN CONJUNTO, CAMPESTRE IND Y EN CONJUNTO⛳","CASA LOTE, LOTE Y LOTE EN CONJUNTO ⛳","CASAS Y EDIFICIOS RENTABLES💲","CASAS 🏡","LOCAL, BODEGA Y OFICINA 🏪"],"buscar":"078"},"frecuencia":"semanal","maxPorEnvio":4,"nombreInmobiliaria":"","nombreAgente":"","propsFiltradas":["781","478","678","698","1778","1785","978","1678","256","1378","422","1786","878","933","078","1781","690","991","849","788","1644","783"],"propsEnviadas":["078"],"proximosEnvios":[{"fecha":"2026-06-04","codigos":[],"enviado":false,"esCheck":true}],"historialEnvios":[{"fecha":"2026-05-28","codigos":["078"],"totalCods":1,"tipoEnvio":"individual","notas":"Envío selección individual"}],"visitas":[],"creadoEn":"2026-05-28T20:44:48.411Z"}</t>
+        <v>0</v>
+      </c>
+      <c r="O40" s="1" t="inlineStr"/>
+      <c r="P40" s="1" t="inlineStr">
+        <is>
+          <t>{"id": "U-177948344535126", "tipo": "cliente", "nombre": "Roberto Pascuas", "celular": "3186938925", "notas": "Compra casa para la hija.", "metodoPago": ["Efectivo", "Crédito"], "estado": "inactivo", "etiqueta": "inactivo", "filtros": {"tipoInmueble": [], "rangoPrecio": [], "zona": [], "habitaciones": [], "garaje": [], "pisos": [], "ubicacion": [], "piscina": [], "cocina": [], "barrio": [], "conjunto": [], "minPrice": null, "maxPrice": null, "kmzCategory": ["APTO Y APTO EN CONJUNTO 🏢", "CASA EN CONJUNTO, CAMPESTRE IND Y EN CONJUNTO⛳", "CASA LOTE, LOTE Y LOTE EN CONJUNTO ⛳", "CASAS Y EDIFICIOS RENTABLES💲", "CASAS 🏡", "LOCAL, BODEGA Y OFICINA 🏪"], "buscar": "223"}, "frecuencia": "semanal", "maxPorEnvio": 4, "nombreInmobiliaria": "", "nombreAgente": "", "propsFiltradas": ["223"], "propsEnviadas": [], "proximosEnvios": [{"fecha": "2026-05-29", "codigos": [], "enviado": false, "esCheck": true}], "historialEnvios": [], "visitas": [{"id": "1779485819832", "codigo": "223", "fecha": "2026-05-23", "hora": "10:00", "estado": "agendada", "oferto": "no", "oferta": "", "notas": "Don Ignacio el propietario ya tiene conocimiento del cliente y la cita.", "cliente": "Roberto Pascuas", "celular": "3186938925", "inmobiliaria": "", "updatedAt": 1779485902389}], "creadoEn": "2026-05-22T20:57:25.351Z", "feedback": {}}</t>
         </is>
       </c>
     </row>
     <row r="41">
-      <c r="A41" t="n">
-        <v>1777994227586</v>
-      </c>
-      <c r="B41" t="inlineStr">
-        <is>
-          <t>2026-06-05T16:51:24.372Z</t>
+      <c r="A41" s="1" t="inlineStr">
+        <is>
+          <t>U-1778622246028103</t>
+        </is>
+      </c>
+      <c r="B41" s="1" t="inlineStr">
+        <is>
+          <t>2026-06-04T15:38:28.622Z</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>Jaison Roldando Gonzalez</t>
-        </is>
-      </c>
-      <c r="D41" t="n">
-        <v>3214939473</v>
+          <t>Roger Martínez .</t>
+        </is>
+      </c>
+      <c r="D41" s="1" t="inlineStr">
+        <is>
+          <t>3175179466</t>
+        </is>
       </c>
       <c r="E41" t="inlineStr">
         <is>
@@ -2944,51 +3167,57 @@
       <c r="F41" t="inlineStr"/>
       <c r="G41" t="inlineStr">
         <is>
-          <t>enviando</t>
+          <t>inactivo</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>tibio</t>
-        </is>
-      </c>
-      <c r="I41" t="inlineStr">
-        <is>
-          <t>Busca lote o casa lote central  - presupuesto $200 mlls .</t>
-        </is>
-      </c>
-      <c r="J41" t="inlineStr"/>
+          <t>inactivo</t>
+        </is>
+      </c>
+      <c r="I41" s="1" t="inlineStr">
+        <is>
+          <t>Inf 038 - 07 9 - 591 - YA INVIRTIO.</t>
+        </is>
+      </c>
+      <c r="J41" s="1" t="inlineStr"/>
       <c r="K41" t="inlineStr"/>
       <c r="L41" t="inlineStr"/>
-      <c r="M41" t="inlineStr"/>
+      <c r="M41" t="inlineStr">
+        <is>
+          <t>manual</t>
+        </is>
+      </c>
       <c r="N41" t="n">
         <v>0</v>
       </c>
-      <c r="O41" t="inlineStr"/>
-      <c r="P41" t="inlineStr">
-        <is>
-          <t>{"id":1777994227586,"fecha":"2026-06-03T15:39:35.409Z","nombre":"Jaison Roldando Gonzalez","celular":3214939473,"tipo":"cliente","estado":"enviando","etiqueta":"tibio","notas":"Busca lote o casa lote central  - presupuesto $200 mlls ."}</t>
+      <c r="O41" s="1" t="inlineStr"/>
+      <c r="P41" s="1" t="inlineStr">
+        <is>
+          <t>{"id": "U-1778622246028103", "fecha": "2026-06-04T15:38:28.622Z", "nombre": "Roger Martínez .", "celular": "3175179466", "tipo": "cliente", "estado": "inactivo", "etiqueta": "inactivo", "notas": "Inf 038 - 07 9 - 591 - YA INVIRTIO.", "fromCloud": true}</t>
         </is>
       </c>
     </row>
     <row r="42">
-      <c r="A42" t="inlineStr">
-        <is>
-          <t>U-177832909617130</t>
-        </is>
-      </c>
-      <c r="B42" t="inlineStr">
-        <is>
-          <t>2026-06-05T16:49:43.730Z</t>
+      <c r="A42" s="1" t="inlineStr">
+        <is>
+          <t>1777895245612</t>
+        </is>
+      </c>
+      <c r="B42" s="1" t="inlineStr">
+        <is>
+          <t>2026-06-03T16:01:58.640Z</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>David Cataño</t>
-        </is>
-      </c>
-      <c r="D42" t="n">
-        <v>3215696084</v>
+          <t>Sandra</t>
+        </is>
+      </c>
+      <c r="D42" s="1" t="inlineStr">
+        <is>
+          <t>3142014730</t>
+        </is>
       </c>
       <c r="E42" t="inlineStr">
         <is>
@@ -3003,55 +3232,51 @@
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>tibio</t>
-        </is>
-      </c>
-      <c r="I42" t="inlineStr">
-        <is>
-          <t>YA INVIRTIO EN IBAGUE. Codg.  844 - Apto Bosques San Juis - $87-Inmb. S. Primv  - Disponible - Pago Caja Honor. Comprador del Cauca. La Inmb. Ya está encontacto con el comprador y le enseñará otro.  En el catálogo $87 - Panel $100...???</t>
-        </is>
-      </c>
-      <c r="J42" t="inlineStr"/>
-      <c r="K42" t="inlineStr">
-        <is>
-          <t>Caja Honor</t>
-        </is>
-      </c>
+          <t>inactivo</t>
+        </is>
+      </c>
+      <c r="I42" s="1" t="inlineStr">
+        <is>
+          <t>Solicita cita Codg. 1010 - sector sur - $165 - Jennifer . . . No fue posible coordinar la cita. Arrendatarios complicados. Se suspende la publicación hasta que entreguen la casa.</t>
+        </is>
+      </c>
+      <c r="J42" s="1" t="inlineStr"/>
+      <c r="K42" t="inlineStr"/>
       <c r="L42" t="inlineStr"/>
       <c r="M42" t="inlineStr">
         <is>
-          <t>semanal</t>
+          <t>manual</t>
         </is>
       </c>
       <c r="N42" t="n">
         <v>0</v>
       </c>
-      <c r="O42" t="inlineStr"/>
-      <c r="P42" t="inlineStr">
-        <is>
-          <t>{"id":"U-177832909617130","tipo":"cliente","nombre":"David Cataño","celular":"3215696084","notas":"YA INVIRTIO EN IBAGUE. Codg.  844 - Apto Bosques San Juis - $87-Inmb. S. Primv  - Disponible - Pago Caja Honor. Comprador del Cauca. La Inmb. Ya está encontacto con el comprador y le enseñará otro.  En el catálogo $87 - Panel $100...???","metodoPago":["Caja Honor"],"estado":"inactivo","etiqueta":"tibio","filtros":{"tipoInmueble":[],"rangoPrecio":[],"zona":[],"habitaciones":[],"garaje":[],"pisos":[],"ubicacion":[],"piscina":[],"cocina":[],"barrio":[],"conjunto":[],"buscar":"844"},"frecuencia":"semanal","maxPorEnvio":4,"nombreInmobiliaria":"","nombreAgente":"","propsFiltradas":["844"],"propsEnviadas":[],"proximosEnvios":[{"fecha":"2026-05-13","codigos":[],"enviado":false,"esCheck":true}],"historialEnvios":[],"visitas":[],"creadoEn":"2026-05-06T14:12:56.783Z","feedback":{}}</t>
+      <c r="O42" s="1" t="inlineStr"/>
+      <c r="P42" s="1" t="inlineStr">
+        <is>
+          <t>{"id": "1777895245612", "fecha": "2026-06-03T16:01:58.640Z", "nombre": "Sandra", "celular": "3142014730", "tipo": "cliente", "estado": "inactivo", "etiqueta": "inactivo", "notas": "Solicita cita Codg. 1010 - sector sur - $165 - Jennifer . . . No fue posible coordinar la cita. Arrendatarios complicados. Se suspende la publicación hasta que entreguen la casa.", "fromCloud": true}</t>
         </is>
       </c>
     </row>
     <row r="43">
-      <c r="A43" t="inlineStr">
-        <is>
-          <t>U-1778271567218168</t>
-        </is>
-      </c>
-      <c r="B43" t="inlineStr">
-        <is>
-          <t>2026-06-05T16:50:07.923Z</t>
+      <c r="A43" s="1" t="inlineStr">
+        <is>
+          <t>U-178035156168992</t>
+        </is>
+      </c>
+      <c r="B43" s="1" t="inlineStr">
+        <is>
+          <t>2026-06-04T19:54:31.263Z</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>Fransua Chaux</t>
-        </is>
-      </c>
-      <c r="D43" t="inlineStr">
-        <is>
-          <t>322 399 3035</t>
+          <t>Sandra Liliana Murcia</t>
+        </is>
+      </c>
+      <c r="D43" s="1" t="inlineStr">
+        <is>
+          <t>3125246887</t>
         </is>
       </c>
       <c r="E43" t="inlineStr">
@@ -3062,7 +3287,7 @@
       <c r="F43" t="inlineStr"/>
       <c r="G43" t="inlineStr">
         <is>
-          <t>enviando</t>
+          <t>visita</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
@@ -3070,93 +3295,77 @@
           <t>activo</t>
         </is>
       </c>
-      <c r="I43" t="inlineStr"/>
-      <c r="J43" t="inlineStr">
-        <is>
-          <t>Tipos: Apartamento en conjunto | Precio: 101000000 - 164000000</t>
-        </is>
-      </c>
+      <c r="I43" s="1" t="inlineStr">
+        <is>
+          <t>Compra lote en conjunto 1710 $445mlls- C&amp;C.</t>
+        </is>
+      </c>
+      <c r="J43" s="1" t="inlineStr"/>
       <c r="K43" t="inlineStr">
         <is>
           <t>Efectivo</t>
         </is>
       </c>
-      <c r="L43" t="n">
-        <v>164000000</v>
-      </c>
+      <c r="L43" t="inlineStr"/>
       <c r="M43" t="inlineStr">
         <is>
-          <t>semanal</t>
+          <t>manual</t>
         </is>
       </c>
       <c r="N43" t="n">
-        <v>2</v>
-      </c>
-      <c r="O43" t="inlineStr">
-        <is>
-          <t>2026-04-30 (1) | 2026-05-11 (1)</t>
-        </is>
-      </c>
-      <c r="P43" t="inlineStr">
-        <is>
-          <t>{"id":"U-1778271567218168","tipo":"cliente","nombre":"Fransua Chaux","celular":"322 399 3035","notas":"","metodoPago":["Efectivo"],"estado":"enviando","etiqueta":"activo","filtros":{"tipoInmueble":["Apartamento en conjunto"],"rangoPrecio":[],"zona":[],"habitaciones":[],"garaje":[],"pisos":[],"ubicacion":[],"piscina":[],"cocina":[],"barrio":[],"conjunto":[],"buscar":"","maxPrice":164000000,"minPrice":101000000},"frecuencia":"semanal","maxPorEnvio":4,"nombreInmobiliaria":"","nombreAgente":"","propsFiltradas":["105","465","4597","1728","1383","647","656","360","920"],"propsEnviadas":["105","1728"],"proximosEnvios":[{"fecha":"2026-05-18","codigos":[],"enviado":false,"esCheck":true}],"historialEnvios":[{"fecha":"2026-04-30","codigos":["105"],"totalCods":1,"tipoEnvio":"individual","notas":""},{"fecha":"2026-05-11","codigos":["1728"],"totalCods":1,"tipoEnvio":"silencioso","notas":"Filtros actualizados (propiedades marcadas como vistas sin enviar WhatsApp)"}],"visitas":[{"id":"1778532779440","codigo":"1728","fecha":"2026-05-11","hora":"","estado":"realizada","oferto":"si","oferta":"147.000.000","notas":"El dueño dijo 147 y ofertaron 147, C&amp;C esperando a ver si ofrecen más.","cliente":"Fransua Chaux","celular":"322 399 3035","inmobiliaria":""},{"id":"1779026220071","codigo":"105","fecha":"2026-05-17","hora":"","estado":"realizada","oferto":"no","oferta":"","notas":"","cliente":"Fransua Chaux","celular":"322 399 3035","inmobiliaria":""}],"creadoEn":"2026-04-30T15:34:12.578Z"}</t>
+        <v>0</v>
+      </c>
+      <c r="O43" s="1" t="inlineStr"/>
+      <c r="P43" s="1" t="inlineStr">
+        <is>
+          <t>{"id": "U-178035156168992", "fecha": "2026-06-04T19:54:31.263Z", "nombre": "Sandra Liliana Murcia", "celular": "3125246887", "tipo": "cliente", "estado": "visita", "etiqueta": "activo", "notas": "Compra lote en conjunto 1710 $445mlls- C&amp;C.", "metodoPago": ["Efectivo"], "fromCloud": true}</t>
         </is>
       </c>
     </row>
     <row r="44">
-      <c r="A44" t="inlineStr">
-        <is>
-          <t>U-1778271567218833</t>
-        </is>
-      </c>
-      <c r="B44" t="inlineStr">
-        <is>
-          <t>2026-06-05T16:51:35.558Z</t>
+      <c r="A44" s="1" t="inlineStr">
+        <is>
+          <t>U-1778872679106678</t>
+        </is>
+      </c>
+      <c r="B44" s="1" t="inlineStr">
+        <is>
+          <t>2026-05-15T19:17:59.106Z</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>Jovel Muñoz</t>
-        </is>
-      </c>
-      <c r="D44" t="n">
-        <v>3232391020</v>
+          <t>Sindy Cabrera</t>
+        </is>
+      </c>
+      <c r="D44" s="1" t="inlineStr">
+        <is>
+          <t>3113330927</t>
+        </is>
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>inmobiliaria</t>
-        </is>
-      </c>
-      <c r="F44" t="inlineStr">
-        <is>
-          <t>Jovel Muñoz</t>
-        </is>
-      </c>
+          <t>cliente</t>
+        </is>
+      </c>
+      <c r="F44" t="inlineStr"/>
       <c r="G44" t="inlineStr">
         <is>
-          <t>visita</t>
+          <t>inactivo</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>tibio</t>
-        </is>
-      </c>
-      <c r="I44" t="inlineStr">
-        <is>
-          <t>Codg. 221  CJ.  Portal del Salitre . Pendiente de visitarla cuando terminen las obras locativas.</t>
-        </is>
-      </c>
-      <c r="J44" t="inlineStr">
-        <is>
-          <t>Tipos: Casa en conjunto</t>
-        </is>
-      </c>
-      <c r="K44" t="inlineStr">
-        <is>
-          <t>Efectivo, Crédito</t>
-        </is>
-      </c>
+          <t>inactivo</t>
+        </is>
+      </c>
+      <c r="I44" s="1" t="inlineStr">
+        <is>
+          <t>Codg. 078 Cocli- Disponible - ICDE. Compra casa o Apto en el norte. Pendiente del presupuesto y forma de pago.</t>
+        </is>
+      </c>
+      <c r="J44" s="1" t="inlineStr"/>
+      <c r="K44" t="inlineStr"/>
       <c r="L44" t="inlineStr"/>
       <c r="M44" t="inlineStr">
         <is>
@@ -3164,33 +3373,39 @@
         </is>
       </c>
       <c r="N44" t="n">
-        <v>0</v>
-      </c>
-      <c r="O44" t="inlineStr"/>
-      <c r="P44" t="inlineStr">
-        <is>
-          <t>{"id":"U-1778271567218833","tipo":"inmobiliaria","nombre":"Jovel Muñoz","celular":"3232391020","notas":"Codg. 221  CJ.  Portal del Salitre . Pendiente de visitarla cuando terminen las obras locativas.","metodoPago":["Efectivo","Crédito"],"estado":"visita","etiqueta":"tibio","filtros":{"tipoInmueble":["Casa en conjunto"],"rangoPrecio":[],"zona":[],"habitaciones":[],"garaje":[],"pisos":[],"ubicacion":[],"piscina":[],"cocina":[],"barrio":[],"conjunto":[],"buscar":"221"},"frecuencia":"semanal","maxPorEnvio":4,"nombreInmobiliaria":"Jovel Muñoz","nombreAgente":"3232391020","propsFiltradas":["221"],"propsEnviadas":[],"proximosEnvios":[{"fecha":"2026-05-12","codigos":[],"enviado":false,"esCheck":true}],"historialEnvios":[],"visitas":[],"creadoEn":"2026-05-05T14:29:10.587Z"}</t>
+        <v>1</v>
+      </c>
+      <c r="O44" s="1" t="inlineStr">
+        <is>
+          <t>2026-05-15 (1)</t>
+        </is>
+      </c>
+      <c r="P44" s="1" t="inlineStr">
+        <is>
+          <t>{"id": "U-1778872679106678", "tipo": "cliente", "nombre": "Sindy Cabrera", "celular": "3113330927", "notas": "Codg. 078 Cocli- Disponible - ICDE. Compra casa o Apto en el norte. Pendiente del presupuesto y forma de pago.", "metodoPago": [], "estado": "inactivo", "etiqueta": "inactivo", "filtros": {"tipoInmueble": [], "rangoPrecio": [], "zona": [], "habitaciones": [], "garaje": [], "pisos": [], "ubicacion": [], "piscina": [], "cocina": [], "barrio": [], "conjunto": [], "minPrice": null, "maxPrice": null, "kmzCategory": [], "buscar": "078"}, "frecuencia": "semanal", "maxPorEnvio": 4, "nombreInmobiliaria": "", "nombreAgente": "", "propsFiltradas": ["781", "078"], "propsEnviadas": ["078"], "proximosEnvios": [{"fecha": "2026-05-22", "codigos": [], "enviado": false, "esCheck": true}], "historialEnvios": [{"fecha": "2026-05-15", "codigos": ["078"], "notas": "Se marcaron 1 propiedades como enviadas (sin WhatsApp)."}], "visitas": [{"id": "1778874888238", "codigo": "078", "fecha": "2026-05-19", "hora": "11:00", "estado": "agendada", "oferto": "no", "oferta": "", "notas": "Visitará la casa 078 - No ha inicado forma de pago. Enseñará don Yirben.", "cliente": "Sindy Cabrera", "celular": "3113330927", "inmobiliaria": ""}], "creadoEn": "2026-05-15T19:17:59.106Z", "feedback": {}}</t>
         </is>
       </c>
     </row>
     <row r="45">
-      <c r="A45" t="inlineStr">
-        <is>
-          <t>U-1779826133120161</t>
-        </is>
-      </c>
-      <c r="B45" t="inlineStr">
-        <is>
-          <t>2026-06-02T23:16:51.750Z</t>
+      <c r="A45" s="1" t="inlineStr">
+        <is>
+          <t>U-1779365901250514</t>
+        </is>
+      </c>
+      <c r="B45" s="1" t="inlineStr">
+        <is>
+          <t>2026-05-21T12:18:21.251Z</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>Rafael Zuñiga</t>
-        </is>
-      </c>
-      <c r="D45" t="n">
-        <v>3233277573</v>
+          <t>Valentina Villarreal Pinzón</t>
+        </is>
+      </c>
+      <c r="D45" s="1" t="inlineStr">
+        <is>
+          <t>3118014180</t>
+        </is>
       </c>
       <c r="E45" t="inlineStr">
         <is>
@@ -3200,82 +3415,140 @@
       <c r="F45" t="inlineStr"/>
       <c r="G45" t="inlineStr">
         <is>
-          <t>visita</t>
+          <t>inactivo</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>activo</t>
-        </is>
-      </c>
-      <c r="I45" t="inlineStr">
-        <is>
-          <t>Compra local, centro, buena visibilidad, $600 mlls.  Desea sobre la calle 7 metropolitano. Está muy bajo el presupuesto. Allí son de aprox. $1.500 mlls - Se le ha ofrecido inmuebles de Felix, Rocha e ICDE. Rocha tiene el contacto.</t>
-        </is>
-      </c>
-      <c r="J45" t="inlineStr">
-        <is>
-          <t>{"id":"U-1779826133120161","tipo":"cliente","nombre":"Rafael Zuñiga","celular":"3233277573","notas":"Compra local, centro, buena visibilidad, $600 mlls.  Desea sobre la calle 7 metropolitano. Está muy bajo el presupuesto. Allí son de aprox. $1.500 mlls - Se le ha ofrecido inmuebles de Felix, Rocha e ICDE. Rocha tiene el contacto.","metodoPago":["Efectivo"],"estado":"visita","etiqueta":"activo","filtros":{"tipoInmueble":[],"rangoPrecio":[],"zona":[],"habitaciones":[],"garaje":[],"pisos":[],"ubicacion":[],"piscina":[],"cocina":[],"barrio":[],"conjunto":[],"minPrice":null,"maxPrice":null,"kmzCategory":[],"buscar":""},"frecuencia":"semanal","maxPorEnvio":4,"nombreInmobiliaria":"","nombreAgente":"","propsFiltradas":["1376","352","1384","800","746","833","074","1757","1366","1329","1773","291","1758","1295","808","473","1284","4911","767","809","1265","1104","694","810","1370","1718","4750","1034","1060","469","4864","432","593","859","988","661","4817","796","781","045","1251","328","845","892","1249","535","567","806","795","1356","153","198","253","605","829","807","1433","450","1351","1776","1141","478","544","579","775","018","799","1133","425","447","483","839","1338","1327","1170","1246","427","472","509","646","824","1139","193","631","679","887","119","627","114","430","013","032","265","279","448","620","678","900","1713","277","440","454","284","308","320","350","604","629","698","805","130","1800","252","695","1026","103","1660","1739","1778","667","714","764","935","1357","155","797","912","073","226","374","813","812","501","075","1100","1337","1341","1499","1687","346","506","543","560","637","648","677","773","902","080","1266","433","1379","1158","1381","1509","1754","397","518","595","704","1274","852","861","633","1196","638","659","682","5110","829","466","765","015","1300","1785","220","863","832","061","1004","1168","1258","1294","1471","1771","1795","426","546","670","836","972","978","1710","1253","1260","1354","1725","510","711","816","860","821","1321","1343","1352","1374","1375","205","280","4658","507","741","1347","906","5353","087","1099","1150","1189","1254","1297","1314","1328","1568","1682","1755","240","363","442","453","650","687","815","865","1363","1588","4927","369","743","491","582","086","1230","1311","1318","1648","176","423","634","818","1362","1365","1081","1167","1332","1342","1678","393","443","4613","5058","596","877","256","089","1287","1714","1767","1790","270","357","830","862","115","102","1062","1245","1276","1331","1378","1379","162","1689","335","404","455","4948","758","855","882","843","1108","1271","475","373","014","039","046","1330","411","867","422","463","505","093","111","1325","1482","179","660","760","854","876","1709","019","028","066","067","079","1140","1206","1316","132","1344","1542","1560","171","1762","1796","184","321","487","5145","550","632","734","752","883","696","052","1470","888","1666","1281","857","026","038","1055","108","1084","1119","1323","1324","134","1372","1373","1430","246","347","431","444","5017","520","587","644","725","761","874","884","970","594","1110","1345","1371","1786","382","467","680","691","754","1209","1419","1487","1531","1763","348","384","4682","306","070","1193","121","1224","1625","1685","1722","1766","289","296","490","611","623","654","692","745","759","772","814","834","864","873","4972","303","387","602","615","866","871","1360","869","878","020","1511","1690","1727","309","410","702","703","726","879","109","1267","1667","185","486","609","827","828","030","1005","1669","266","4552","1358","100","1073","1308","1721","713","733","933","947","078","106","1382","1772","495","621","622","1756","136","496","562","564","569","662","736","802","221","872","1541","1794","223","339","345","511","1242","1549","262","288","539","554","853","763","1010","1781","215","228","868","847","1003","105","1112","137","552","592","607","690","798","4597","465","625","880","1285","1326","1383","1728","282","362","672","706","716","809","647","792","1340","1359","1364","360","489","601","674","953","1413","856","1268","1451","1730","325","343","606","609","727","851","939","671","118","1369","514","5224","5342","916","920","991","449","1368","738","849","1198","788","016","1187","541","1744","464","642","837","844","588","779","823","1036","1090","739","723","1644","693","783","143","1231","1464","1646","1647","167","517","720","754","017","042","548"],"propsEnviadas":[],"proximosEnvios":[{"fecha":"2026-06-02","codigos":[],"enviado":false,"esCheck":true}],"historialEnvios":[],"visitas":[],"creadoEn":"2026-05-26T20:08:53.120Z","feedback":{}}</t>
-        </is>
-      </c>
-      <c r="K45" t="inlineStr"/>
+          <t>inactivo</t>
+        </is>
+      </c>
+      <c r="I45" s="1" t="inlineStr">
+        <is>
+          <t>Compra casa rentable, económica.</t>
+        </is>
+      </c>
+      <c r="J45" s="1" t="inlineStr"/>
+      <c r="K45" t="inlineStr">
+        <is>
+          <t>Efectivo, Crédito</t>
+        </is>
+      </c>
       <c r="L45" t="inlineStr"/>
-      <c r="M45" t="inlineStr"/>
-      <c r="N45" t="inlineStr"/>
-      <c r="O45" t="inlineStr"/>
-      <c r="P45" t="inlineStr"/>
+      <c r="M45" t="inlineStr">
+        <is>
+          <t>semanal</t>
+        </is>
+      </c>
+      <c r="N45" t="n">
+        <v>0</v>
+      </c>
+      <c r="O45" s="1" t="inlineStr"/>
+      <c r="P45" s="1" t="inlineStr">
+        <is>
+          <t>{"id": "U-1779365901250514", "tipo": "cliente", "nombre": "Valentina Villarreal Pinzón", "celular": "3118014180", "notas": "Compra casa rentable, económica.", "metodoPago": ["Efectivo", "Crédito"], "estado": "inactivo", "etiqueta": "inactivo", "filtros": {"tipoInmueble": [], "rangoPrecio": [], "zona": [], "habitaciones": [], "garaje": [], "pisos": [], "ubicacion": [], "piscina": [], "cocina": [], "barrio": [], "conjunto": [], "minPrice": null, "maxPrice": null, "kmzCategory": ["APTO Y APTO EN CONJUNTO 🏢", "CASA EN CONJUNTO, CAMPESTRE IND Y EN CONJUNTO⛳", "CASA LOTE, LOTE Y LOTE EN CONJUNTO ⛳", "CASAS Y EDIFICIOS RENTABLES💲", "CASAS 🏡", "LOCAL, BODEGA Y OFICINA 🏪"], "buscar": "223"}, "frecuencia": "semanal", "maxPorEnvio": 4, "nombreInmobiliaria": "", "nombreAgente": "", "propsFiltradas": ["223"], "propsEnviadas": [], "proximosEnvios": [{"fecha": "2026-05-28", "codigos": [], "enviado": false, "esCheck": true}], "historialEnvios": [], "visitas": [{"id": "1779366011043", "codigo": "223", "fecha": "2026-05-21", "hora": "15:00", "estado": "agendada", "oferto": "no", "oferta": "", "notas": "Ya se informó a propietario Ignacio. Pendiente reconfirmar.", "cliente": "Valentina", "celular": "3118014180", "inmobiliaria": "", "updatedAt": 1779366011043}], "creadoEn": "2026-05-21T12:18:21.251Z", "feedback": {}}</t>
+        </is>
+      </c>
     </row>
     <row r="46">
-      <c r="A46" t="inlineStr">
-        <is>
-          <t>U-1780355426553551</t>
-        </is>
-      </c>
-      <c r="B46" t="inlineStr">
-        <is>
-          <t>2026-06-05T16:51:58.835Z</t>
-        </is>
-      </c>
-      <c r="C46" t="inlineStr">
-        <is>
-          <t>María Sildana Arango</t>
-        </is>
-      </c>
-      <c r="D46" t="n">
-        <v>3248276336</v>
-      </c>
-      <c r="E46" t="inlineStr">
-        <is>
-          <t>cliente</t>
-        </is>
-      </c>
-      <c r="F46" t="inlineStr"/>
-      <c r="G46" t="inlineStr">
+      <c r="A46" s="1" t="n">
+        <v/>
+      </c>
+      <c r="B46" s="1" t="n">
+        <v/>
+      </c>
+      <c r="C46" t="n">
+        <v/>
+      </c>
+      <c r="D46" s="1" t="n">
+        <v/>
+      </c>
+      <c r="E46" t="n">
+        <v/>
+      </c>
+      <c r="F46" t="n">
+        <v/>
+      </c>
+      <c r="G46" t="n">
+        <v/>
+      </c>
+      <c r="H46" t="n">
+        <v/>
+      </c>
+      <c r="I46" s="1" t="n">
+        <v/>
+      </c>
+      <c r="J46" s="1" t="n">
+        <v/>
+      </c>
+      <c r="K46" t="n">
+        <v/>
+      </c>
+      <c r="L46" s="1" t="n">
+        <v/>
+      </c>
+      <c r="M46" t="n">
+        <v/>
+      </c>
+      <c r="N46" t="n">
+        <v/>
+      </c>
+      <c r="O46" s="1" t="n">
+        <v/>
+      </c>
+      <c r="P46" s="1" t="n">
+        <v/>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" s="1" t="inlineStr">
+        <is>
+          <t>LEAD-AGENDA-GLOBAL</t>
+        </is>
+      </c>
+      <c r="B47" s="1" t="inlineStr"/>
+      <c r="C47" t="inlineStr">
+        <is>
+          <t>Agenda Global (Citas Genéricas)</t>
+        </is>
+      </c>
+      <c r="D47" s="1" t="inlineStr"/>
+      <c r="E47" t="inlineStr">
+        <is>
+          <t>cliente</t>
+        </is>
+      </c>
+      <c r="F47" t="inlineStr"/>
+      <c r="G47" t="inlineStr">
         <is>
           <t>inactivo</t>
         </is>
       </c>
-      <c r="H46" t="inlineStr">
+      <c r="H47" t="inlineStr">
         <is>
           <t>inactivo</t>
         </is>
       </c>
-      <c r="I46" t="inlineStr">
-        <is>
-          <t>Interesada Codg, 625 Luis Carlos Galán - $155mll-Jennifer. Verificando la disponibilidad y Solicito visita. Inmueble NO DISPONIBLE. Desea en este sector.</t>
-        </is>
-      </c>
-      <c r="J46" t="inlineStr"/>
-      <c r="K46" t="inlineStr"/>
-      <c r="L46" t="inlineStr"/>
-      <c r="M46" t="inlineStr"/>
-      <c r="N46" t="n">
+      <c r="I47" s="1" t="inlineStr">
+        <is>
+          <t>Contenedor para sincronizar citas antiguas o sin datos en la nube.</t>
+        </is>
+      </c>
+      <c r="J47" s="1" t="inlineStr"/>
+      <c r="K47" t="inlineStr"/>
+      <c r="L47" t="inlineStr"/>
+      <c r="M47" t="inlineStr">
+        <is>
+          <t>manual</t>
+        </is>
+      </c>
+      <c r="N47" t="n">
         <v>0</v>
       </c>
-      <c r="O46" t="inlineStr"/>
-      <c r="P46" t="inlineStr">
-        <is>
-          <t>{"id":"U-1780355426553551","fecha":"2026-06-03T15:44:18.888Z","nombre":"María Sildana Arango","celular":3248276336,"tipo":"cliente","estado":"inactivo","etiqueta":"inactivo","notas":"Interesada Codg, 625 Luis Carlos Galán - $155mll-Jennifer. Verificando la disponibilidad y Solicito visita. Inmueble NO DISPONIBLE. Desea en este sector."}</t>
+      <c r="O47" s="1" t="inlineStr"/>
+      <c r="P47" s="1" t="inlineStr">
+        <is>
+          <t>{"ID": "LEAD-AGENDA-GLOBAL", "Fecha Actualización": "2026-06-06T02:38:48.927Z", "Nombre": "Agenda Global (Citas Genéricas)", "Celular": "", "Tipo": "cliente", "Inmobiliaria/Agente": "", "Estado": "inactivo", "Etiqueta": "inactivo", "Notas": "Contenedor para sincronizar citas antiguas o sin datos en la nube.", "Preferencias (Filtros)": "", "Método Pago": "", "Presupuesto": "", "Frecuencia": 0, "Total Enviadas": "", "Historial (Resumen)": "{\"ID\":\"LEAD-AGENDA-GLOBAL\",\"Fecha Actualización\":\"2026-06-06T02:38:18.902Z\",\"Nombre\":\"Agenda Global (Citas Genéricas)\",\"Celular\":\"\",\"Tipo\":\"cliente\",\"Inmobiliaria/Agente\":\"\",\"Estado\":\"inactivo\",\"Etiqueta\":\"inactivo\",\"Notas\":\"Contenedor para sincronizar citas antiguas o sin datos en la nube.\",\"Preferencias (Filtros)\":\"\",\"Método Pago\":\"\",\"Presupuesto\":\"\",\"Frecuencia\":0,\"Total Enviadas\":\"\",\"Historial (Resumen)\":\"{\\\"ID\\\":\\\"LEAD-AGENDA-GLOBAL\\\",\\\"Fecha Actualización\\\":\\\"2026-06-06T02:37:48.329Z\\\",\\\"Nombre\\\":\\\"Agenda Global (Citas Genéricas)\\\",\\\"Celular\\\":\\\"\\\",\\\"Tipo\\\":\\\"cliente\\\",\\\"Inmobiliaria/Agente\\\":\\\"\\\",\\\"Estado\\\":\\\"inactivo\\\",\\\"Etiqueta\\\":\\\"inactivo\\\",\\\"Notas\\\":\\\"Contenedor para sincronizar citas antiguas o sin datos en la nube.\\\",\\\"Preferencias (Filtros)\\\":\\\"\\\",\\\"Método Pago\\\":\\\"\\\",\\\"Presupuesto\\\":\\\"\\\",\\\"Frecuencia\\\":0,\\\"Total Enviadas\\\":\\\"\\\",\\\"Historial (Resumen)\\\":\\\"{\\\\\\\"ID\\\\\\\":\\\\\\\"LEAD-AGENDA-GLOBAL\\\\\\\",\\\\\\\"Fecha Actualización\\\\\\\":\\\\\\\"2026-06-06T02:37:18.154Z\\\\\\\",\\\\\\\"Nombre\\\\\\\":\\\\\\\"Agenda Global (Citas Genéricas)\\\\\\\",\\\\\\\"Celular\\\\\\\":\\\\\\\"\\\\\\\",\\\\\\\"Tipo\\\\\\\":\\\\\\\"cliente\\\\\\\",\\\\\\\"Inmobiliaria/Agente\\\\\\\":\\\\\\\"\\\\\\\",\\\\\\\"Estado\\\\\\\":\\\\\\\"inactivo\\\\\\\",\\\\\\\"Etiqueta\\\\\\\":\\\\\\\"inactivo\\\\\\\",\\\\\\\"Notas\\\\\\\":\\\\\\\"Contenedor para sincronizar citas antiguas o sin datos en la nube.\\\\\\\",\\\\\\\"Preferencias (Filtros)\\\\\\\":\\\\\\\"\\\\\\\",\\\\\\\"Método Pago\\\\\\\":\\\\\\\"\\\\\\\",\\\\\\\"Presupuesto\\\\\\\":\\\\\\\"\\\\\\\",\\\\\\\"Frecuencia\\\\\\\":0,\\\\\\\"Total Enviadas\\\\\\\":\\\\\\\"\\\\\\\",\\\\\\\"Historial (Resumen)\\\\\\\":\\\\\\\"{\\\\\\\\\\\\\\\"ID\\\\\\\\\\\\\\\":\\\\\\\\\\\\\\\"LEAD-AGENDA-GLOBAL\\\\\\\\\\\\\\\",\\\\\\\\\\\\\\\"Fecha Actualización\\\\\\\\\\\\\\\":\\\\\\\\\\\\\\\"2026-06-06T02:37:00.781Z\\\\\\\\\\\\\\\",\\\\\\\\\\\\\\\"Nombre\\\\\\\\\\\\\\\":\\\\\\\\\\\\\\\"Agenda Global (Citas Genéricas)\\\\\\\\\\\\\\\",\\\\\\\\\\\\\\\"Celular\\\\\\\\\\\\\\\":\\\\\\\\\\\\\\\"\\\\\\\\\\\\\\\",\\\\\\\\\\\\\\\"Tipo\\\\\\\\\\\\\\\":\\\\\\\\\\\\\\\"cliente\\\\\\\\\\\\\\\",\\\\\\\\\\\\\\\"Inmobiliaria/Agente\\\\\\\\\\\\\\\":\\\\\\\\\\\\\\\"\\\\\\\\\\\\\\\",\\\\\\\\\\\\\\\"Estado\\\\\\\\\\\\\\\":\\\\\\\\\\\\\\\"inactivo\\\\\\\\\\\\\\\",\\\\\\\\\\\\\\\"Etiqueta\\\\\\\\\\\\\\\":\\\\\\\\\\\\\\\"inactivo\\\\\\\\\\\\\\\",\\\\\\\\\\\\\\\"Notas\\\\\\\\\\\\\\\":\\\\\\\\\\\\\\\"Contenedor para sincronizar citas antiguas o sin datos en la nube.\\\\\\\\\\\\\\\",\\\\\\\\\\\\\\\"Preferencias (Filtros)\\\\\\\\\\\\\\\":\\\\\\\\\\\\\\\"\\\\\\\\\\\\\\\",\\\\\\\\\\\\\\\"Método Pago\\\\\\\\\\\\\\\":\\\\\\\\\\\\\\\"\\\\\\\\\\\\\\\",\\\\\\\\\\\\\\\"Presupuesto\\\\\\\\\\\\\\\":\\\\\\\\\\\\\\\"\\\\\\\\\\\\\\\",\\\\\\\\\\\\\\\"Frecuencia\\\\\\\\\\\\\\\":0,\\\\\\\\\\\\\\\"Total Enviadas\\\\\\\\\\\\\\\":\\\\\\\\\\\\\\\"\\\\\\\\\\\\\\\",\\\\\\\\\\\\\\\"Historial (Resumen)\\\\\\\\\\\\\\\":\\\\\\\\\\\\\\\"{\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\"ID\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\":\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\"LEAD-AGENDA-GLOBAL\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\",\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\"Fecha Actualización\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\":\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\"2026-06-06T02:36:45.259Z\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\",\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\"Nombre\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\":\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\"Agenda Global (Citas Genéricas)\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\",\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\"Celular\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\":0,\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\"Tipo\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\":\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\"cliente\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\",\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\"Inmobiliaria/Agente\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\":\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\"\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\",\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\"Estado\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\":\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\"inactivo\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\",\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\"Etiqueta\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\":\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\"inactivo\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\",\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\"Notas\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\":\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\"Contenedor para sincronizar citas antiguas o sin datos en la nube.\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\",\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\"Preferencias (Filtros)\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\":\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\"\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\",\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\"Método Pago\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\":\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\"\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\",\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\"Presupuesto\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\":\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\"\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\",\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\"Frecuencia\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\":0,\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\"Total Enviadas\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\":\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\"\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\",\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\"Historial (Resumen)\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\":\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\"{\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\"id\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\":\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\"LEAD-AGENDA-GLOBAL\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\",\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\"fecha\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\":\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\"2026-06-06T02:36:15.378Z\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\",\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\"nombre\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\":\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\"Agenda Global (Citas Genéricas)\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\",\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\"celular\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\":0,\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\"tipo\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\":\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\"cliente\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\",\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\"estado\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\":\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\"inactivo\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\",\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\"etiqueta\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\":\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\"inactivo\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\",\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\"notas\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\":\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\"Contenedor para sincronizar citas antiguas o sin datos en la nube.\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\",\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\"metodoPago\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\":[],\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\"fromCloud\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\":true,\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\"visitas\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\":[{\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\"id\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\":\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\"1780002087534\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\",\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\"codigo\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\":\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\"223\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\",\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\"fecha\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\":\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\"2026-05-29\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\",\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\"hora\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\":\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\"09:00\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\",\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\"estado\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\":\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\"agendada\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\",\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\"oferto\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\":\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\"no\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\",\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\"oferta\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\":\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\"\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\",\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\"notas\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\":\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\"Don Ignacio enseña la casa\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\",\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\"cliente\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\":\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\"Oscar Luis Suarez Cubillos\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\",\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\"celular\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\":\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\"3118571606\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\",\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\"inmobiliaria\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\":\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\"\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\",\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\"updatedAt\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\":1780002087534},{\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\"id\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\":\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\"1779744890238\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\",\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\"codigo\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\":\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\"449\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\",\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\"fecha\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\":\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\"2026-05-26\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\",\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\"hora\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\":\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\"\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\",\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\"estado\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\":\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\"agendada\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\",\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\"oferto\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\":\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\"no\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\",\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\"oferta\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\":\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\"\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\",\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\"notas\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\":\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\"\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\",\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\"cliente\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\":\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\"Paola\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\",\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\"celular\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\":\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\"+1 (720) 581-2521\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\",\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\"inmobiliaria\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\":\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\"\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\",\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\"updatedAt\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\":1779744890238},{\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\"id\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\":\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\"1779803459727\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\",\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\"codigo\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\":\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\"325\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\",\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\"fecha\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\":\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\"2026-05-26\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\",\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\"hora\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\":\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\"\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\",\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\"estado\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\":\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\"solicito_visita\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\",\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\"oferto\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\":\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\"no\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\",\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\"oferta\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\":\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\"\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\",\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\"notas\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\":\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\"\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\",\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\"cliente\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\":\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\"Paola\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\",\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\"celular\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\":\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\"+1 (720) 581-2521\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\",\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\"inmobiliaria\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\":\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\"\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\",\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\"updatedAt\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\":1779803459727},{\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\"id\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\":\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\"1779803499789\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\",\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\"codigo\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\":\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\"514\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\",\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\"fecha\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\":\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\"2026-05-26\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\",\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\"hora\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\":\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\"\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\",\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\"estado\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\":\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\"solicito_visita\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\",\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\"oferto\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\":\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\"no\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\",\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\"oferta\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\":\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\"\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\",\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\"notas\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\":\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\"\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\",\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\"cliente\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\":\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\"Paola\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\",\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\"celular\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\":\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\"+1 (720) 581-2521\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\",\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\"inmobiliaria\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\":\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\"\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\",\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\"updatedAt\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\":1779803499789},{\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\"id\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\":\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\"1780001589171\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\",\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\"codigo\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\":\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\"078\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\",\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\"fecha\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\":\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\"2026-05-29\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\",\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\"hora\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\":\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\"16:00\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\",\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\"estado\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\":\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\"agendada\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\",\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\"oferto\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\":\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\"no\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\",\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\"oferta\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\":\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\"\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\",\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\"notas\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\":\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\"\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\",\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\"cliente\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\":\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\"Martha Cubillos\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\",\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\"celular\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\":\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\"3209029142\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\",\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\"inmobiliaria\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\":\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\"\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\",\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\"updatedAt\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\":1780001589171}]}\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\",\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\"Full_JSON\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\":\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\"\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\",\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\"id\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\":\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\"LEAD-AGENDA-GLOBAL\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\",\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\"nombre\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\":\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\"Agenda Global (Citas Genéricas)\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\",\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\"tipo\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\":\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\"cliente\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\",\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\"estado\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\":\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\"inactivo\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\",\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\"etiqueta\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\":\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\"inactivo\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\",\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\"notas\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\":\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\"Contenedor para sincronizar citas antiguas o sin datos en la nube.\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\",\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\"metodoPago\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\":[],\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\"fromCloud\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\":true,\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\"visitas\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\":[{\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\"id\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\":\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\"1780002087534\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\",\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\"codigo\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\":\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\"223\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\",\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\"fecha\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\":\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\"2026-05-29\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\",\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\"hora\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\":\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\"09:00\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\",\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\"estado\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\":\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\"agendada\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\",\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\"oferto\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\":\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\"no\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\",\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\"oferta\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\":\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\"\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\",\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\"notas\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\":\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\"Don Ignacio enseña la casa\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\",\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\"cliente\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\":\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\"Oscar Luis Suarez Cubillos\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\",\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\"celular\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\":\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\"3118571606\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\",\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\"inmobiliaria\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\":\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\"\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\",\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\"updatedAt\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\":1780002087534},{\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\"id\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\":\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\"1779744890238\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\",\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\"codigo\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\":\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\"449\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\",\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\"fecha\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\":\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\"2026-05-26\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\",\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\"hora\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\":\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\"\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\",\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\"estado\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\":\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\"agendada\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\",\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\"oferto\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\":\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\"no\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\",\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\"oferta\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\":\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\"\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\",\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\"notas\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\":\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\"\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\",\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\"cliente\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\":\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\"Paola\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\",\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\"celular\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\":\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\"+1 (720) 581-2521\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\",\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\"inmobiliaria\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\":\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\"\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\",\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\"updatedAt\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\":1779744890238},{\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\"id\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\":\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\"1779803459727\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\",\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\"codigo\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\":\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\"325\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\",\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\"fecha\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\":\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\"2026-05-26\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\",\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\"hora\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\":\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\"\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\",\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\"estado\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\":\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\"solicito_visita\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\",\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\"oferto\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\":\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\"no\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\",\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\"oferta\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\":\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\"\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\",\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\"notas\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\":\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\"\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\",\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\"cliente\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\":\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\"Paola\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\",\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\"celular\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\":\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\"+1 (720) 581-2521\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\",\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\"inmobiliaria\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\":\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\"\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\",\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\"updatedAt\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\":1779803459727},{\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\"id\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\":\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\"1779803499789\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\",\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\"codigo\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\":\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\"514\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\",\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\"fecha\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\":\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\"2026-05-26\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\",\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\"hora\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\":\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\"\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\",\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\"estado\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\":\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\"solicito_visita\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\",\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\"oferto\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\":\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\"no\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\",\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\"oferta\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\":\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\"\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\",\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\"notas\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\":\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\"\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\",\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\"cliente\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\":\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\"Paola\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\",\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\"celular\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\":\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\"+1 (720) 581-2521\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\",\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\"inmobiliaria\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\":\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\"\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\",\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\"updatedAt\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\":1779803499789},{\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\"id\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\":\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\"1780001589171\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\",\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\"codigo\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\":\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\"078\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\",\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\"fecha\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\":\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\"2026-05-29\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\",\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\"hora\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\":\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\"16:00\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\",\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\"estado\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\":\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\"agendada\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\",\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\"oferto\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\":\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\"no\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\\",\\\\\\\\\\\\\\\\\\\\\\\\</t>
         </is>
       </c>
     </row>
